--- a/s60_signal/position-00857-601857.xlsx
+++ b/s60_signal/position-00857-601857.xlsx
@@ -1387,7 +1387,7 @@
     <t>2021-05-13</t>
   </si>
   <si>
-    <t>2021-07-20</t>
+    <t>2021-07-22</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -97479,10 +97479,10 @@
         <v>2.749870839434123</v>
       </c>
       <c r="D1907" t="s">
-        <v>273</v>
+        <v>447</v>
       </c>
       <c r="E1907">
-        <v>2.443407848879175</v>
+        <v>2.905695360994824</v>
       </c>
       <c r="F1907">
         <v>-1</v>
@@ -97491,10 +97491,10 @@
         <v>0.007630129160565878</v>
       </c>
       <c r="H1907">
-        <v>0.007036592151120826</v>
+        <v>0.007854304639005175</v>
       </c>
       <c r="I1907">
-        <v>0.3064629905549485</v>
+        <v>-0.1558245215607013</v>
       </c>
       <c r="J1907">
         <v>0.68350956878596</v>
@@ -97506,10 +97506,10 @@
         <v>5.19</v>
       </c>
       <c r="M1907">
-        <v>3.36</v>
+        <v>3.62</v>
       </c>
       <c r="N1907">
-        <v>4.74</v>
+        <v>5.38</v>
       </c>
       <c r="O1907">
         <v>1</v>
@@ -99023,10 +99023,10 @@
         <v>1</v>
       </c>
       <c r="B1938" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C1938">
-        <v>2.72596801966984</v>
+        <v>2.77411437304491</v>
       </c>
       <c r="D1938" t="s">
         <v>436</v>
@@ -99038,22 +99038,22 @@
         <v>1</v>
       </c>
       <c r="G1938">
-        <v>0.00561403198033016</v>
+        <v>0.00572588562695509</v>
       </c>
       <c r="H1938">
         <v>0.006357007506704671</v>
       </c>
       <c r="I1938">
-        <v>0.2970244736254903</v>
+        <v>0.2488781202504202</v>
       </c>
       <c r="J1938">
         <v>0.5308941104155001</v>
       </c>
       <c r="K1938">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L1938">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="M1938">
         <v>3.14</v>
@@ -99073,43 +99073,43 @@
         <v>2</v>
       </c>
       <c r="B1939" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1939">
-        <v>3.294708025816665</v>
+        <v>2.77535013746153</v>
       </c>
       <c r="D1939" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1939">
-        <v>2.95619578900392</v>
+        <v>3.02299249329533</v>
       </c>
       <c r="F1939">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1939">
-        <v>0.007085291974183336</v>
+        <v>0.005684649862538471</v>
       </c>
       <c r="H1939">
-        <v>0.00652380421099608</v>
+        <v>0.006357007506704671</v>
       </c>
       <c r="I1939">
-        <v>0.3385122368127451</v>
+        <v>0.2476423558338001</v>
       </c>
       <c r="J1939">
         <v>0.5308941104155001</v>
       </c>
       <c r="K1939">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L1939">
-        <v>5.19</v>
+        <v>4.23</v>
       </c>
       <c r="M1939">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1939">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1939">
         <v>1</v>
@@ -99123,10 +99123,10 @@
         <v>3</v>
       </c>
       <c r="B1940" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1940">
-        <v>3.2326023804211</v>
+        <v>3.294708025816665</v>
       </c>
       <c r="D1940" t="s">
         <v>273</v>
@@ -99138,22 +99138,22 @@
         <v>-1</v>
       </c>
       <c r="G1940">
-        <v>0.0072673976195789</v>
+        <v>0.007085291974183336</v>
       </c>
       <c r="H1940">
         <v>0.00652380421099608</v>
       </c>
       <c r="I1940">
-        <v>0.2764065914171798</v>
+        <v>0.3385122368127451</v>
       </c>
       <c r="J1940">
         <v>0.5308941104155001</v>
       </c>
       <c r="K1940">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1940">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1940">
         <v>3.36</v>
@@ -99170,63 +99170,63 @@
     </row>
     <row r="1941" spans="1:16">
       <c r="A1941" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1941" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1941">
-        <v>2.812196186654786</v>
+        <v>3.2326023804211</v>
       </c>
       <c r="D1941" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1941">
-        <v>3.067880564616677</v>
+        <v>2.95619578900392</v>
       </c>
       <c r="F1941">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1941">
-        <v>0.005787803813345213</v>
+        <v>0.0072673976195789</v>
       </c>
       <c r="H1941">
-        <v>0.006312119435383325</v>
+        <v>0.00652380421099608</v>
       </c>
       <c r="I1941">
-        <v>0.2556843779618907</v>
+        <v>0.2764065914171798</v>
       </c>
       <c r="J1941">
-        <v>0.5165985463004216</v>
+        <v>0.5308941104155001</v>
       </c>
       <c r="K1941">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1941">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1941">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1941">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1941">
         <v>1</v>
       </c>
       <c r="P1941" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1942" spans="1:16">
       <c r="A1942" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1942" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1942">
-        <v>2.813856041284828</v>
+        <v>2.812196186654786</v>
       </c>
       <c r="D1942" t="s">
         <v>436</v>
@@ -99238,22 +99238,22 @@
         <v>1</v>
       </c>
       <c r="G1942">
-        <v>0.005686143958715172</v>
+        <v>0.005787803813345213</v>
       </c>
       <c r="H1942">
         <v>0.006312119435383325</v>
       </c>
       <c r="I1942">
-        <v>0.2540245233318483</v>
+        <v>0.2556843779618907</v>
       </c>
       <c r="J1942">
         <v>0.5165985463004216</v>
       </c>
       <c r="K1942">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1942">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1942">
         <v>3.14</v>
@@ -99270,13 +99270,13 @@
     </row>
     <row r="1943" spans="1:16">
       <c r="A1943" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1943" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C1943">
-        <v>2.814519983136845</v>
+        <v>2.813856041284828</v>
       </c>
       <c r="D1943" t="s">
         <v>436</v>
@@ -99288,22 +99288,22 @@
         <v>1</v>
       </c>
       <c r="G1943">
-        <v>0.005645480016863155</v>
+        <v>0.005686143958715172</v>
       </c>
       <c r="H1943">
         <v>0.006312119435383325</v>
       </c>
       <c r="I1943">
-        <v>0.2533605814798312</v>
+        <v>0.2540245233318483</v>
       </c>
       <c r="J1943">
         <v>0.5165985463004216</v>
       </c>
       <c r="K1943">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="L1943">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="M1943">
         <v>3.14</v>
@@ -99320,46 +99320,46 @@
     </row>
     <row r="1944" spans="1:16">
       <c r="A1944" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1944" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1944">
-        <v>3.345743189707496</v>
+        <v>2.814519983136845</v>
       </c>
       <c r="D1944" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1944">
-        <v>3.004228884430584</v>
+        <v>3.067880564616677</v>
       </c>
       <c r="F1944">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1944">
-        <v>0.007034256810292505</v>
+        <v>0.005645480016863155</v>
       </c>
       <c r="H1944">
-        <v>0.006475771115569417</v>
+        <v>0.006312119435383325</v>
       </c>
       <c r="I1944">
-        <v>0.3415143052769118</v>
+        <v>0.2533605814798312</v>
       </c>
       <c r="J1944">
         <v>0.5165985463004216</v>
       </c>
       <c r="K1944">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L1944">
-        <v>5.19</v>
+        <v>4.23</v>
       </c>
       <c r="M1944">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1944">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1944">
         <v>1</v>
@@ -99370,13 +99370,13 @@
     </row>
     <row r="1945" spans="1:16">
       <c r="A1945" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1945" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1945">
-        <v>3.286925524058398</v>
+        <v>3.345743189707496</v>
       </c>
       <c r="D1945" t="s">
         <v>273</v>
@@ -99388,22 +99388,22 @@
         <v>-1</v>
       </c>
       <c r="G1945">
-        <v>0.007213074475941602</v>
+        <v>0.007034256810292505</v>
       </c>
       <c r="H1945">
         <v>0.006475771115569417</v>
       </c>
       <c r="I1945">
-        <v>0.2826966396278143</v>
+        <v>0.3415143052769118</v>
       </c>
       <c r="J1945">
         <v>0.5165985463004216</v>
       </c>
       <c r="K1945">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1945">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1945">
         <v>3.36</v>
@@ -99420,63 +99420,63 @@
     </row>
     <row r="1946" spans="1:16">
       <c r="A1946" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1946" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1946">
-        <v>2.834723748850407</v>
+        <v>3.286925524058398</v>
       </c>
       <c r="D1946" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1946">
-        <v>3.092441865066069</v>
+        <v>3.004228884430584</v>
       </c>
       <c r="F1946">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1946">
-        <v>0.005765276251149593</v>
+        <v>0.007213074475941602</v>
       </c>
       <c r="H1946">
-        <v>0.006287558134933932</v>
+        <v>0.006475771115569417</v>
       </c>
       <c r="I1946">
-        <v>0.2577181162156625</v>
+        <v>0.2826966396278143</v>
       </c>
       <c r="J1946">
-        <v>0.5087764760936087</v>
+        <v>0.5165985463004216</v>
       </c>
       <c r="K1946">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1946">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1946">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1946">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1946">
         <v>1</v>
       </c>
       <c r="P1946" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1947" spans="1:16">
       <c r="A1947" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1947" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1947">
-        <v>2.835601396459768</v>
+        <v>2.834723748850407</v>
       </c>
       <c r="D1947" t="s">
         <v>436</v>
@@ -99488,22 +99488,22 @@
         <v>1</v>
       </c>
       <c r="G1947">
-        <v>0.005664398603540233</v>
+        <v>0.005765276251149593</v>
       </c>
       <c r="H1947">
         <v>0.006287558134933932</v>
       </c>
       <c r="I1947">
-        <v>0.2568404686063017</v>
+        <v>0.2577181162156625</v>
       </c>
       <c r="J1947">
         <v>0.5087764760936087</v>
       </c>
       <c r="K1947">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1947">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1947">
         <v>3.14</v>
@@ -99520,13 +99520,13 @@
     </row>
     <row r="1948" spans="1:16">
       <c r="A1948" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1948" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C1948">
-        <v>2.835952455503513</v>
+        <v>2.835601396459768</v>
       </c>
       <c r="D1948" t="s">
         <v>436</v>
@@ -99538,22 +99538,22 @@
         <v>1</v>
       </c>
       <c r="G1948">
-        <v>0.005624047544496488</v>
+        <v>0.005664398603540233</v>
       </c>
       <c r="H1948">
         <v>0.006287558134933932</v>
       </c>
       <c r="I1948">
-        <v>0.2564894095625565</v>
+        <v>0.2568404686063017</v>
       </c>
       <c r="J1948">
         <v>0.5087764760936087</v>
       </c>
       <c r="K1948">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="L1948">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="M1948">
         <v>3.14</v>
@@ -99570,46 +99570,46 @@
     </row>
     <row r="1949" spans="1:16">
       <c r="A1949" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1949" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1949">
-        <v>3.373667980345818</v>
+        <v>2.835952455503513</v>
       </c>
       <c r="D1949" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1949">
-        <v>3.030511040325475</v>
+        <v>3.092441865066069</v>
       </c>
       <c r="F1949">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1949">
-        <v>0.007006332019654182</v>
+        <v>0.005624047544496488</v>
       </c>
       <c r="H1949">
-        <v>0.006449488959674525</v>
+        <v>0.006287558134933932</v>
       </c>
       <c r="I1949">
-        <v>0.3431569400203425</v>
+        <v>0.2564894095625565</v>
       </c>
       <c r="J1949">
         <v>0.5087764760936087</v>
       </c>
       <c r="K1949">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L1949">
-        <v>5.19</v>
+        <v>4.23</v>
       </c>
       <c r="M1949">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1949">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1949">
         <v>1</v>
@@ -99620,13 +99620,13 @@
     </row>
     <row r="1950" spans="1:16">
       <c r="A1950" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1950" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1950">
-        <v>3.316649390844287</v>
+        <v>3.373667980345818</v>
       </c>
       <c r="D1950" t="s">
         <v>273</v>
@@ -99638,22 +99638,22 @@
         <v>-1</v>
       </c>
       <c r="G1950">
-        <v>0.007183350609155714</v>
+        <v>0.007006332019654182</v>
       </c>
       <c r="H1950">
         <v>0.006449488959674525</v>
       </c>
       <c r="I1950">
-        <v>0.286138350518812</v>
+        <v>0.3431569400203425</v>
       </c>
       <c r="J1950">
         <v>0.5087764760936087</v>
       </c>
       <c r="K1950">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1950">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1950">
         <v>3.36</v>
@@ -99670,63 +99670,63 @@
     </row>
     <row r="1951" spans="1:16">
       <c r="A1951" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1951" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1951">
-        <v>2.849763859967231</v>
+        <v>3.316649390844287</v>
       </c>
       <c r="D1951" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1951">
-        <v>3.108839763992051</v>
+        <v>3.030511040325475</v>
       </c>
       <c r="F1951">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1951">
-        <v>0.005750236140032769</v>
+        <v>0.007183350609155714</v>
       </c>
       <c r="H1951">
-        <v>0.006271160236007951</v>
+        <v>0.006449488959674525</v>
       </c>
       <c r="I1951">
-        <v>0.2590759040248196</v>
+        <v>0.286138350518812</v>
       </c>
       <c r="J1951">
-        <v>0.5035542152891559</v>
+        <v>0.5087764760936087</v>
       </c>
       <c r="K1951">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1951">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1951">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1951">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1951">
         <v>1</v>
       </c>
       <c r="P1951" t="s">
-        <v>253</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1952" spans="1:16">
       <c r="A1952" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1952" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1952">
-        <v>2.850119281496147</v>
+        <v>2.849763859967231</v>
       </c>
       <c r="D1952" t="s">
         <v>436</v>
@@ -99738,22 +99738,22 @@
         <v>1</v>
       </c>
       <c r="G1952">
-        <v>0.005649880718503853</v>
+        <v>0.005750236140032769</v>
       </c>
       <c r="H1952">
         <v>0.006271160236007951</v>
       </c>
       <c r="I1952">
-        <v>0.258720482495904</v>
+        <v>0.2590759040248196</v>
       </c>
       <c r="J1952">
         <v>0.5035542152891559</v>
       </c>
       <c r="K1952">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1952">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1952">
         <v>3.14</v>
@@ -99770,13 +99770,13 @@
     </row>
     <row r="1953" spans="1:16">
       <c r="A1953" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1953" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C1953">
-        <v>2.850261450107713</v>
+        <v>2.850119281496147</v>
       </c>
       <c r="D1953" t="s">
         <v>436</v>
@@ -99788,22 +99788,22 @@
         <v>1</v>
       </c>
       <c r="G1953">
-        <v>0.005609738549892287</v>
+        <v>0.005649880718503853</v>
       </c>
       <c r="H1953">
         <v>0.006271160236007951</v>
       </c>
       <c r="I1953">
-        <v>0.2585783138843372</v>
+        <v>0.258720482495904</v>
       </c>
       <c r="J1953">
         <v>0.5035542152891559</v>
       </c>
       <c r="K1953">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="L1953">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="M1953">
         <v>3.14</v>
@@ -99820,46 +99820,46 @@
     </row>
     <row r="1954" spans="1:16">
       <c r="A1954" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1954" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1954">
-        <v>3.392311451417714</v>
+        <v>2.850261450107713</v>
       </c>
       <c r="D1954" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1954">
-        <v>3.048057836628437</v>
+        <v>3.108839763992051</v>
       </c>
       <c r="F1954">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1954">
-        <v>0.006987688548582287</v>
+        <v>0.005609738549892287</v>
       </c>
       <c r="H1954">
-        <v>0.006431942163371564</v>
+        <v>0.006271160236007951</v>
       </c>
       <c r="I1954">
-        <v>0.3442536147892774</v>
+        <v>0.2585783138843372</v>
       </c>
       <c r="J1954">
         <v>0.5035542152891559</v>
       </c>
       <c r="K1954">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L1954">
-        <v>5.19</v>
+        <v>4.23</v>
       </c>
       <c r="M1954">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1954">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1954">
         <v>1</v>
@@ -99870,13 +99870,13 @@
     </row>
     <row r="1955" spans="1:16">
       <c r="A1955" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1955" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1955">
-        <v>3.336493981901207</v>
+        <v>3.392311451417714</v>
       </c>
       <c r="D1955" t="s">
         <v>273</v>
@@ -99888,22 +99888,22 @@
         <v>-1</v>
       </c>
       <c r="G1955">
-        <v>0.007163506018098792</v>
+        <v>0.006987688548582287</v>
       </c>
       <c r="H1955">
         <v>0.006431942163371564</v>
       </c>
       <c r="I1955">
-        <v>0.2884361452727706</v>
+        <v>0.3442536147892774</v>
       </c>
       <c r="J1955">
         <v>0.5035542152891559</v>
       </c>
       <c r="K1955">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1955">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1955">
         <v>3.36</v>
@@ -99920,63 +99920,63 @@
     </row>
     <row r="1956" spans="1:16">
       <c r="A1956" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1956" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1956">
-        <v>2.882304897086411</v>
+        <v>3.336493981901207</v>
       </c>
       <c r="D1956" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1956">
-        <v>3.144318533628935</v>
+        <v>3.048057836628437</v>
       </c>
       <c r="F1956">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1956">
-        <v>0.005717695102913588</v>
+        <v>0.007163506018098792</v>
       </c>
       <c r="H1956">
-        <v>0.006235681466371066</v>
+        <v>0.006431942163371564</v>
       </c>
       <c r="I1956">
-        <v>0.2620136365425236</v>
+        <v>0.2884361452727706</v>
       </c>
       <c r="J1956">
-        <v>0.4922552440672183</v>
+        <v>0.5035542152891559</v>
       </c>
       <c r="K1956">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1956">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1956">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1956">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1956">
         <v>1</v>
       </c>
       <c r="P1956" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="1957" spans="1:16">
       <c r="A1957" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1957" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1957">
-        <v>2.881530421493133</v>
+        <v>2.882304897086411</v>
       </c>
       <c r="D1957" t="s">
         <v>436</v>
@@ -99988,22 +99988,22 @@
         <v>1</v>
       </c>
       <c r="G1957">
-        <v>0.005618469578506867</v>
+        <v>0.005717695102913588</v>
       </c>
       <c r="H1957">
         <v>0.006235681466371066</v>
       </c>
       <c r="I1957">
-        <v>0.2627881121358016</v>
+        <v>0.2620136365425236</v>
       </c>
       <c r="J1957">
         <v>0.4922552440672183</v>
       </c>
       <c r="K1957">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1957">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1957">
         <v>3.14</v>
@@ -100020,13 +100020,13 @@
     </row>
     <row r="1958" spans="1:16">
       <c r="A1958" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1958" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C1958">
-        <v>2.881220631255822</v>
+        <v>2.881530421493133</v>
       </c>
       <c r="D1958" t="s">
         <v>436</v>
@@ -100038,22 +100038,22 @@
         <v>1</v>
       </c>
       <c r="G1958">
-        <v>0.005578779368744179</v>
+        <v>0.005618469578506867</v>
       </c>
       <c r="H1958">
         <v>0.006235681466371066</v>
       </c>
       <c r="I1958">
-        <v>0.2630979023731128</v>
+        <v>0.2627881121358016</v>
       </c>
       <c r="J1958">
         <v>0.4922552440672183</v>
       </c>
       <c r="K1958">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="L1958">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="M1958">
         <v>3.14</v>
@@ -100070,46 +100070,46 @@
     </row>
     <row r="1959" spans="1:16">
       <c r="A1959" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1959" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C1959">
-        <v>3.432648778680031</v>
+        <v>2.886762764171116</v>
       </c>
       <c r="D1959" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1959">
-        <v>3.086022379934147</v>
+        <v>3.144318533628935</v>
       </c>
       <c r="F1959">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1959">
-        <v>0.00694735122131997</v>
+        <v>0.005653237235828883</v>
       </c>
       <c r="H1959">
-        <v>0.006393977620065853</v>
+        <v>0.006235681466371066</v>
       </c>
       <c r="I1959">
-        <v>0.346626398745884</v>
+        <v>0.2575557694578188</v>
       </c>
       <c r="J1959">
         <v>0.4922552440672183</v>
       </c>
       <c r="K1959">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L1959">
-        <v>5.19</v>
+        <v>4.27</v>
       </c>
       <c r="M1959">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1959">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1959">
         <v>1</v>
@@ -100120,13 +100120,13 @@
     </row>
     <row r="1960" spans="1:16">
       <c r="A1960" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1960" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1960">
-        <v>3.379430072544571</v>
+        <v>3.432648778680031</v>
       </c>
       <c r="D1960" t="s">
         <v>273</v>
@@ -100138,22 +100138,22 @@
         <v>-1</v>
       </c>
       <c r="G1960">
-        <v>0.00712056992745543</v>
+        <v>0.00694735122131997</v>
       </c>
       <c r="H1960">
         <v>0.006393977620065853</v>
       </c>
       <c r="I1960">
-        <v>0.2934076926104234</v>
+        <v>0.346626398745884</v>
       </c>
       <c r="J1960">
         <v>0.4922552440672183</v>
       </c>
       <c r="K1960">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1960">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1960">
         <v>3.36</v>
@@ -100170,63 +100170,63 @@
     </row>
     <row r="1961" spans="1:16">
       <c r="A1961" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1961" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1961">
-        <v>2.907310156141165</v>
+        <v>3.379430072544571</v>
       </c>
       <c r="D1961" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1961">
-        <v>3.171581211903909</v>
+        <v>3.086022379934147</v>
       </c>
       <c r="F1961">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1961">
-        <v>0.005692689843858835</v>
+        <v>0.00712056992745543</v>
       </c>
       <c r="H1961">
-        <v>0.006208418788096091</v>
+        <v>0.006393977620065853</v>
       </c>
       <c r="I1961">
-        <v>0.2642710557627441</v>
+        <v>0.2934076926104234</v>
       </c>
       <c r="J1961">
-        <v>0.4835728624509845</v>
+        <v>0.4922552440672183</v>
       </c>
       <c r="K1961">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1961">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1961">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1961">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1961">
         <v>1</v>
       </c>
       <c r="P1961" t="s">
-        <v>585</v>
+        <v>248</v>
       </c>
     </row>
     <row r="1962" spans="1:16">
       <c r="A1962" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1962" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1962">
-        <v>2.905667442386263</v>
+        <v>2.907310156141165</v>
       </c>
       <c r="D1962" t="s">
         <v>436</v>
@@ -100238,22 +100238,22 @@
         <v>1</v>
       </c>
       <c r="G1962">
-        <v>0.005594332557613737</v>
+        <v>0.005692689843858835</v>
       </c>
       <c r="H1962">
         <v>0.006208418788096091</v>
       </c>
       <c r="I1962">
-        <v>0.2659137695176459</v>
+        <v>0.2642710557627441</v>
       </c>
       <c r="J1962">
         <v>0.4835728624509845</v>
       </c>
       <c r="K1962">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1962">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1962">
         <v>3.14</v>
@@ -100270,13 +100270,13 @@
     </row>
     <row r="1963" spans="1:16">
       <c r="A1963" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1963" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C1963">
-        <v>2.911160256512733</v>
+        <v>2.905667442386263</v>
       </c>
       <c r="D1963" t="s">
         <v>436</v>
@@ -100288,22 +100288,22 @@
         <v>1</v>
       </c>
       <c r="G1963">
-        <v>0.005628839743487266</v>
+        <v>0.005594332557613737</v>
       </c>
       <c r="H1963">
         <v>0.006208418788096091</v>
       </c>
       <c r="I1963">
-        <v>0.2604209553911758</v>
+        <v>0.2659137695176459</v>
       </c>
       <c r="J1963">
         <v>0.4835728624509845</v>
       </c>
       <c r="K1963">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1963">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1963">
         <v>3.14</v>
@@ -100320,46 +100320,46 @@
     </row>
     <row r="1964" spans="1:16">
       <c r="A1964" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1964" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C1964">
-        <v>3.463644881049986</v>
+        <v>2.911160256512733</v>
       </c>
       <c r="D1964" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1964">
-        <v>3.115195182164692</v>
+        <v>3.171581211903909</v>
       </c>
       <c r="F1964">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1964">
-        <v>0.006916355118950016</v>
+        <v>0.005628839743487266</v>
       </c>
       <c r="H1964">
-        <v>0.006364804817835308</v>
+        <v>0.006208418788096091</v>
       </c>
       <c r="I1964">
-        <v>0.3484496988852936</v>
+        <v>0.2604209553911758</v>
       </c>
       <c r="J1964">
         <v>0.4835728624509845</v>
       </c>
       <c r="K1964">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L1964">
-        <v>5.19</v>
+        <v>4.27</v>
       </c>
       <c r="M1964">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1964">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1964">
         <v>1</v>
@@ -100370,13 +100370,13 @@
     </row>
     <row r="1965" spans="1:16">
       <c r="A1965" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1965" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1965">
-        <v>3.412423122686259</v>
+        <v>3.463644881049986</v>
       </c>
       <c r="D1965" t="s">
         <v>273</v>
@@ -100388,22 +100388,22 @@
         <v>-1</v>
       </c>
       <c r="G1965">
-        <v>0.007087576877313742</v>
+        <v>0.006916355118950016</v>
       </c>
       <c r="H1965">
         <v>0.006364804817835308</v>
       </c>
       <c r="I1965">
-        <v>0.2972279405215668</v>
+        <v>0.3484496988852936</v>
       </c>
       <c r="J1965">
         <v>0.4835728624509845</v>
       </c>
       <c r="K1965">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1965">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1965">
         <v>3.36</v>
@@ -100420,63 +100420,63 @@
     </row>
     <row r="1966" spans="1:16">
       <c r="A1966" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1966" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1966">
-        <v>2.925123519687019</v>
+        <v>3.412423122686259</v>
       </c>
       <c r="D1966" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1966">
-        <v>3.19100272632543</v>
+        <v>3.115195182164692</v>
       </c>
       <c r="F1966">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1966">
-        <v>0.005674876480312981</v>
+        <v>0.007087576877313742</v>
       </c>
       <c r="H1966">
-        <v>0.006188997273674571</v>
+        <v>0.006364804817835308</v>
       </c>
       <c r="I1966">
-        <v>0.2658792066384112</v>
+        <v>0.2972279405215668</v>
       </c>
       <c r="J1966">
-        <v>0.4773876667753407</v>
+        <v>0.4835728624509845</v>
       </c>
       <c r="K1966">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1966">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1966">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1966">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1966">
         <v>1</v>
       </c>
       <c r="P1966" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1967" spans="1:16">
       <c r="A1967" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1967" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1967">
-        <v>2.922862286364553</v>
+        <v>2.925123519687019</v>
       </c>
       <c r="D1967" t="s">
         <v>436</v>
@@ -100488,22 +100488,22 @@
         <v>1</v>
       </c>
       <c r="G1967">
-        <v>0.005577137713635447</v>
+        <v>0.005674876480312981</v>
       </c>
       <c r="H1967">
         <v>0.006188997273674571</v>
       </c>
       <c r="I1967">
-        <v>0.2681404399608773</v>
+        <v>0.2658792066384112</v>
       </c>
       <c r="J1967">
         <v>0.4773876667753407</v>
       </c>
       <c r="K1967">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1967">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1967">
         <v>3.14</v>
@@ -100520,13 +100520,13 @@
     </row>
     <row r="1968" spans="1:16">
       <c r="A1968" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1968" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C1968">
-        <v>2.928540656361292</v>
+        <v>2.922862286364553</v>
       </c>
       <c r="D1968" t="s">
         <v>436</v>
@@ -100538,22 +100538,22 @@
         <v>1</v>
       </c>
       <c r="G1968">
-        <v>0.005611459343638707</v>
+        <v>0.005577137713635447</v>
       </c>
       <c r="H1968">
         <v>0.006188997273674571</v>
       </c>
       <c r="I1968">
-        <v>0.2624620699641378</v>
+        <v>0.2681404399608773</v>
       </c>
       <c r="J1968">
         <v>0.4773876667753407</v>
       </c>
       <c r="K1968">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1968">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1968">
         <v>3.14</v>
@@ -100570,46 +100570,46 @@
     </row>
     <row r="1969" spans="1:16">
       <c r="A1969" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1969" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C1969">
-        <v>3.485726029612034</v>
+        <v>2.928540656361292</v>
       </c>
       <c r="D1969" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1969">
-        <v>3.135977439634855</v>
+        <v>3.19100272632543</v>
       </c>
       <c r="F1969">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1969">
-        <v>0.006894273970387966</v>
+        <v>0.005611459343638707</v>
       </c>
       <c r="H1969">
-        <v>0.006344022560365145</v>
+        <v>0.006188997273674571</v>
       </c>
       <c r="I1969">
-        <v>0.3497485899771791</v>
+        <v>0.2624620699641378</v>
       </c>
       <c r="J1969">
         <v>0.4773876667753407</v>
       </c>
       <c r="K1969">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L1969">
-        <v>5.19</v>
+        <v>4.27</v>
       </c>
       <c r="M1969">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1969">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1969">
         <v>1</v>
@@ -100620,13 +100620,13 @@
     </row>
     <row r="1970" spans="1:16">
       <c r="A1970" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1970" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1970">
-        <v>3.435926866253705</v>
+        <v>3.485726029612034</v>
       </c>
       <c r="D1970" t="s">
         <v>273</v>
@@ -100638,22 +100638,22 @@
         <v>-1</v>
       </c>
       <c r="G1970">
-        <v>0.007064073133746295</v>
+        <v>0.006894273970387966</v>
       </c>
       <c r="H1970">
         <v>0.006344022560365145</v>
       </c>
       <c r="I1970">
-        <v>0.2999494266188503</v>
+        <v>0.3497485899771791</v>
       </c>
       <c r="J1970">
         <v>0.4773876667753407</v>
       </c>
       <c r="K1970">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1970">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1970">
         <v>3.36</v>
@@ -100670,63 +100670,63 @@
     </row>
     <row r="1971" spans="1:16">
       <c r="A1971" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1971" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1971">
-        <v>2.92262134024316</v>
+        <v>3.435926866253705</v>
       </c>
       <c r="D1971" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1971">
-        <v>3.18827465568178</v>
+        <v>3.135977439634855</v>
       </c>
       <c r="F1971">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1971">
-        <v>0.00567737865975684</v>
+        <v>0.007064073133746295</v>
       </c>
       <c r="H1971">
-        <v>0.006191725344318221</v>
+        <v>0.006344022560365145</v>
       </c>
       <c r="I1971">
-        <v>0.2656533154386196</v>
+        <v>0.2999494266188503</v>
       </c>
       <c r="J1971">
-        <v>0.4782564790822359</v>
+        <v>0.4773876667753407</v>
       </c>
       <c r="K1971">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1971">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1971">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1971">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1971">
         <v>1</v>
       </c>
       <c r="P1971" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1972" spans="1:16">
       <c r="A1972" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1972" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1972">
-        <v>2.920446988151384</v>
+        <v>2.92262134024316</v>
       </c>
       <c r="D1972" t="s">
         <v>436</v>
@@ -100738,22 +100738,22 @@
         <v>1</v>
       </c>
       <c r="G1972">
-        <v>0.005579553011848615</v>
+        <v>0.00567737865975684</v>
       </c>
       <c r="H1972">
         <v>0.006191725344318221</v>
       </c>
       <c r="I1972">
-        <v>0.2678276675303954</v>
+        <v>0.2656533154386196</v>
       </c>
       <c r="J1972">
         <v>0.4782564790822359</v>
       </c>
       <c r="K1972">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1972">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1972">
         <v>3.14</v>
@@ -100770,13 +100770,13 @@
     </row>
     <row r="1973" spans="1:16">
       <c r="A1973" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1973" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C1973">
-        <v>2.926099293778917</v>
+        <v>2.920446988151384</v>
       </c>
       <c r="D1973" t="s">
         <v>436</v>
@@ -100788,22 +100788,22 @@
         <v>1</v>
       </c>
       <c r="G1973">
-        <v>0.005613900706221083</v>
+        <v>0.005579553011848615</v>
       </c>
       <c r="H1973">
         <v>0.006191725344318221</v>
       </c>
       <c r="I1973">
-        <v>0.2621753619028633</v>
+        <v>0.2678276675303954</v>
       </c>
       <c r="J1973">
         <v>0.4782564790822359</v>
       </c>
       <c r="K1973">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1973">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1973">
         <v>3.14</v>
@@ -100820,46 +100820,46 @@
     </row>
     <row r="1974" spans="1:16">
       <c r="A1974" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1974" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C1974">
-        <v>3.482624369676418</v>
+        <v>2.926099293778917</v>
       </c>
       <c r="D1974" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1974">
-        <v>3.133058230283687</v>
+        <v>3.18827465568178</v>
       </c>
       <c r="F1974">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1974">
-        <v>0.006897375630323582</v>
+        <v>0.005613900706221083</v>
       </c>
       <c r="H1974">
-        <v>0.006346941769716313</v>
+        <v>0.006191725344318221</v>
       </c>
       <c r="I1974">
-        <v>0.349566139392731</v>
+        <v>0.2621753619028633</v>
       </c>
       <c r="J1974">
         <v>0.4782564790822359</v>
       </c>
       <c r="K1974">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L1974">
-        <v>5.19</v>
+        <v>4.27</v>
       </c>
       <c r="M1974">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1974">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1974">
         <v>1</v>
@@ -100870,13 +100870,13 @@
     </row>
     <row r="1975" spans="1:16">
       <c r="A1975" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1975" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1975">
-        <v>3.432625379487503</v>
+        <v>3.482624369676418</v>
       </c>
       <c r="D1975" t="s">
         <v>273</v>
@@ -100888,22 +100888,22 @@
         <v>-1</v>
       </c>
       <c r="G1975">
-        <v>0.007067374620512497</v>
+        <v>0.006897375630323582</v>
       </c>
       <c r="H1975">
         <v>0.006346941769716313</v>
       </c>
       <c r="I1975">
-        <v>0.2995671492038161</v>
+        <v>0.349566139392731</v>
       </c>
       <c r="J1975">
         <v>0.4782564790822359</v>
       </c>
       <c r="K1975">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1975">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1975">
         <v>3.36</v>
@@ -100920,63 +100920,63 @@
     </row>
     <row r="1976" spans="1:16">
       <c r="A1976" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1976" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1976">
-        <v>2.929140321660022</v>
+        <v>3.432625379487503</v>
       </c>
       <c r="D1976" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1976">
-        <v>3.19538215625433</v>
+        <v>3.133058230283687</v>
       </c>
       <c r="F1976">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1976">
-        <v>0.005670859678339977</v>
+        <v>0.007067374620512497</v>
       </c>
       <c r="H1976">
-        <v>0.00618461784374567</v>
+        <v>0.006346941769716313</v>
       </c>
       <c r="I1976">
-        <v>0.2662418345943078</v>
+        <v>0.2995671492038161</v>
       </c>
       <c r="J1976">
-        <v>0.4759929438680478</v>
+        <v>0.4782564790822359</v>
       </c>
       <c r="K1976">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1976">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1976">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1976">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1976">
         <v>1</v>
       </c>
       <c r="P1976" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1977" spans="1:16">
       <c r="A1977" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1977" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1977">
-        <v>2.926739616046827</v>
+        <v>2.929140321660022</v>
       </c>
       <c r="D1977" t="s">
         <v>436</v>
@@ -100988,22 +100988,22 @@
         <v>1</v>
       </c>
       <c r="G1977">
-        <v>0.005573260383953173</v>
+        <v>0.005670859678339977</v>
       </c>
       <c r="H1977">
         <v>0.00618461784374567</v>
       </c>
       <c r="I1977">
-        <v>0.268642540207503</v>
+        <v>0.2662418345943078</v>
       </c>
       <c r="J1977">
         <v>0.4759929438680478</v>
       </c>
       <c r="K1977">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1977">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1977">
         <v>3.14</v>
@@ -101020,13 +101020,13 @@
     </row>
     <row r="1978" spans="1:16">
       <c r="A1978" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1978" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C1978">
-        <v>2.932459827730785</v>
+        <v>2.926739616046827</v>
       </c>
       <c r="D1978" t="s">
         <v>436</v>
@@ -101038,22 +101038,22 @@
         <v>1</v>
       </c>
       <c r="G1978">
-        <v>0.005607540172269214</v>
+        <v>0.005573260383953173</v>
       </c>
       <c r="H1978">
         <v>0.00618461784374567</v>
       </c>
       <c r="I1978">
-        <v>0.2629223285235454</v>
+        <v>0.268642540207503</v>
       </c>
       <c r="J1978">
         <v>0.4759929438680478</v>
       </c>
       <c r="K1978">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1978">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1978">
         <v>3.14</v>
@@ -101070,46 +101070,46 @@
     </row>
     <row r="1979" spans="1:16">
       <c r="A1979" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1979" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C1979">
-        <v>3.49070519039107</v>
+        <v>2.932459827730785</v>
       </c>
       <c r="D1979" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1979">
-        <v>3.14066370860336</v>
+        <v>3.19538215625433</v>
       </c>
       <c r="F1979">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1979">
-        <v>0.006889294809608931</v>
+        <v>0.005607540172269214</v>
       </c>
       <c r="H1979">
-        <v>0.00633933629139664</v>
+        <v>0.00618461784374567</v>
       </c>
       <c r="I1979">
-        <v>0.3500414817877098</v>
+        <v>0.2629223285235454</v>
       </c>
       <c r="J1979">
         <v>0.4759929438680478</v>
       </c>
       <c r="K1979">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L1979">
-        <v>5.19</v>
+        <v>4.27</v>
       </c>
       <c r="M1979">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1979">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1979">
         <v>1</v>
@@ -101120,13 +101120,13 @@
     </row>
     <row r="1980" spans="1:16">
       <c r="A1980" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1980" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1980">
-        <v>3.441226813301419</v>
+        <v>3.49070519039107</v>
       </c>
       <c r="D1980" t="s">
         <v>273</v>
@@ -101138,22 +101138,22 @@
         <v>-1</v>
       </c>
       <c r="G1980">
-        <v>0.007058773186698582</v>
+        <v>0.006889294809608931</v>
       </c>
       <c r="H1980">
         <v>0.00633933629139664</v>
       </c>
       <c r="I1980">
-        <v>0.3005631046980586</v>
+        <v>0.3500414817877098</v>
       </c>
       <c r="J1980">
         <v>0.4759929438680478</v>
       </c>
       <c r="K1980">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1980">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1980">
         <v>3.36</v>
@@ -101170,63 +101170,63 @@
     </row>
     <row r="1981" spans="1:16">
       <c r="A1981" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1981" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1981">
-        <v>2.939070121195086</v>
+        <v>3.441226813301419</v>
       </c>
       <c r="D1981" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1981">
-        <v>3.206208396025199</v>
+        <v>3.14066370860336</v>
       </c>
       <c r="F1981">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1981">
-        <v>0.005660929878804914</v>
+        <v>0.007058773186698582</v>
       </c>
       <c r="H1981">
-        <v>0.006173791603974802</v>
+        <v>0.00633933629139664</v>
       </c>
       <c r="I1981">
-        <v>0.2671382748301125</v>
+        <v>0.3005631046980586</v>
       </c>
       <c r="J1981">
-        <v>0.4725450968072616</v>
+        <v>0.4759929438680478</v>
       </c>
       <c r="K1981">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1981">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1981">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1981">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1981">
         <v>1</v>
       </c>
       <c r="P1981" t="s">
-        <v>249</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1982" spans="1:16">
       <c r="A1982" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1982" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1982">
-        <v>2.936324630875813</v>
+        <v>2.939070121195086</v>
       </c>
       <c r="D1982" t="s">
         <v>436</v>
@@ -101238,22 +101238,22 @@
         <v>1</v>
       </c>
       <c r="G1982">
-        <v>0.005563675369124188</v>
+        <v>0.005660929878804914</v>
       </c>
       <c r="H1982">
         <v>0.006173791603974802</v>
       </c>
       <c r="I1982">
-        <v>0.2698837651493857</v>
+        <v>0.2671382748301125</v>
       </c>
       <c r="J1982">
         <v>0.4725450968072616</v>
       </c>
       <c r="K1982">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1982">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1982">
         <v>3.14</v>
@@ -101270,13 +101270,13 @@
     </row>
     <row r="1983" spans="1:16">
       <c r="A1983" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1983" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C1983">
-        <v>2.942148277971595</v>
+        <v>2.936324630875813</v>
       </c>
       <c r="D1983" t="s">
         <v>436</v>
@@ -101288,22 +101288,22 @@
         <v>1</v>
       </c>
       <c r="G1983">
-        <v>0.005597851722028405</v>
+        <v>0.005563675369124188</v>
       </c>
       <c r="H1983">
         <v>0.006173791603974802</v>
       </c>
       <c r="I1983">
-        <v>0.264060118053604</v>
+        <v>0.2698837651493857</v>
       </c>
       <c r="J1983">
         <v>0.4725450968072616</v>
       </c>
       <c r="K1983">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1983">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1983">
         <v>3.14</v>
@@ -101320,46 +101320,46 @@
     </row>
     <row r="1984" spans="1:16">
       <c r="A1984" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1984" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C1984">
-        <v>3.503014004398076</v>
+        <v>2.947971925067377</v>
       </c>
       <c r="D1984" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1984">
-        <v>3.152248474727601</v>
+        <v>3.206208396025199</v>
       </c>
       <c r="F1984">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1984">
-        <v>0.006876985995601924</v>
+        <v>0.005632028074932623</v>
       </c>
       <c r="H1984">
-        <v>0.006327751525272399</v>
+        <v>0.006173791603974802</v>
       </c>
       <c r="I1984">
-        <v>0.350765529670475</v>
+        <v>0.2582364709578213</v>
       </c>
       <c r="J1984">
         <v>0.4725450968072616</v>
       </c>
       <c r="K1984">
-        <v>3.57</v>
+        <v>2.84</v>
       </c>
       <c r="L1984">
-        <v>5.19</v>
+        <v>4.29</v>
       </c>
       <c r="M1984">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1984">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1984">
         <v>1</v>
@@ -101370,13 +101370,13 @@
     </row>
     <row r="1985" spans="1:16">
       <c r="A1985" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1985" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1985">
-        <v>3.454328632132406</v>
+        <v>3.503014004398076</v>
       </c>
       <c r="D1985" t="s">
         <v>273</v>
@@ -101388,22 +101388,22 @@
         <v>-1</v>
       </c>
       <c r="G1985">
-        <v>0.007045671367867595</v>
+        <v>0.006876985995601924</v>
       </c>
       <c r="H1985">
         <v>0.006327751525272399</v>
       </c>
       <c r="I1985">
-        <v>0.3020801574048044</v>
+        <v>0.350765529670475</v>
       </c>
       <c r="J1985">
         <v>0.4725450968072616</v>
       </c>
       <c r="K1985">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1985">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1985">
         <v>3.36</v>
@@ -101420,63 +101420,63 @@
     </row>
     <row r="1986" spans="1:16">
       <c r="A1986" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1986" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1986">
-        <v>2.956264096115409</v>
+        <v>3.454328632132406</v>
       </c>
       <c r="D1986" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1986">
-        <v>3.224954604792496</v>
+        <v>3.152248474727601</v>
       </c>
       <c r="F1986">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1986">
-        <v>0.005643735903884591</v>
+        <v>0.007045671367867595</v>
       </c>
       <c r="H1986">
-        <v>0.006155045395207505</v>
+        <v>0.006327751525272399</v>
       </c>
       <c r="I1986">
-        <v>0.2686905086770865</v>
+        <v>0.3020801574048044</v>
       </c>
       <c r="J1986">
-        <v>0.466574966626594</v>
+        <v>0.4725450968072616</v>
       </c>
       <c r="K1986">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1986">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1986">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1986">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1986">
         <v>1</v>
       </c>
       <c r="P1986" t="s">
-        <v>589</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1987" spans="1:16">
       <c r="A1987" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1987" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1987">
-        <v>2.952921592778069</v>
+        <v>2.956264096115409</v>
       </c>
       <c r="D1987" t="s">
         <v>436</v>
@@ -101488,22 +101488,22 @@
         <v>1</v>
       </c>
       <c r="G1987">
-        <v>0.005547078407221932</v>
+        <v>0.005643735903884591</v>
       </c>
       <c r="H1987">
         <v>0.006155045395207505</v>
       </c>
       <c r="I1987">
-        <v>0.2720330120144268</v>
+        <v>0.2686905086770865</v>
       </c>
       <c r="J1987">
         <v>0.466574966626594</v>
       </c>
       <c r="K1987">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1987">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1987">
         <v>3.14</v>
@@ -101520,13 +101520,13 @@
     </row>
     <row r="1988" spans="1:16">
       <c r="A1988" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1988" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="C1988">
-        <v>2.964927094780473</v>
+        <v>2.967587342444334</v>
       </c>
       <c r="D1988" t="s">
         <v>436</v>
@@ -101538,22 +101538,22 @@
         <v>1</v>
       </c>
       <c r="G1988">
-        <v>0.005615072905219527</v>
+        <v>0.005552412657555666</v>
       </c>
       <c r="H1988">
         <v>0.006155045395207505</v>
       </c>
       <c r="I1988">
-        <v>0.2600275100120224</v>
+        <v>0.2573672623481613</v>
       </c>
       <c r="J1988">
         <v>0.466574966626594</v>
       </c>
       <c r="K1988">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="L1988">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="M1988">
         <v>3.14</v>
@@ -101570,46 +101570,46 @@
     </row>
     <row r="1989" spans="1:16">
       <c r="A1989" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1989" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="C1989">
-        <v>3.52432736914306</v>
+        <v>2.952921592778069</v>
       </c>
       <c r="D1989" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1989">
-        <v>3.172308112134645</v>
+        <v>3.224954604792496</v>
       </c>
       <c r="F1989">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1989">
-        <v>0.006855672630856941</v>
+        <v>0.005547078407221932</v>
       </c>
       <c r="H1989">
-        <v>0.006307691887865356</v>
+        <v>0.006155045395207505</v>
       </c>
       <c r="I1989">
-        <v>0.3520192570084149</v>
+        <v>0.2720330120144268</v>
       </c>
       <c r="J1989">
         <v>0.466574966626594</v>
       </c>
       <c r="K1989">
-        <v>3.57</v>
+        <v>2.78</v>
       </c>
       <c r="L1989">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M1989">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1989">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1989">
         <v>1</v>
@@ -101620,46 +101620,46 @@
     </row>
     <row r="1990" spans="1:16">
       <c r="A1990" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1990" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C1990">
-        <v>3.477015126818943</v>
+        <v>2.964927094780473</v>
       </c>
       <c r="D1990" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1990">
-        <v>3.172308112134645</v>
+        <v>3.224954604792496</v>
       </c>
       <c r="F1990">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1990">
-        <v>0.007022984873181057</v>
+        <v>0.005615072905219527</v>
       </c>
       <c r="H1990">
-        <v>0.006307691887865356</v>
+        <v>0.006155045395207505</v>
       </c>
       <c r="I1990">
-        <v>0.3047070146842978</v>
+        <v>0.2600275100120224</v>
       </c>
       <c r="J1990">
         <v>0.466574966626594</v>
       </c>
       <c r="K1990">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="L1990">
-        <v>5.25</v>
+        <v>4.29</v>
       </c>
       <c r="M1990">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1990">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1990">
         <v>1</v>
@@ -101670,113 +101670,113 @@
     </row>
     <row r="1991" spans="1:16">
       <c r="A1991" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1991" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C1991">
-        <v>2.968719772490877</v>
+        <v>3.52432736914306</v>
       </c>
       <c r="D1991" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1991">
-        <v>3.238534751951859</v>
+        <v>3.172308112134645</v>
       </c>
       <c r="F1991">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1991">
-        <v>0.005631280227509123</v>
+        <v>0.006855672630856941</v>
       </c>
       <c r="H1991">
-        <v>0.006141465248048142</v>
+        <v>0.006307691887865356</v>
       </c>
       <c r="I1991">
-        <v>0.2698149794609828</v>
+        <v>0.3520192570084149</v>
       </c>
       <c r="J1991">
-        <v>0.4622500789962232</v>
+        <v>0.466574966626594</v>
       </c>
       <c r="K1991">
-        <v>2.88</v>
+        <v>3.57</v>
       </c>
       <c r="L1991">
-        <v>4.3</v>
+        <v>5.19</v>
       </c>
       <c r="M1991">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1991">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1991">
         <v>1</v>
       </c>
       <c r="P1991" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1992" spans="1:16">
       <c r="A1992" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B1992" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C1992">
-        <v>2.979567281180461</v>
+        <v>3.477015126818943</v>
       </c>
       <c r="D1992" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1992">
-        <v>3.238534751951859</v>
+        <v>3.172308112134645</v>
       </c>
       <c r="F1992">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1992">
-        <v>0.005540432718819538</v>
+        <v>0.007022984873181057</v>
       </c>
       <c r="H1992">
-        <v>0.006141465248048142</v>
+        <v>0.006307691887865356</v>
       </c>
       <c r="I1992">
-        <v>0.258967470771398</v>
+        <v>0.3047070146842978</v>
       </c>
       <c r="J1992">
-        <v>0.4622500789962232</v>
+        <v>0.466574966626594</v>
       </c>
       <c r="K1992">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="L1992">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="M1992">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1992">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1992">
         <v>1</v>
       </c>
       <c r="P1992" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1993" spans="1:16">
       <c r="A1993" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1993" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1993">
-        <v>2.9649447803905</v>
+        <v>2.968719772490877</v>
       </c>
       <c r="D1993" t="s">
         <v>436</v>
@@ -101788,22 +101788,22 @@
         <v>1</v>
       </c>
       <c r="G1993">
-        <v>0.0055350552196095</v>
+        <v>0.005631280227509123</v>
       </c>
       <c r="H1993">
         <v>0.006141465248048142</v>
       </c>
       <c r="I1993">
-        <v>0.2735899715613597</v>
+        <v>0.2698149794609828</v>
       </c>
       <c r="J1993">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1993">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1993">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1993">
         <v>3.14</v>
@@ -101820,13 +101820,13 @@
     </row>
     <row r="1994" spans="1:16">
       <c r="A1994" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1994" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="C1994">
-        <v>2.977209775650726</v>
+        <v>2.979567281180461</v>
       </c>
       <c r="D1994" t="s">
         <v>436</v>
@@ -101838,22 +101838,22 @@
         <v>1</v>
       </c>
       <c r="G1994">
-        <v>0.005602790224349274</v>
+        <v>0.005540432718819538</v>
       </c>
       <c r="H1994">
         <v>0.006141465248048142</v>
       </c>
       <c r="I1994">
-        <v>0.2613249763011334</v>
+        <v>0.258967470771398</v>
       </c>
       <c r="J1994">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1994">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="L1994">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="M1994">
         <v>3.14</v>
@@ -101870,46 +101870,46 @@
     </row>
     <row r="1995" spans="1:16">
       <c r="A1995" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1995" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="C1995">
-        <v>3.539767217983484</v>
+        <v>2.9649447803905</v>
       </c>
       <c r="D1995" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1995">
-        <v>3.18683973457269</v>
+        <v>3.238534751951859</v>
       </c>
       <c r="F1995">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1995">
-        <v>0.006840232782016517</v>
+        <v>0.0055350552196095</v>
       </c>
       <c r="H1995">
-        <v>0.006293160265427311</v>
+        <v>0.006141465248048142</v>
       </c>
       <c r="I1995">
-        <v>0.3529274834107934</v>
+        <v>0.2735899715613597</v>
       </c>
       <c r="J1995">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1995">
-        <v>3.57</v>
+        <v>2.78</v>
       </c>
       <c r="L1995">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M1995">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1995">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1995">
         <v>1</v>
@@ -101920,46 +101920,46 @@
     </row>
     <row r="1996" spans="1:16">
       <c r="A1996" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1996" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C1996">
-        <v>3.493449699814352</v>
+        <v>2.977209775650726</v>
       </c>
       <c r="D1996" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E1996">
-        <v>3.18683973457269</v>
+        <v>3.238534751951859</v>
       </c>
       <c r="F1996">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1996">
-        <v>0.007006550300185647</v>
+        <v>0.005602790224349274</v>
       </c>
       <c r="H1996">
-        <v>0.006293160265427311</v>
+        <v>0.006141465248048142</v>
       </c>
       <c r="I1996">
-        <v>0.3066099652416616</v>
+        <v>0.2613249763011334</v>
       </c>
       <c r="J1996">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1996">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="L1996">
-        <v>5.25</v>
+        <v>4.29</v>
       </c>
       <c r="M1996">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1996">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1996">
         <v>1</v>
@@ -101970,113 +101970,113 @@
     </row>
     <row r="1997" spans="1:16">
       <c r="A1997" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1997" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C1997">
-        <v>2.976617917319586</v>
+        <v>3.539767217983484</v>
       </c>
       <c r="D1997" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1997">
-        <v>3.247145923744271</v>
+        <v>3.18683973457269</v>
       </c>
       <c r="F1997">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1997">
-        <v>0.005623382082680414</v>
+        <v>0.006840232782016517</v>
       </c>
       <c r="H1997">
-        <v>0.00613285407625573</v>
+        <v>0.006293160265427311</v>
       </c>
       <c r="I1997">
-        <v>0.2705280064246853</v>
+        <v>0.3529274834107934</v>
       </c>
       <c r="J1997">
-        <v>0.459507667597366</v>
+        <v>0.4622500789962232</v>
       </c>
       <c r="K1997">
-        <v>2.88</v>
+        <v>3.57</v>
       </c>
       <c r="L1997">
-        <v>4.3</v>
+        <v>5.19</v>
       </c>
       <c r="M1997">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1997">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1997">
         <v>1</v>
       </c>
       <c r="P1997" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1998" spans="1:16">
       <c r="A1998" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B1998" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C1998">
-        <v>2.987163760755296</v>
+        <v>3.493449699814352</v>
       </c>
       <c r="D1998" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E1998">
-        <v>3.247145923744271</v>
+        <v>3.18683973457269</v>
       </c>
       <c r="F1998">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1998">
-        <v>0.005532836239244704</v>
+        <v>0.007006550300185647</v>
       </c>
       <c r="H1998">
-        <v>0.00613285407625573</v>
+        <v>0.006293160265427311</v>
       </c>
       <c r="I1998">
-        <v>0.2599821629889751</v>
+        <v>0.3066099652416616</v>
       </c>
       <c r="J1998">
-        <v>0.459507667597366</v>
+        <v>0.4622500789962232</v>
       </c>
       <c r="K1998">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="L1998">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="M1998">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1998">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1998">
         <v>1</v>
       </c>
       <c r="P1998" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1999" spans="1:16">
       <c r="A1999" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1999" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C1999">
-        <v>2.972568684079323</v>
+        <v>2.990403147347507</v>
       </c>
       <c r="D1999" t="s">
         <v>436</v>
@@ -102088,22 +102088,22 @@
         <v>1</v>
       </c>
       <c r="G1999">
-        <v>0.005527431315920677</v>
+        <v>0.005609596852652493</v>
       </c>
       <c r="H1999">
         <v>0.00613285407625573</v>
       </c>
       <c r="I1999">
-        <v>0.2745772396649482</v>
+        <v>0.2567427763967642</v>
       </c>
       <c r="J1999">
         <v>0.459507667597366</v>
       </c>
       <c r="K1999">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="L1999">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1999">
         <v>3.14</v>
@@ -102120,13 +102120,13 @@
     </row>
     <row r="2000" spans="1:16">
       <c r="A2000" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2000" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="C2000">
-        <v>2.984998224023481</v>
+        <v>2.987163760755296</v>
       </c>
       <c r="D2000" t="s">
         <v>436</v>
@@ -102138,22 +102138,22 @@
         <v>1</v>
       </c>
       <c r="G2000">
-        <v>0.00559500177597652</v>
+        <v>0.005532836239244704</v>
       </c>
       <c r="H2000">
         <v>0.00613285407625573</v>
       </c>
       <c r="I2000">
-        <v>0.2621476997207903</v>
+        <v>0.2599821629889751</v>
       </c>
       <c r="J2000">
         <v>0.459507667597366</v>
       </c>
       <c r="K2000">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="L2000">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="M2000">
         <v>3.14</v>
@@ -102170,46 +102170,46 @@
     </row>
     <row r="2001" spans="1:16">
       <c r="A2001" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2001" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C2001">
-        <v>3.549557626677404</v>
+        <v>2.990948990783217</v>
       </c>
       <c r="D2001" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E2001">
-        <v>3.19605423687285</v>
+        <v>3.247145923744271</v>
       </c>
       <c r="F2001">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2001">
-        <v>0.006830442373322598</v>
+        <v>0.005509051009216784</v>
       </c>
       <c r="H2001">
-        <v>0.00628394576312715</v>
+        <v>0.00613285407625573</v>
       </c>
       <c r="I2001">
-        <v>0.3535033898045534</v>
+        <v>0.2561969329610543</v>
       </c>
       <c r="J2001">
         <v>0.459507667597366</v>
       </c>
       <c r="K2001">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2001">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2001">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2001">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2001">
         <v>1</v>
@@ -102220,46 +102220,46 @@
     </row>
     <row r="2002" spans="1:16">
       <c r="A2002" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2002" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C2002">
-        <v>3.503870863130009</v>
+        <v>2.984998224023481</v>
       </c>
       <c r="D2002" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E2002">
-        <v>3.19605423687285</v>
+        <v>3.247145923744271</v>
       </c>
       <c r="F2002">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2002">
-        <v>0.006996129136869991</v>
+        <v>0.00559500177597652</v>
       </c>
       <c r="H2002">
-        <v>0.00628394576312715</v>
+        <v>0.00613285407625573</v>
       </c>
       <c r="I2002">
-        <v>0.3078166262571589</v>
+        <v>0.2621476997207903</v>
       </c>
       <c r="J2002">
         <v>0.459507667597366</v>
       </c>
       <c r="K2002">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="L2002">
-        <v>5.25</v>
+        <v>4.29</v>
       </c>
       <c r="M2002">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2002">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2002">
         <v>1</v>
@@ -102270,113 +102270,113 @@
     </row>
     <row r="2003" spans="1:16">
       <c r="A2003" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2003" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="C2003">
-        <v>2.997405526308626</v>
+        <v>3.549557626677404</v>
       </c>
       <c r="D2003" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E2003">
-        <v>3.254860825476872</v>
+        <v>3.19605423687285</v>
       </c>
       <c r="F2003">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2003">
-        <v>0.005602594473691374</v>
+        <v>0.006830442373322598</v>
       </c>
       <c r="H2003">
-        <v>0.006125139174523129</v>
+        <v>0.00628394576312715</v>
       </c>
       <c r="I2003">
-        <v>0.2574552991682468</v>
+        <v>0.3535033898045534</v>
       </c>
       <c r="J2003">
-        <v>0.4570506925232892</v>
+        <v>0.459507667597366</v>
       </c>
       <c r="K2003">
-        <v>2.85</v>
+        <v>3.57</v>
       </c>
       <c r="L2003">
-        <v>4.3</v>
+        <v>5.19</v>
       </c>
       <c r="M2003">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2003">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2003">
         <v>1</v>
       </c>
       <c r="P2003" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2004" spans="1:16">
       <c r="A2004" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2004" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C2004">
-        <v>2.993969581710489</v>
+        <v>3.503870863130009</v>
       </c>
       <c r="D2004" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E2004">
-        <v>3.254860825476872</v>
+        <v>3.19605423687285</v>
       </c>
       <c r="F2004">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2004">
-        <v>0.005526030418289511</v>
+        <v>0.006996129136869991</v>
       </c>
       <c r="H2004">
-        <v>0.006125139174523129</v>
+        <v>0.00628394576312715</v>
       </c>
       <c r="I2004">
-        <v>0.260891243766384</v>
+        <v>0.3078166262571589</v>
       </c>
       <c r="J2004">
-        <v>0.4570506925232892</v>
+        <v>0.459507667597366</v>
       </c>
       <c r="K2004">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="L2004">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="M2004">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2004">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2004">
         <v>1</v>
       </c>
       <c r="P2004" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2005" spans="1:16">
       <c r="A2005" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2005" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="C2005">
-        <v>2.997681102486188</v>
+        <v>2.997405526308626</v>
       </c>
       <c r="D2005" t="s">
         <v>436</v>
@@ -102388,22 +102388,22 @@
         <v>1</v>
       </c>
       <c r="G2005">
-        <v>0.005502318897513812</v>
+        <v>0.005602594473691374</v>
       </c>
       <c r="H2005">
         <v>0.006125139174523129</v>
       </c>
       <c r="I2005">
-        <v>0.2571797229906849</v>
+        <v>0.2574552991682468</v>
       </c>
       <c r="J2005">
         <v>0.4570506925232892</v>
       </c>
       <c r="K2005">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="L2005">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M2005">
         <v>3.14</v>
@@ -102420,13 +102420,13 @@
     </row>
     <row r="2006" spans="1:16">
       <c r="A2006" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2006" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C2006">
-        <v>2.991976033233859</v>
+        <v>3.000258060934791</v>
       </c>
       <c r="D2006" t="s">
         <v>436</v>
@@ -102438,22 +102438,22 @@
         <v>1</v>
       </c>
       <c r="G2006">
-        <v>0.00558802396676614</v>
+        <v>0.00555974193906521</v>
       </c>
       <c r="H2006">
         <v>0.006125139174523129</v>
       </c>
       <c r="I2006">
-        <v>0.2628847922430135</v>
+        <v>0.2546027645420819</v>
       </c>
       <c r="J2006">
         <v>0.4570506925232892</v>
       </c>
       <c r="K2006">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="L2006">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="M2006">
         <v>3.14</v>
@@ -102470,46 +102470,46 @@
     </row>
     <row r="2007" spans="1:16">
       <c r="A2007" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2007" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C2007">
-        <v>3.558329027691858</v>
+        <v>2.997681102486188</v>
       </c>
       <c r="D2007" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E2007">
-        <v>3.204309673121749</v>
+        <v>3.254860825476872</v>
       </c>
       <c r="F2007">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2007">
-        <v>0.006821670972308143</v>
+        <v>0.005502318897513812</v>
       </c>
       <c r="H2007">
-        <v>0.006275690326878251</v>
+        <v>0.006125139174523129</v>
       </c>
       <c r="I2007">
-        <v>0.3540193545701094</v>
+        <v>0.2571797229906849</v>
       </c>
       <c r="J2007">
         <v>0.4570506925232892</v>
       </c>
       <c r="K2007">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2007">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2007">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2007">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2007">
         <v>1</v>
@@ -102520,46 +102520,46 @@
     </row>
     <row r="2008" spans="1:16">
       <c r="A2008" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2008" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C2008">
-        <v>3.513207368411501</v>
+        <v>2.991976033233859</v>
       </c>
       <c r="D2008" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E2008">
-        <v>3.204309673121749</v>
+        <v>3.254860825476872</v>
       </c>
       <c r="F2008">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2008">
-        <v>0.006986792631588498</v>
+        <v>0.00558802396676614</v>
       </c>
       <c r="H2008">
-        <v>0.006275690326878251</v>
+        <v>0.006125139174523129</v>
       </c>
       <c r="I2008">
-        <v>0.3088976952897524</v>
+        <v>0.2628847922430135</v>
       </c>
       <c r="J2008">
         <v>0.4570506925232892</v>
       </c>
       <c r="K2008">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="L2008">
-        <v>5.25</v>
+        <v>4.29</v>
       </c>
       <c r="M2008">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2008">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2008">
         <v>1</v>
@@ -102570,113 +102570,113 @@
     </row>
     <row r="2009" spans="1:16">
       <c r="A2009" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2009" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="C2009">
-        <v>3.007962728062543</v>
+        <v>3.558329027691858</v>
       </c>
       <c r="D2009" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E2009">
-        <v>3.266492268812767</v>
+        <v>3.204309673121749</v>
       </c>
       <c r="F2009">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2009">
-        <v>0.005592037271937457</v>
+        <v>0.006821670972308143</v>
       </c>
       <c r="H2009">
-        <v>0.006113507731187234</v>
+        <v>0.006275690326878251</v>
       </c>
       <c r="I2009">
-        <v>0.2585295407502239</v>
+        <v>0.3540193545701094</v>
       </c>
       <c r="J2009">
-        <v>0.4533464112061254</v>
+        <v>0.4570506925232892</v>
       </c>
       <c r="K2009">
-        <v>2.85</v>
+        <v>3.57</v>
       </c>
       <c r="L2009">
-        <v>4.3</v>
+        <v>5.19</v>
       </c>
       <c r="M2009">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2009">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2009">
         <v>1</v>
       </c>
       <c r="P2009" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2010" spans="1:16">
       <c r="A2010" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2010" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C2010">
-        <v>3.010630048622849</v>
+        <v>3.513207368411501</v>
       </c>
       <c r="D2010" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E2010">
-        <v>3.266492268812767</v>
+        <v>3.204309673121749</v>
       </c>
       <c r="F2010">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2010">
-        <v>0.005549369951377152</v>
+        <v>0.006986792631588498</v>
       </c>
       <c r="H2010">
-        <v>0.006113507731187234</v>
+        <v>0.006275690326878251</v>
       </c>
       <c r="I2010">
-        <v>0.2558622201899174</v>
+        <v>0.3088976952897524</v>
       </c>
       <c r="J2010">
-        <v>0.4533464112061254</v>
+        <v>0.4570506925232892</v>
       </c>
       <c r="K2010">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="L2010">
-        <v>4.28</v>
+        <v>5.25</v>
       </c>
       <c r="M2010">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2010">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2010">
         <v>1</v>
       </c>
       <c r="P2010" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2011" spans="1:16">
       <c r="A2011" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2011" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="C2011">
-        <v>3.007830833295216</v>
+        <v>3.007962728062543</v>
       </c>
       <c r="D2011" t="s">
         <v>436</v>
@@ -102688,22 +102688,22 @@
         <v>1</v>
       </c>
       <c r="G2011">
-        <v>0.005492169166704784</v>
+        <v>0.005592037271937457</v>
       </c>
       <c r="H2011">
         <v>0.006113507731187234</v>
       </c>
       <c r="I2011">
-        <v>0.2586614355175505</v>
+        <v>0.2585295407502239</v>
       </c>
       <c r="J2011">
         <v>0.4533464112061254</v>
       </c>
       <c r="K2011">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="L2011">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M2011">
         <v>3.14</v>
@@ -102720,13 +102720,13 @@
     </row>
     <row r="2012" spans="1:16">
       <c r="A2012" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2012" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C2012">
-        <v>3.002496192174604</v>
+        <v>3.010630048622849</v>
       </c>
       <c r="D2012" t="s">
         <v>436</v>
@@ -102738,22 +102738,22 @@
         <v>1</v>
       </c>
       <c r="G2012">
-        <v>0.005577503807825396</v>
+        <v>0.005549369951377152</v>
       </c>
       <c r="H2012">
         <v>0.006113507731187234</v>
       </c>
       <c r="I2012">
-        <v>0.2639960766381626</v>
+        <v>0.2558622201899174</v>
       </c>
       <c r="J2012">
         <v>0.4533464112061254</v>
       </c>
       <c r="K2012">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="L2012">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="M2012">
         <v>3.14</v>
@@ -102770,46 +102770,46 @@
     </row>
     <row r="2013" spans="1:16">
       <c r="A2013" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2013" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C2013">
-        <v>3.571553311994133</v>
+        <v>3.007830833295216</v>
       </c>
       <c r="D2013" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E2013">
-        <v>3.216756058347419</v>
+        <v>3.266492268812767</v>
       </c>
       <c r="F2013">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2013">
-        <v>0.006808446688005869</v>
+        <v>0.005492169166704784</v>
       </c>
       <c r="H2013">
-        <v>0.006263243941652582</v>
+        <v>0.006113507731187234</v>
       </c>
       <c r="I2013">
-        <v>0.3547972536467139</v>
+        <v>0.2586614355175505</v>
       </c>
       <c r="J2013">
         <v>0.4533464112061254</v>
       </c>
       <c r="K2013">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2013">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2013">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2013">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2013">
         <v>1</v>
@@ -102820,46 +102820,46 @@
     </row>
     <row r="2014" spans="1:16">
       <c r="A2014" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2014" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C2014">
-        <v>3.527283637416724</v>
+        <v>3.002496192174604</v>
       </c>
       <c r="D2014" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E2014">
-        <v>3.216756058347419</v>
+        <v>3.266492268812767</v>
       </c>
       <c r="F2014">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2014">
-        <v>0.006972716362583276</v>
+        <v>0.005577503807825396</v>
       </c>
       <c r="H2014">
-        <v>0.006263243941652582</v>
+        <v>0.006113507731187234</v>
       </c>
       <c r="I2014">
-        <v>0.3105275790693049</v>
+        <v>0.2639960766381626</v>
       </c>
       <c r="J2014">
         <v>0.4533464112061254</v>
       </c>
       <c r="K2014">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="L2014">
-        <v>5.25</v>
+        <v>4.29</v>
       </c>
       <c r="M2014">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2014">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2014">
         <v>1</v>
@@ -102870,113 +102870,113 @@
     </row>
     <row r="2015" spans="1:16">
       <c r="A2015" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2015" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="C2015">
-        <v>3.016151146705838</v>
+        <v>3.571553311994133</v>
       </c>
       <c r="D2015" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E2015">
-        <v>3.275513894967134</v>
+        <v>3.216756058347419</v>
       </c>
       <c r="F2015">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2015">
-        <v>0.005583848853294163</v>
+        <v>0.006808446688005869</v>
       </c>
       <c r="H2015">
-        <v>0.006104486105032866</v>
+        <v>0.006263243941652582</v>
       </c>
       <c r="I2015">
-        <v>0.2593627482612963</v>
+        <v>0.3547972536467139</v>
       </c>
       <c r="J2015">
-        <v>0.4504732818576006</v>
+        <v>0.4533464112061254</v>
       </c>
       <c r="K2015">
-        <v>2.85</v>
+        <v>3.57</v>
       </c>
       <c r="L2015">
-        <v>4.3</v>
+        <v>5.19</v>
       </c>
       <c r="M2015">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2015">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2015">
         <v>1</v>
       </c>
       <c r="P2015" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2016" spans="1:16">
       <c r="A2016" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2016" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C2016">
-        <v>3.018674810798719</v>
+        <v>3.527283637416724</v>
       </c>
       <c r="D2016" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E2016">
-        <v>3.275513894967134</v>
+        <v>3.216756058347419</v>
       </c>
       <c r="F2016">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2016">
-        <v>0.005541325189201282</v>
+        <v>0.006972716362583276</v>
       </c>
       <c r="H2016">
-        <v>0.006104486105032866</v>
+        <v>0.006263243941652582</v>
       </c>
       <c r="I2016">
-        <v>0.2568390841684156</v>
+        <v>0.3105275790693049</v>
       </c>
       <c r="J2016">
-        <v>0.4504732818576006</v>
+        <v>0.4533464112061254</v>
       </c>
       <c r="K2016">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="L2016">
-        <v>4.28</v>
+        <v>5.25</v>
       </c>
       <c r="M2016">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2016">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2016">
         <v>1</v>
       </c>
       <c r="P2016" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2017" spans="1:16">
       <c r="A2017" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2017" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C2017">
-        <v>3.015703207710174</v>
+        <v>3.018674810798719</v>
       </c>
       <c r="D2017" t="s">
         <v>436</v>
@@ -102988,22 +102988,22 @@
         <v>1</v>
       </c>
       <c r="G2017">
-        <v>0.005484296792289825</v>
+        <v>0.005541325189201282</v>
       </c>
       <c r="H2017">
         <v>0.006104486105032866</v>
       </c>
       <c r="I2017">
-        <v>0.2598106872569601</v>
+        <v>0.2568390841684156</v>
       </c>
       <c r="J2017">
         <v>0.4504732818576006</v>
       </c>
       <c r="K2017">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="L2017">
-        <v>4.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2017">
         <v>3.14</v>
@@ -103020,13 +103020,13 @@
     </row>
     <row r="2018" spans="1:16">
       <c r="A2018" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2018" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C2018">
-        <v>3.010655879524414</v>
+        <v>3.015703207710174</v>
       </c>
       <c r="D2018" t="s">
         <v>436</v>
@@ -103038,22 +103038,22 @@
         <v>1</v>
       </c>
       <c r="G2018">
-        <v>0.005569344120475586</v>
+        <v>0.005484296792289825</v>
       </c>
       <c r="H2018">
         <v>0.006104486105032866</v>
       </c>
       <c r="I2018">
-        <v>0.2648580154427198</v>
+        <v>0.2598106872569601</v>
       </c>
       <c r="J2018">
         <v>0.4504732818576006</v>
       </c>
       <c r="K2018">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="L2018">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="M2018">
         <v>3.14</v>
@@ -103070,46 +103070,46 @@
     </row>
     <row r="2019" spans="1:16">
       <c r="A2019" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2019" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C2019">
-        <v>3.581810383768366</v>
+        <v>3.010655879524414</v>
       </c>
       <c r="D2019" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E2019">
-        <v>3.226409772958462</v>
+        <v>3.275513894967134</v>
       </c>
       <c r="F2019">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2019">
-        <v>0.006798189616231635</v>
+        <v>0.005569344120475586</v>
       </c>
       <c r="H2019">
-        <v>0.006253590227041538</v>
+        <v>0.006104486105032866</v>
       </c>
       <c r="I2019">
-        <v>0.3554006108099044</v>
+        <v>0.2648580154427198</v>
       </c>
       <c r="J2019">
         <v>0.4504732818576006</v>
       </c>
       <c r="K2019">
-        <v>3.57</v>
+        <v>2.84</v>
       </c>
       <c r="L2019">
-        <v>5.19</v>
+        <v>4.29</v>
       </c>
       <c r="M2019">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2019">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2019">
         <v>1</v>
@@ -103120,13 +103120,13 @@
     </row>
     <row r="2020" spans="1:16">
       <c r="A2020" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2020" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2020">
-        <v>3.538201528941118</v>
+        <v>3.581810383768366</v>
       </c>
       <c r="D2020" t="s">
         <v>273</v>
@@ -103138,22 +103138,22 @@
         <v>-1</v>
       </c>
       <c r="G2020">
-        <v>0.006961798471058883</v>
+        <v>0.006798189616231635</v>
       </c>
       <c r="H2020">
         <v>0.006253590227041538</v>
       </c>
       <c r="I2020">
-        <v>0.3117917559826555</v>
+        <v>0.3554006108099044</v>
       </c>
       <c r="J2020">
         <v>0.4504732818576006</v>
       </c>
       <c r="K2020">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2020">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2020">
         <v>3.36</v>
@@ -103170,63 +103170,63 @@
     </row>
     <row r="2021" spans="1:16">
       <c r="A2021" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2021" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C2021">
-        <v>3.028785702645333</v>
+        <v>3.538201528941118</v>
       </c>
       <c r="D2021" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E2021">
-        <v>3.286852537966552</v>
+        <v>3.226409772958462</v>
       </c>
       <c r="F2021">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2021">
-        <v>0.005531214297354667</v>
+        <v>0.006961798471058883</v>
       </c>
       <c r="H2021">
-        <v>0.006093147462033449</v>
+        <v>0.006253590227041538</v>
       </c>
       <c r="I2021">
-        <v>0.2580668353212188</v>
+        <v>0.3117917559826555</v>
       </c>
       <c r="J2021">
-        <v>0.4468622490552383</v>
+        <v>0.4504732818576006</v>
       </c>
       <c r="K2021">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="L2021">
-        <v>4.28</v>
+        <v>5.25</v>
       </c>
       <c r="M2021">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2021">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2021">
         <v>1</v>
       </c>
       <c r="P2021" t="s">
-        <v>250</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2022" spans="1:16">
       <c r="A2022" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2022" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C2022">
-        <v>3.025597437588647</v>
+        <v>3.028785702645333</v>
       </c>
       <c r="D2022" t="s">
         <v>436</v>
@@ -103238,22 +103238,22 @@
         <v>1</v>
       </c>
       <c r="G2022">
-        <v>0.005474402562411352</v>
+        <v>0.005531214297354667</v>
       </c>
       <c r="H2022">
         <v>0.006093147462033449</v>
       </c>
       <c r="I2022">
-        <v>0.2612551003779049</v>
+        <v>0.2580668353212188</v>
       </c>
       <c r="J2022">
         <v>0.4468622490552383</v>
       </c>
       <c r="K2022">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="L2022">
-        <v>4.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2022">
         <v>3.14</v>
@@ -103270,13 +103270,13 @@
     </row>
     <row r="2023" spans="1:16">
       <c r="A2023" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2023" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C2023">
-        <v>3.020911212683123</v>
+        <v>3.025597437588647</v>
       </c>
       <c r="D2023" t="s">
         <v>436</v>
@@ -103288,22 +103288,22 @@
         <v>1</v>
       </c>
       <c r="G2023">
-        <v>0.005559088787316877</v>
+        <v>0.005474402562411352</v>
       </c>
       <c r="H2023">
         <v>0.006093147462033449</v>
       </c>
       <c r="I2023">
-        <v>0.2659413252834284</v>
+        <v>0.2612551003779049</v>
       </c>
       <c r="J2023">
         <v>0.4468622490552383</v>
       </c>
       <c r="K2023">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="L2023">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="M2023">
         <v>3.14</v>
@@ -103320,46 +103320,46 @@
     </row>
     <row r="2024" spans="1:16">
       <c r="A2024" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2024" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C2024">
-        <v>3.5947017708728</v>
+        <v>3.020911212683123</v>
       </c>
       <c r="D2024" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E2024">
-        <v>3.238542843174399</v>
+        <v>3.286852537966552</v>
       </c>
       <c r="F2024">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2024">
-        <v>0.006785298229127201</v>
+        <v>0.005559088787316877</v>
       </c>
       <c r="H2024">
-        <v>0.006241457156825601</v>
+        <v>0.006093147462033449</v>
       </c>
       <c r="I2024">
-        <v>0.3561589276984005</v>
+        <v>0.2659413252834284</v>
       </c>
       <c r="J2024">
         <v>0.4468622490552383</v>
       </c>
       <c r="K2024">
-        <v>3.57</v>
+        <v>2.84</v>
       </c>
       <c r="L2024">
-        <v>5.19</v>
+        <v>4.29</v>
       </c>
       <c r="M2024">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2024">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2024">
         <v>1</v>
@@ -103370,13 +103370,13 @@
     </row>
     <row r="2025" spans="1:16">
       <c r="A2025" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2025" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2025">
-        <v>3.551923453590095</v>
+        <v>3.5947017708728</v>
       </c>
       <c r="D2025" t="s">
         <v>273</v>
@@ -103388,22 +103388,22 @@
         <v>-1</v>
       </c>
       <c r="G2025">
-        <v>0.006948076546409905</v>
+        <v>0.006785298229127201</v>
       </c>
       <c r="H2025">
         <v>0.006241457156825601</v>
       </c>
       <c r="I2025">
-        <v>0.3133806104156953</v>
+        <v>0.3561589276984005</v>
       </c>
       <c r="J2025">
         <v>0.4468622490552383</v>
       </c>
       <c r="K2025">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2025">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2025">
         <v>3.36</v>
@@ -103420,63 +103420,63 @@
     </row>
     <row r="2026" spans="1:16">
       <c r="A2026" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2026" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C2026">
-        <v>3.039921109638204</v>
+        <v>3.551923453590095</v>
       </c>
       <c r="D2026" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E2026">
-        <v>3.299340101522843</v>
+        <v>3.238542843174399</v>
       </c>
       <c r="F2026">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2026">
-        <v>0.005520078890361797</v>
+        <v>0.006948076546409905</v>
       </c>
       <c r="H2026">
-        <v>0.006080659898477159</v>
+        <v>0.006241457156825601</v>
       </c>
       <c r="I2026">
-        <v>0.259418991884639</v>
+        <v>0.3133806104156953</v>
       </c>
       <c r="J2026">
-        <v>0.442885317986356</v>
+        <v>0.4468622490552383</v>
       </c>
       <c r="K2026">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="L2026">
-        <v>4.28</v>
+        <v>5.25</v>
       </c>
       <c r="M2026">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2026">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2026">
         <v>1</v>
       </c>
       <c r="P2026" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2027" spans="1:16">
       <c r="A2027" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2027" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C2027">
-        <v>3.036494228717384</v>
+        <v>3.039921109638204</v>
       </c>
       <c r="D2027" t="s">
         <v>436</v>
@@ -103488,22 +103488,22 @@
         <v>1</v>
       </c>
       <c r="G2027">
-        <v>0.005463505771282616</v>
+        <v>0.005520078890361797</v>
       </c>
       <c r="H2027">
         <v>0.006080659898477159</v>
       </c>
       <c r="I2027">
-        <v>0.2628458728054581</v>
+        <v>0.259418991884639</v>
       </c>
       <c r="J2027">
         <v>0.442885317986356</v>
       </c>
       <c r="K2027">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="L2027">
-        <v>4.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2027">
         <v>3.14</v>
@@ -103520,13 +103520,13 @@
     </row>
     <row r="2028" spans="1:16">
       <c r="A2028" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2028" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C2028">
-        <v>3.032205696918749</v>
+        <v>3.036494228717384</v>
       </c>
       <c r="D2028" t="s">
         <v>436</v>
@@ -103538,22 +103538,22 @@
         <v>1</v>
       </c>
       <c r="G2028">
-        <v>0.005547794303081251</v>
+        <v>0.005463505771282616</v>
       </c>
       <c r="H2028">
         <v>0.006080659898477159</v>
       </c>
       <c r="I2028">
-        <v>0.2671344046040938</v>
+        <v>0.2628458728054581</v>
       </c>
       <c r="J2028">
         <v>0.442885317986356</v>
       </c>
       <c r="K2028">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="L2028">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="M2028">
         <v>3.14</v>
@@ -103570,46 +103570,46 @@
     </row>
     <row r="2029" spans="1:16">
       <c r="A2029" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2029" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C2029">
-        <v>3.608899414788709</v>
+        <v>3.032205696918749</v>
       </c>
       <c r="D2029" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="E2029">
-        <v>3.251905331565844</v>
+        <v>3.299340101522843</v>
       </c>
       <c r="F2029">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2029">
-        <v>0.006771100585211291</v>
+        <v>0.005547794303081251</v>
       </c>
       <c r="H2029">
-        <v>0.006228094668434157</v>
+        <v>0.006080659898477159</v>
       </c>
       <c r="I2029">
-        <v>0.3569940832228653</v>
+        <v>0.2671344046040938</v>
       </c>
       <c r="J2029">
         <v>0.442885317986356</v>
       </c>
       <c r="K2029">
-        <v>3.57</v>
+        <v>2.84</v>
       </c>
       <c r="L2029">
-        <v>5.19</v>
+        <v>4.29</v>
       </c>
       <c r="M2029">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2029">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2029">
         <v>1</v>
@@ -103620,13 +103620,13 @@
     </row>
     <row r="2030" spans="1:16">
       <c r="A2030" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2030" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2030">
-        <v>3.567035791651847</v>
+        <v>3.608899414788709</v>
       </c>
       <c r="D2030" t="s">
         <v>273</v>
@@ -103638,22 +103638,22 @@
         <v>-1</v>
       </c>
       <c r="G2030">
-        <v>0.006932964208348154</v>
+        <v>0.006771100585211291</v>
       </c>
       <c r="H2030">
         <v>0.006228094668434157</v>
       </c>
       <c r="I2030">
-        <v>0.3151304600860034</v>
+        <v>0.3569940832228653</v>
       </c>
       <c r="J2030">
         <v>0.442885317986356</v>
       </c>
       <c r="K2030">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2030">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2030">
         <v>3.36</v>
@@ -103670,63 +103670,63 @@
     </row>
     <row r="2031" spans="1:16">
       <c r="A2031" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2031" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C2031">
-        <v>3.052236224586666</v>
+        <v>3.567035791651847</v>
       </c>
       <c r="D2031" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="E2031">
-        <v>3.317380198978881</v>
+        <v>3.251905331565844</v>
       </c>
       <c r="F2031">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2031">
-        <v>0.005447763775413334</v>
+        <v>0.006932964208348154</v>
       </c>
       <c r="H2031">
-        <v>0.006062619801021119</v>
+        <v>0.006228094668434157</v>
       </c>
       <c r="I2031">
-        <v>0.265143974392215</v>
+        <v>0.3151304600860034</v>
       </c>
       <c r="J2031">
-        <v>0.4371400640194647</v>
+        <v>0.442885317986356</v>
       </c>
       <c r="K2031">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="L2031">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="M2031">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2031">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2031">
         <v>1</v>
       </c>
       <c r="P2031" t="s">
-        <v>595</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2032" spans="1:16">
       <c r="A2032" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2032" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C2032">
-        <v>3.04852221818472</v>
+        <v>3.052236224586666</v>
       </c>
       <c r="D2032" t="s">
         <v>436</v>
@@ -103738,22 +103738,22 @@
         <v>1</v>
       </c>
       <c r="G2032">
-        <v>0.00553147778181528</v>
+        <v>0.005447763775413334</v>
       </c>
       <c r="H2032">
         <v>0.006062619801021119</v>
       </c>
       <c r="I2032">
-        <v>0.2688579807941611</v>
+        <v>0.265143974392215</v>
       </c>
       <c r="J2032">
         <v>0.4371400640194647</v>
       </c>
       <c r="K2032">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="L2032">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="M2032">
         <v>3.14</v>
@@ -103770,7 +103770,7 @@
     </row>
     <row r="2033" spans="1:16">
       <c r="A2033" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2033" t="s">
         <v>266</v>
@@ -103820,7 +103820,7 @@
     </row>
     <row r="2034" spans="1:16">
       <c r="A2034" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2034" t="s">
         <v>267</v>
@@ -104832,7 +104832,7 @@
         <v>457</v>
       </c>
       <c r="E2054">
-        <v>1.954877750507645</v>
+        <v>1.910151755152943</v>
       </c>
       <c r="F2054">
         <v>1</v>
@@ -104841,10 +104841,10 @@
         <v>0.007586793443917998</v>
       </c>
       <c r="H2054">
-        <v>0.007445122249492356</v>
+        <v>0.007569848244847058</v>
       </c>
       <c r="I2054">
-        <v>0.06167119442564228</v>
+        <v>0.01694519907094039</v>
       </c>
       <c r="J2054">
         <v>0.8472599535470232</v>
@@ -104856,10 +104856,10 @@
         <v>4.74</v>
       </c>
       <c r="M2054">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="N2054">
-        <v>4.7</v>
+        <v>4.74</v>
       </c>
       <c r="O2054">
         <v>1</v>

--- a/s60_signal/position-00857-601857.xlsx
+++ b/s60_signal/position-00857-601857.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6171" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6183" uniqueCount="596">
   <si>
     <t>trade_time</t>
   </si>
@@ -826,13 +826,13 @@
     <t>2021-04-08</t>
   </si>
   <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
     <t>2021-03-24</t>
   </si>
   <si>
     <t>2021-04-01</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
   </si>
   <si>
     <t>2021-03-26</t>
@@ -2159,7 +2159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2053"/>
+  <dimension ref="A1:P2057"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -98814,10 +98814,10 @@
         <v>1</v>
       </c>
       <c r="B1934" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C1934">
-        <v>2.629007791170007</v>
+        <v>2.675015315975228</v>
       </c>
       <c r="D1934" t="s">
         <v>436</v>
@@ -98829,22 +98829,22 @@
         <v>1</v>
       </c>
       <c r="G1934">
-        <v>0.005710992208829992</v>
+        <v>0.005824984684024772</v>
       </c>
       <c r="H1934">
         <v>0.006468939535193448</v>
       </c>
       <c r="I1934">
-        <v>0.2820526736365458</v>
+        <v>0.2360451488313249</v>
       </c>
       <c r="J1934">
         <v>0.5665412532463208</v>
       </c>
       <c r="K1934">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L1934">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="M1934">
         <v>3.14</v>
@@ -98864,43 +98864,43 @@
         <v>2</v>
       </c>
       <c r="B1935" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C1935">
-        <v>3.167447725910635</v>
+        <v>2.629007791170007</v>
       </c>
       <c r="D1935" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1935">
-        <v>2.836421389092362</v>
+        <v>2.911060464806553</v>
       </c>
       <c r="F1935">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1935">
-        <v>0.007212552274089365</v>
+        <v>0.005710992208829992</v>
       </c>
       <c r="H1935">
-        <v>0.006643578610907639</v>
+        <v>0.006468939535193448</v>
       </c>
       <c r="I1935">
-        <v>0.3310263368182729</v>
+        <v>0.2820526736365458</v>
       </c>
       <c r="J1935">
         <v>0.5665412532463208</v>
       </c>
       <c r="K1935">
-        <v>3.57</v>
+        <v>2.72</v>
       </c>
       <c r="L1935">
-        <v>5.19</v>
+        <v>4.17</v>
       </c>
       <c r="M1935">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1935">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1935">
         <v>1</v>
@@ -98914,10 +98914,10 @@
         <v>3</v>
       </c>
       <c r="B1936" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1936">
-        <v>3.097143237663981</v>
+        <v>3.167447725910635</v>
       </c>
       <c r="D1936" t="s">
         <v>456</v>
@@ -98929,22 +98929,22 @@
         <v>-1</v>
       </c>
       <c r="G1936">
-        <v>0.007402856762336018</v>
+        <v>0.007212552274089365</v>
       </c>
       <c r="H1936">
         <v>0.006643578610907639</v>
       </c>
       <c r="I1936">
-        <v>0.260721848571619</v>
+        <v>0.3310263368182729</v>
       </c>
       <c r="J1936">
         <v>0.5665412532463208</v>
       </c>
       <c r="K1936">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1936">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1936">
         <v>3.36</v>
@@ -98961,63 +98961,63 @@
     </row>
     <row r="1937" spans="1:16">
       <c r="A1937" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1937" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1937">
-        <v>2.77102496200336</v>
+        <v>3.097143237663981</v>
       </c>
       <c r="D1937" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1937">
-        <v>3.02299249329533</v>
+        <v>2.836421389092362</v>
       </c>
       <c r="F1937">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1937">
-        <v>0.005828975037996641</v>
+        <v>0.007402856762336018</v>
       </c>
       <c r="H1937">
-        <v>0.006357007506704671</v>
+        <v>0.006643578610907639</v>
       </c>
       <c r="I1937">
-        <v>0.2519675312919705</v>
+        <v>0.260721848571619</v>
       </c>
       <c r="J1937">
-        <v>0.5308941104155001</v>
+        <v>0.5665412532463208</v>
       </c>
       <c r="K1937">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1937">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1937">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1937">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1937">
         <v>1</v>
       </c>
       <c r="P1937" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1938" spans="1:16">
       <c r="A1938" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1938" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1938">
-        <v>2.77411437304491</v>
+        <v>2.77102496200336</v>
       </c>
       <c r="D1938" t="s">
         <v>436</v>
@@ -99029,22 +99029,22 @@
         <v>1</v>
       </c>
       <c r="G1938">
-        <v>0.00572588562695509</v>
+        <v>0.005828975037996641</v>
       </c>
       <c r="H1938">
         <v>0.006357007506704671</v>
       </c>
       <c r="I1938">
-        <v>0.2488781202504202</v>
+        <v>0.2519675312919705</v>
       </c>
       <c r="J1938">
         <v>0.5308941104155001</v>
       </c>
       <c r="K1938">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1938">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1938">
         <v>3.14</v>
@@ -99061,13 +99061,13 @@
     </row>
     <row r="1939" spans="1:16">
       <c r="A1939" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1939" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C1939">
-        <v>2.778187549732444</v>
+        <v>2.77411437304491</v>
       </c>
       <c r="D1939" t="s">
         <v>436</v>
@@ -99079,22 +99079,22 @@
         <v>1</v>
       </c>
       <c r="G1939">
-        <v>0.005761812450267555</v>
+        <v>0.00572588562695509</v>
       </c>
       <c r="H1939">
         <v>0.006357007506704671</v>
       </c>
       <c r="I1939">
-        <v>0.2448049435628858</v>
+        <v>0.2488781202504202</v>
       </c>
       <c r="J1939">
         <v>0.5308941104155001</v>
       </c>
       <c r="K1939">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1939">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1939">
         <v>3.14</v>
@@ -99111,46 +99111,46 @@
     </row>
     <row r="1940" spans="1:16">
       <c r="A1940" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1940" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1940">
-        <v>3.294708025816665</v>
+        <v>2.778187549732444</v>
       </c>
       <c r="D1940" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1940">
-        <v>2.95619578900392</v>
+        <v>3.02299249329533</v>
       </c>
       <c r="F1940">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1940">
-        <v>0.007085291974183336</v>
+        <v>0.005761812450267555</v>
       </c>
       <c r="H1940">
-        <v>0.00652380421099608</v>
+        <v>0.006357007506704671</v>
       </c>
       <c r="I1940">
-        <v>0.3385122368127451</v>
+        <v>0.2448049435628858</v>
       </c>
       <c r="J1940">
         <v>0.5308941104155001</v>
       </c>
       <c r="K1940">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L1940">
-        <v>5.19</v>
+        <v>4.27</v>
       </c>
       <c r="M1940">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1940">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1940">
         <v>1</v>
@@ -99161,13 +99161,13 @@
     </row>
     <row r="1941" spans="1:16">
       <c r="A1941" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1941" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1941">
-        <v>3.2326023804211</v>
+        <v>3.294708025816665</v>
       </c>
       <c r="D1941" t="s">
         <v>456</v>
@@ -99179,22 +99179,22 @@
         <v>-1</v>
       </c>
       <c r="G1941">
-        <v>0.0072673976195789</v>
+        <v>0.007085291974183336</v>
       </c>
       <c r="H1941">
         <v>0.00652380421099608</v>
       </c>
       <c r="I1941">
-        <v>0.2764065914171798</v>
+        <v>0.3385122368127451</v>
       </c>
       <c r="J1941">
         <v>0.5308941104155001</v>
       </c>
       <c r="K1941">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1941">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1941">
         <v>3.36</v>
@@ -99211,63 +99211,63 @@
     </row>
     <row r="1942" spans="1:16">
       <c r="A1942" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1942" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1942">
-        <v>2.812196186654786</v>
+        <v>3.2326023804211</v>
       </c>
       <c r="D1942" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1942">
-        <v>3.067880564616677</v>
+        <v>2.95619578900392</v>
       </c>
       <c r="F1942">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1942">
-        <v>0.005787803813345213</v>
+        <v>0.0072673976195789</v>
       </c>
       <c r="H1942">
-        <v>0.006312119435383325</v>
+        <v>0.00652380421099608</v>
       </c>
       <c r="I1942">
-        <v>0.2556843779618907</v>
+        <v>0.2764065914171798</v>
       </c>
       <c r="J1942">
-        <v>0.5165985463004216</v>
+        <v>0.5308941104155001</v>
       </c>
       <c r="K1942">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1942">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1942">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1942">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1942">
         <v>1</v>
       </c>
       <c r="P1942" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1943" spans="1:16">
       <c r="A1943" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1943" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1943">
-        <v>2.813856041284828</v>
+        <v>2.812196186654786</v>
       </c>
       <c r="D1943" t="s">
         <v>436</v>
@@ -99279,22 +99279,22 @@
         <v>1</v>
       </c>
       <c r="G1943">
-        <v>0.005686143958715172</v>
+        <v>0.005787803813345213</v>
       </c>
       <c r="H1943">
         <v>0.006312119435383325</v>
       </c>
       <c r="I1943">
-        <v>0.2540245233318483</v>
+        <v>0.2556843779618907</v>
       </c>
       <c r="J1943">
         <v>0.5165985463004216</v>
       </c>
       <c r="K1943">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1943">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1943">
         <v>3.14</v>
@@ -99311,13 +99311,13 @@
     </row>
     <row r="1944" spans="1:16">
       <c r="A1944" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1944" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C1944">
-        <v>2.818358084895815</v>
+        <v>2.813856041284828</v>
       </c>
       <c r="D1944" t="s">
         <v>436</v>
@@ -99329,22 +99329,22 @@
         <v>1</v>
       </c>
       <c r="G1944">
-        <v>0.005721641915104185</v>
+        <v>0.005686143958715172</v>
       </c>
       <c r="H1944">
         <v>0.006312119435383325</v>
       </c>
       <c r="I1944">
-        <v>0.2495224797208619</v>
+        <v>0.2540245233318483</v>
       </c>
       <c r="J1944">
         <v>0.5165985463004216</v>
       </c>
       <c r="K1944">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1944">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1944">
         <v>3.14</v>
@@ -99361,46 +99361,46 @@
     </row>
     <row r="1945" spans="1:16">
       <c r="A1945" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1945" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1945">
-        <v>3.345743189707496</v>
+        <v>2.818358084895815</v>
       </c>
       <c r="D1945" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1945">
-        <v>3.004228884430584</v>
+        <v>3.067880564616677</v>
       </c>
       <c r="F1945">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1945">
-        <v>0.007034256810292505</v>
+        <v>0.005721641915104185</v>
       </c>
       <c r="H1945">
-        <v>0.006475771115569417</v>
+        <v>0.006312119435383325</v>
       </c>
       <c r="I1945">
-        <v>0.3415143052769118</v>
+        <v>0.2495224797208619</v>
       </c>
       <c r="J1945">
         <v>0.5165985463004216</v>
       </c>
       <c r="K1945">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L1945">
-        <v>5.19</v>
+        <v>4.27</v>
       </c>
       <c r="M1945">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1945">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1945">
         <v>1</v>
@@ -99411,13 +99411,13 @@
     </row>
     <row r="1946" spans="1:16">
       <c r="A1946" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1946" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1946">
-        <v>3.286925524058398</v>
+        <v>3.345743189707496</v>
       </c>
       <c r="D1946" t="s">
         <v>456</v>
@@ -99429,22 +99429,22 @@
         <v>-1</v>
       </c>
       <c r="G1946">
-        <v>0.007213074475941602</v>
+        <v>0.007034256810292505</v>
       </c>
       <c r="H1946">
         <v>0.006475771115569417</v>
       </c>
       <c r="I1946">
-        <v>0.2826966396278143</v>
+        <v>0.3415143052769118</v>
       </c>
       <c r="J1946">
         <v>0.5165985463004216</v>
       </c>
       <c r="K1946">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1946">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1946">
         <v>3.36</v>
@@ -99461,63 +99461,63 @@
     </row>
     <row r="1947" spans="1:16">
       <c r="A1947" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1947" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1947">
-        <v>2.834723748850407</v>
+        <v>3.286925524058398</v>
       </c>
       <c r="D1947" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1947">
-        <v>3.092441865066069</v>
+        <v>3.004228884430584</v>
       </c>
       <c r="F1947">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1947">
-        <v>0.005765276251149593</v>
+        <v>0.007213074475941602</v>
       </c>
       <c r="H1947">
-        <v>0.006287558134933932</v>
+        <v>0.006475771115569417</v>
       </c>
       <c r="I1947">
-        <v>0.2577181162156625</v>
+        <v>0.2826966396278143</v>
       </c>
       <c r="J1947">
-        <v>0.5087764760936087</v>
+        <v>0.5165985463004216</v>
       </c>
       <c r="K1947">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1947">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1947">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1947">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1947">
         <v>1</v>
       </c>
       <c r="P1947" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1948" spans="1:16">
       <c r="A1948" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1948" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1948">
-        <v>2.835601396459768</v>
+        <v>2.834723748850407</v>
       </c>
       <c r="D1948" t="s">
         <v>436</v>
@@ -99529,22 +99529,22 @@
         <v>1</v>
       </c>
       <c r="G1948">
-        <v>0.005664398603540233</v>
+        <v>0.005765276251149593</v>
       </c>
       <c r="H1948">
         <v>0.006287558134933932</v>
       </c>
       <c r="I1948">
-        <v>0.2568404686063017</v>
+        <v>0.2577181162156625</v>
       </c>
       <c r="J1948">
         <v>0.5087764760936087</v>
       </c>
       <c r="K1948">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1948">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1948">
         <v>3.14</v>
@@ -99561,13 +99561,13 @@
     </row>
     <row r="1949" spans="1:16">
       <c r="A1949" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1949" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C1949">
-        <v>2.840338102176959</v>
+        <v>2.835601396459768</v>
       </c>
       <c r="D1949" t="s">
         <v>436</v>
@@ -99579,22 +99579,22 @@
         <v>1</v>
       </c>
       <c r="G1949">
-        <v>0.00569966189782304</v>
+        <v>0.005664398603540233</v>
       </c>
       <c r="H1949">
         <v>0.006287558134933932</v>
       </c>
       <c r="I1949">
-        <v>0.2521037628891101</v>
+        <v>0.2568404686063017</v>
       </c>
       <c r="J1949">
         <v>0.5087764760936087</v>
       </c>
       <c r="K1949">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1949">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1949">
         <v>3.14</v>
@@ -99611,46 +99611,46 @@
     </row>
     <row r="1950" spans="1:16">
       <c r="A1950" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1950" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1950">
-        <v>3.373667980345818</v>
+        <v>2.840338102176959</v>
       </c>
       <c r="D1950" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1950">
-        <v>3.030511040325475</v>
+        <v>3.092441865066069</v>
       </c>
       <c r="F1950">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1950">
-        <v>0.007006332019654182</v>
+        <v>0.00569966189782304</v>
       </c>
       <c r="H1950">
-        <v>0.006449488959674525</v>
+        <v>0.006287558134933932</v>
       </c>
       <c r="I1950">
-        <v>0.3431569400203425</v>
+        <v>0.2521037628891101</v>
       </c>
       <c r="J1950">
         <v>0.5087764760936087</v>
       </c>
       <c r="K1950">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L1950">
-        <v>5.19</v>
+        <v>4.27</v>
       </c>
       <c r="M1950">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1950">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1950">
         <v>1</v>
@@ -99661,13 +99661,13 @@
     </row>
     <row r="1951" spans="1:16">
       <c r="A1951" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1951" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1951">
-        <v>3.316649390844287</v>
+        <v>3.373667980345818</v>
       </c>
       <c r="D1951" t="s">
         <v>456</v>
@@ -99679,22 +99679,22 @@
         <v>-1</v>
       </c>
       <c r="G1951">
-        <v>0.007183350609155714</v>
+        <v>0.007006332019654182</v>
       </c>
       <c r="H1951">
         <v>0.006449488959674525</v>
       </c>
       <c r="I1951">
-        <v>0.286138350518812</v>
+        <v>0.3431569400203425</v>
       </c>
       <c r="J1951">
         <v>0.5087764760936087</v>
       </c>
       <c r="K1951">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1951">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1951">
         <v>3.36</v>
@@ -99711,63 +99711,63 @@
     </row>
     <row r="1952" spans="1:16">
       <c r="A1952" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1952" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1952">
-        <v>2.849763859967231</v>
+        <v>3.316649390844287</v>
       </c>
       <c r="D1952" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1952">
-        <v>3.108839763992051</v>
+        <v>3.030511040325475</v>
       </c>
       <c r="F1952">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1952">
-        <v>0.005750236140032769</v>
+        <v>0.007183350609155714</v>
       </c>
       <c r="H1952">
-        <v>0.006271160236007951</v>
+        <v>0.006449488959674525</v>
       </c>
       <c r="I1952">
-        <v>0.2590759040248196</v>
+        <v>0.286138350518812</v>
       </c>
       <c r="J1952">
-        <v>0.5035542152891559</v>
+        <v>0.5087764760936087</v>
       </c>
       <c r="K1952">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1952">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1952">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1952">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1952">
         <v>1</v>
       </c>
       <c r="P1952" t="s">
-        <v>253</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1953" spans="1:16">
       <c r="A1953" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1953" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1953">
-        <v>2.850119281496147</v>
+        <v>2.849763859967231</v>
       </c>
       <c r="D1953" t="s">
         <v>436</v>
@@ -99779,22 +99779,22 @@
         <v>1</v>
       </c>
       <c r="G1953">
-        <v>0.005649880718503853</v>
+        <v>0.005750236140032769</v>
       </c>
       <c r="H1953">
         <v>0.006271160236007951</v>
       </c>
       <c r="I1953">
-        <v>0.258720482495904</v>
+        <v>0.2590759040248196</v>
       </c>
       <c r="J1953">
         <v>0.5035542152891559</v>
       </c>
       <c r="K1953">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1953">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1953">
         <v>3.14</v>
@@ -99811,13 +99811,13 @@
     </row>
     <row r="1954" spans="1:16">
       <c r="A1954" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1954" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C1954">
-        <v>2.855012655037472</v>
+        <v>2.850119281496147</v>
       </c>
       <c r="D1954" t="s">
         <v>436</v>
@@ -99829,22 +99829,22 @@
         <v>1</v>
       </c>
       <c r="G1954">
-        <v>0.005684987344962527</v>
+        <v>0.005649880718503853</v>
       </c>
       <c r="H1954">
         <v>0.006271160236007951</v>
       </c>
       <c r="I1954">
-        <v>0.2538271089545789</v>
+        <v>0.258720482495904</v>
       </c>
       <c r="J1954">
         <v>0.5035542152891559</v>
       </c>
       <c r="K1954">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1954">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1954">
         <v>3.14</v>
@@ -99861,46 +99861,46 @@
     </row>
     <row r="1955" spans="1:16">
       <c r="A1955" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1955" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1955">
-        <v>3.392311451417714</v>
+        <v>2.855012655037472</v>
       </c>
       <c r="D1955" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1955">
-        <v>3.048057836628437</v>
+        <v>3.108839763992051</v>
       </c>
       <c r="F1955">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1955">
-        <v>0.006987688548582287</v>
+        <v>0.005684987344962527</v>
       </c>
       <c r="H1955">
-        <v>0.006431942163371564</v>
+        <v>0.006271160236007951</v>
       </c>
       <c r="I1955">
-        <v>0.3442536147892774</v>
+        <v>0.2538271089545789</v>
       </c>
       <c r="J1955">
         <v>0.5035542152891559</v>
       </c>
       <c r="K1955">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L1955">
-        <v>5.19</v>
+        <v>4.27</v>
       </c>
       <c r="M1955">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1955">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1955">
         <v>1</v>
@@ -99911,13 +99911,13 @@
     </row>
     <row r="1956" spans="1:16">
       <c r="A1956" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1956" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1956">
-        <v>3.336493981901207</v>
+        <v>3.392311451417714</v>
       </c>
       <c r="D1956" t="s">
         <v>456</v>
@@ -99929,22 +99929,22 @@
         <v>-1</v>
       </c>
       <c r="G1956">
-        <v>0.007163506018098792</v>
+        <v>0.006987688548582287</v>
       </c>
       <c r="H1956">
         <v>0.006431942163371564</v>
       </c>
       <c r="I1956">
-        <v>0.2884361452727706</v>
+        <v>0.3442536147892774</v>
       </c>
       <c r="J1956">
         <v>0.5035542152891559</v>
       </c>
       <c r="K1956">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1956">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1956">
         <v>3.36</v>
@@ -99961,63 +99961,63 @@
     </row>
     <row r="1957" spans="1:16">
       <c r="A1957" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1957" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1957">
-        <v>2.882304897086411</v>
+        <v>3.336493981901207</v>
       </c>
       <c r="D1957" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1957">
-        <v>3.144318533628935</v>
+        <v>3.048057836628437</v>
       </c>
       <c r="F1957">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1957">
-        <v>0.005717695102913588</v>
+        <v>0.007163506018098792</v>
       </c>
       <c r="H1957">
-        <v>0.006235681466371066</v>
+        <v>0.006431942163371564</v>
       </c>
       <c r="I1957">
-        <v>0.2620136365425236</v>
+        <v>0.2884361452727706</v>
       </c>
       <c r="J1957">
-        <v>0.4922552440672183</v>
+        <v>0.5035542152891559</v>
       </c>
       <c r="K1957">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1957">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1957">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1957">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1957">
         <v>1</v>
       </c>
       <c r="P1957" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="1958" spans="1:16">
       <c r="A1958" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1958" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1958">
-        <v>2.881530421493133</v>
+        <v>2.882304897086411</v>
       </c>
       <c r="D1958" t="s">
         <v>436</v>
@@ -100029,22 +100029,22 @@
         <v>1</v>
       </c>
       <c r="G1958">
-        <v>0.005618469578506867</v>
+        <v>0.005717695102913588</v>
       </c>
       <c r="H1958">
         <v>0.006235681466371066</v>
       </c>
       <c r="I1958">
-        <v>0.2627881121358016</v>
+        <v>0.2620136365425236</v>
       </c>
       <c r="J1958">
         <v>0.4922552440672183</v>
       </c>
       <c r="K1958">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1958">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1958">
         <v>3.14</v>
@@ -100061,13 +100061,13 @@
     </row>
     <row r="1959" spans="1:16">
       <c r="A1959" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1959" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C1959">
-        <v>2.886762764171116</v>
+        <v>2.881530421493133</v>
       </c>
       <c r="D1959" t="s">
         <v>436</v>
@@ -100079,22 +100079,22 @@
         <v>1</v>
       </c>
       <c r="G1959">
-        <v>0.005653237235828883</v>
+        <v>0.005618469578506867</v>
       </c>
       <c r="H1959">
         <v>0.006235681466371066</v>
       </c>
       <c r="I1959">
-        <v>0.2575557694578188</v>
+        <v>0.2627881121358016</v>
       </c>
       <c r="J1959">
         <v>0.4922552440672183</v>
       </c>
       <c r="K1959">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="L1959">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1959">
         <v>3.14</v>
@@ -100111,46 +100111,46 @@
     </row>
     <row r="1960" spans="1:16">
       <c r="A1960" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1960" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C1960">
-        <v>3.432648778680031</v>
+        <v>2.8919951068491</v>
       </c>
       <c r="D1960" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1960">
-        <v>3.086022379934147</v>
+        <v>3.144318533628935</v>
       </c>
       <c r="F1960">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1960">
-        <v>0.00694735122131997</v>
+        <v>0.0056880048931509</v>
       </c>
       <c r="H1960">
-        <v>0.006393977620065853</v>
+        <v>0.006235681466371066</v>
       </c>
       <c r="I1960">
-        <v>0.346626398745884</v>
+        <v>0.2523234267798347</v>
       </c>
       <c r="J1960">
         <v>0.4922552440672183</v>
       </c>
       <c r="K1960">
-        <v>3.57</v>
+        <v>2.84</v>
       </c>
       <c r="L1960">
-        <v>5.19</v>
+        <v>4.29</v>
       </c>
       <c r="M1960">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1960">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1960">
         <v>1</v>
@@ -100161,13 +100161,13 @@
     </row>
     <row r="1961" spans="1:16">
       <c r="A1961" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1961" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1961">
-        <v>3.379430072544571</v>
+        <v>3.432648778680031</v>
       </c>
       <c r="D1961" t="s">
         <v>456</v>
@@ -100179,22 +100179,22 @@
         <v>-1</v>
       </c>
       <c r="G1961">
-        <v>0.00712056992745543</v>
+        <v>0.00694735122131997</v>
       </c>
       <c r="H1961">
         <v>0.006393977620065853</v>
       </c>
       <c r="I1961">
-        <v>0.2934076926104234</v>
+        <v>0.346626398745884</v>
       </c>
       <c r="J1961">
         <v>0.4922552440672183</v>
       </c>
       <c r="K1961">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1961">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1961">
         <v>3.36</v>
@@ -100211,63 +100211,63 @@
     </row>
     <row r="1962" spans="1:16">
       <c r="A1962" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1962" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1962">
-        <v>2.907310156141165</v>
+        <v>3.379430072544571</v>
       </c>
       <c r="D1962" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1962">
-        <v>3.171581211903909</v>
+        <v>3.086022379934147</v>
       </c>
       <c r="F1962">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1962">
-        <v>0.005692689843858835</v>
+        <v>0.00712056992745543</v>
       </c>
       <c r="H1962">
-        <v>0.006208418788096091</v>
+        <v>0.006393977620065853</v>
       </c>
       <c r="I1962">
-        <v>0.2642710557627441</v>
+        <v>0.2934076926104234</v>
       </c>
       <c r="J1962">
-        <v>0.4835728624509845</v>
+        <v>0.4922552440672183</v>
       </c>
       <c r="K1962">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1962">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1962">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1962">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1962">
         <v>1</v>
       </c>
       <c r="P1962" t="s">
-        <v>584</v>
+        <v>248</v>
       </c>
     </row>
     <row r="1963" spans="1:16">
       <c r="A1963" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1963" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1963">
-        <v>2.905667442386263</v>
+        <v>2.907310156141165</v>
       </c>
       <c r="D1963" t="s">
         <v>436</v>
@@ -100279,22 +100279,22 @@
         <v>1</v>
       </c>
       <c r="G1963">
-        <v>0.005594332557613737</v>
+        <v>0.005692689843858835</v>
       </c>
       <c r="H1963">
         <v>0.006208418788096091</v>
       </c>
       <c r="I1963">
-        <v>0.2659137695176459</v>
+        <v>0.2642710557627441</v>
       </c>
       <c r="J1963">
         <v>0.4835728624509845</v>
       </c>
       <c r="K1963">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1963">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1963">
         <v>3.14</v>
@@ -100311,13 +100311,13 @@
     </row>
     <row r="1964" spans="1:16">
       <c r="A1964" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1964" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C1964">
-        <v>2.916653070639204</v>
+        <v>2.905667442386263</v>
       </c>
       <c r="D1964" t="s">
         <v>436</v>
@@ -100329,22 +100329,22 @@
         <v>1</v>
       </c>
       <c r="G1964">
-        <v>0.005663346929360796</v>
+        <v>0.005594332557613737</v>
       </c>
       <c r="H1964">
         <v>0.006208418788096091</v>
       </c>
       <c r="I1964">
-        <v>0.2549281412647049</v>
+        <v>0.2659137695176459</v>
       </c>
       <c r="J1964">
         <v>0.4835728624509845</v>
       </c>
       <c r="K1964">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="L1964">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="M1964">
         <v>3.14</v>
@@ -100361,46 +100361,46 @@
     </row>
     <row r="1965" spans="1:16">
       <c r="A1965" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1965" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C1965">
-        <v>3.463644881049986</v>
+        <v>2.916653070639204</v>
       </c>
       <c r="D1965" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1965">
-        <v>3.115195182164692</v>
+        <v>3.171581211903909</v>
       </c>
       <c r="F1965">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1965">
-        <v>0.006916355118950016</v>
+        <v>0.005663346929360796</v>
       </c>
       <c r="H1965">
-        <v>0.006364804817835308</v>
+        <v>0.006208418788096091</v>
       </c>
       <c r="I1965">
-        <v>0.3484496988852936</v>
+        <v>0.2549281412647049</v>
       </c>
       <c r="J1965">
         <v>0.4835728624509845</v>
       </c>
       <c r="K1965">
-        <v>3.57</v>
+        <v>2.84</v>
       </c>
       <c r="L1965">
-        <v>5.19</v>
+        <v>4.29</v>
       </c>
       <c r="M1965">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1965">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1965">
         <v>1</v>
@@ -100411,13 +100411,13 @@
     </row>
     <row r="1966" spans="1:16">
       <c r="A1966" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1966" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1966">
-        <v>3.412423122686259</v>
+        <v>3.463644881049986</v>
       </c>
       <c r="D1966" t="s">
         <v>456</v>
@@ -100429,22 +100429,22 @@
         <v>-1</v>
       </c>
       <c r="G1966">
-        <v>0.007087576877313742</v>
+        <v>0.006916355118950016</v>
       </c>
       <c r="H1966">
         <v>0.006364804817835308</v>
       </c>
       <c r="I1966">
-        <v>0.2972279405215668</v>
+        <v>0.3484496988852936</v>
       </c>
       <c r="J1966">
         <v>0.4835728624509845</v>
       </c>
       <c r="K1966">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1966">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1966">
         <v>3.36</v>
@@ -100461,63 +100461,63 @@
     </row>
     <row r="1967" spans="1:16">
       <c r="A1967" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1967" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1967">
-        <v>2.925123519687019</v>
+        <v>3.412423122686259</v>
       </c>
       <c r="D1967" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1967">
-        <v>3.19100272632543</v>
+        <v>3.115195182164692</v>
       </c>
       <c r="F1967">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1967">
-        <v>0.005674876480312981</v>
+        <v>0.007087576877313742</v>
       </c>
       <c r="H1967">
-        <v>0.006188997273674571</v>
+        <v>0.006364804817835308</v>
       </c>
       <c r="I1967">
-        <v>0.2658792066384112</v>
+        <v>0.2972279405215668</v>
       </c>
       <c r="J1967">
-        <v>0.4773876667753407</v>
+        <v>0.4835728624509845</v>
       </c>
       <c r="K1967">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="L1967">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M1967">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1967">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1967">
         <v>1</v>
       </c>
       <c r="P1967" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1968" spans="1:16">
       <c r="A1968" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1968" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C1968">
-        <v>2.922862286364553</v>
+        <v>2.925123519687019</v>
       </c>
       <c r="D1968" t="s">
         <v>436</v>
@@ -100529,22 +100529,22 @@
         <v>1</v>
       </c>
       <c r="G1968">
-        <v>0.005577137713635447</v>
+        <v>0.005674876480312981</v>
       </c>
       <c r="H1968">
         <v>0.006188997273674571</v>
       </c>
       <c r="I1968">
-        <v>0.2681404399608773</v>
+        <v>0.2658792066384112</v>
       </c>
       <c r="J1968">
         <v>0.4773876667753407</v>
       </c>
       <c r="K1968">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="L1968">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="M1968">
         <v>3.14</v>
@@ -100561,13 +100561,13 @@
     </row>
     <row r="1969" spans="1:16">
       <c r="A1969" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1969" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C1969">
-        <v>2.934219026358033</v>
+        <v>2.937636163032306</v>
       </c>
       <c r="D1969" t="s">
         <v>436</v>
@@ -100579,22 +100579,22 @@
         <v>1</v>
       </c>
       <c r="G1969">
-        <v>0.005645780973641968</v>
+        <v>0.005582363836967694</v>
       </c>
       <c r="H1969">
         <v>0.006188997273674571</v>
       </c>
       <c r="I1969">
-        <v>0.2567836999673974</v>
+        <v>0.2533665632931239</v>
       </c>
       <c r="J1969">
         <v>0.4773876667753407</v>
       </c>
       <c r="K1969">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="L1969">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="M1969">
         <v>3.14</v>
@@ -100611,46 +100611,46 @@
     </row>
     <row r="1970" spans="1:16">
       <c r="A1970" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1970" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="C1970">
-        <v>3.485726029612034</v>
+        <v>2.922862286364553</v>
       </c>
       <c r="D1970" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1970">
-        <v>3.135977439634855</v>
+        <v>3.19100272632543</v>
       </c>
       <c r="F1970">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1970">
-        <v>0.006894273970387966</v>
+        <v>0.005577137713635447</v>
       </c>
       <c r="H1970">
-        <v>0.006344022560365145</v>
+        <v>0.006188997273674571</v>
       </c>
       <c r="I1970">
-        <v>0.3497485899771791</v>
+        <v>0.2681404399608773</v>
       </c>
       <c r="J1970">
         <v>0.4773876667753407</v>
       </c>
       <c r="K1970">
-        <v>3.57</v>
+        <v>2.78</v>
       </c>
       <c r="L1970">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M1970">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1970">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1970">
         <v>1</v>
@@ -100661,46 +100661,46 @@
     </row>
     <row r="1971" spans="1:16">
       <c r="A1971" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1971" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C1971">
-        <v>3.435926866253705</v>
+        <v>2.934219026358033</v>
       </c>
       <c r="D1971" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1971">
-        <v>3.135977439634855</v>
+        <v>3.19100272632543</v>
       </c>
       <c r="F1971">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1971">
-        <v>0.007064073133746295</v>
+        <v>0.005645780973641968</v>
       </c>
       <c r="H1971">
-        <v>0.006344022560365145</v>
+        <v>0.006188997273674571</v>
       </c>
       <c r="I1971">
-        <v>0.2999494266188503</v>
+        <v>0.2567836999673974</v>
       </c>
       <c r="J1971">
         <v>0.4773876667753407</v>
       </c>
       <c r="K1971">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="L1971">
-        <v>5.25</v>
+        <v>4.29</v>
       </c>
       <c r="M1971">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1971">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1971">
         <v>1</v>
@@ -100711,113 +100711,113 @@
     </row>
     <row r="1972" spans="1:16">
       <c r="A1972" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1972" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C1972">
-        <v>2.92262134024316</v>
+        <v>3.485726029612034</v>
       </c>
       <c r="D1972" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1972">
-        <v>3.18827465568178</v>
+        <v>3.135977439634855</v>
       </c>
       <c r="F1972">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1972">
-        <v>0.00567737865975684</v>
+        <v>0.006894273970387966</v>
       </c>
       <c r="H1972">
-        <v>0.006191725344318221</v>
+        <v>0.006344022560365145</v>
       </c>
       <c r="I1972">
-        <v>0.2656533154386196</v>
+        <v>0.3497485899771791</v>
       </c>
       <c r="J1972">
-        <v>0.4782564790822359</v>
+        <v>0.4773876667753407</v>
       </c>
       <c r="K1972">
-        <v>2.88</v>
+        <v>3.57</v>
       </c>
       <c r="L1972">
-        <v>4.3</v>
+        <v>5.19</v>
       </c>
       <c r="M1972">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1972">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1972">
         <v>1</v>
       </c>
       <c r="P1972" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1973" spans="1:16">
       <c r="A1973" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B1973" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C1973">
-        <v>2.920446988151384</v>
+        <v>3.435926866253705</v>
       </c>
       <c r="D1973" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1973">
-        <v>3.18827465568178</v>
+        <v>3.135977439634855</v>
       </c>
       <c r="F1973">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1973">
-        <v>0.005579553011848615</v>
+        <v>0.007064073133746295</v>
       </c>
       <c r="H1973">
-        <v>0.006191725344318221</v>
+        <v>0.006344022560365145</v>
       </c>
       <c r="I1973">
-        <v>0.2678276675303954</v>
+        <v>0.2999494266188503</v>
       </c>
       <c r="J1973">
-        <v>0.4782564790822359</v>
+        <v>0.4773876667753407</v>
       </c>
       <c r="K1973">
-        <v>2.78</v>
+        <v>3.8</v>
       </c>
       <c r="L1973">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="M1973">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1973">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1973">
         <v>1</v>
       </c>
       <c r="P1973" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1974" spans="1:16">
       <c r="A1974" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1974" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C1974">
-        <v>2.93175159940645</v>
+        <v>2.92262134024316</v>
       </c>
       <c r="D1974" t="s">
         <v>436</v>
@@ -100829,22 +100829,22 @@
         <v>1</v>
       </c>
       <c r="G1974">
-        <v>0.00564824840059355</v>
+        <v>0.00567737865975684</v>
       </c>
       <c r="H1974">
         <v>0.006191725344318221</v>
       </c>
       <c r="I1974">
-        <v>0.2565230562753298</v>
+        <v>0.2656533154386196</v>
       </c>
       <c r="J1974">
         <v>0.4782564790822359</v>
       </c>
       <c r="K1974">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L1974">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="M1974">
         <v>3.14</v>
@@ -100861,46 +100861,46 @@
     </row>
     <row r="1975" spans="1:16">
       <c r="A1975" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1975" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C1975">
-        <v>3.482624369676418</v>
+        <v>2.935229552942206</v>
       </c>
       <c r="D1975" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1975">
-        <v>3.133058230283687</v>
+        <v>3.18827465568178</v>
       </c>
       <c r="F1975">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1975">
-        <v>0.006897375630323582</v>
+        <v>0.005584770447057794</v>
       </c>
       <c r="H1975">
-        <v>0.006346941769716313</v>
+        <v>0.006191725344318221</v>
       </c>
       <c r="I1975">
-        <v>0.349566139392731</v>
+        <v>0.2530451027395735</v>
       </c>
       <c r="J1975">
         <v>0.4782564790822359</v>
       </c>
       <c r="K1975">
-        <v>3.57</v>
+        <v>2.77</v>
       </c>
       <c r="L1975">
-        <v>5.19</v>
+        <v>4.26</v>
       </c>
       <c r="M1975">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1975">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1975">
         <v>1</v>
@@ -100911,46 +100911,46 @@
     </row>
     <row r="1976" spans="1:16">
       <c r="A1976" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1976" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C1976">
-        <v>3.432625379487503</v>
+        <v>2.920446988151384</v>
       </c>
       <c r="D1976" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1976">
-        <v>3.133058230283687</v>
+        <v>3.18827465568178</v>
       </c>
       <c r="F1976">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1976">
-        <v>0.007067374620512497</v>
+        <v>0.005579553011848615</v>
       </c>
       <c r="H1976">
-        <v>0.006346941769716313</v>
+        <v>0.006191725344318221</v>
       </c>
       <c r="I1976">
-        <v>0.2995671492038161</v>
+        <v>0.2678276675303954</v>
       </c>
       <c r="J1976">
         <v>0.4782564790822359</v>
       </c>
       <c r="K1976">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="L1976">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="M1976">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1976">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1976">
         <v>1</v>
@@ -100961,40 +100961,40 @@
     </row>
     <row r="1977" spans="1:16">
       <c r="A1977" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1977" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C1977">
-        <v>2.929140321660022</v>
+        <v>2.93175159940645</v>
       </c>
       <c r="D1977" t="s">
         <v>436</v>
       </c>
       <c r="E1977">
-        <v>3.19538215625433</v>
+        <v>3.18827465568178</v>
       </c>
       <c r="F1977">
         <v>1</v>
       </c>
       <c r="G1977">
-        <v>0.005670859678339977</v>
+        <v>0.00564824840059355</v>
       </c>
       <c r="H1977">
-        <v>0.00618461784374567</v>
+        <v>0.006191725344318221</v>
       </c>
       <c r="I1977">
-        <v>0.2662418345943078</v>
+        <v>0.2565230562753298</v>
       </c>
       <c r="J1977">
-        <v>0.4759929438680478</v>
+        <v>0.4782564790822359</v>
       </c>
       <c r="K1977">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="L1977">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="M1977">
         <v>3.14</v>
@@ -101006,151 +101006,151 @@
         <v>1</v>
       </c>
       <c r="P1977" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1978" spans="1:16">
       <c r="A1978" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1978" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="C1978">
-        <v>2.926739616046827</v>
+        <v>3.482624369676418</v>
       </c>
       <c r="D1978" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1978">
-        <v>3.19538215625433</v>
+        <v>3.133058230283687</v>
       </c>
       <c r="F1978">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1978">
-        <v>0.005573260383953173</v>
+        <v>0.006897375630323582</v>
       </c>
       <c r="H1978">
-        <v>0.00618461784374567</v>
+        <v>0.006346941769716313</v>
       </c>
       <c r="I1978">
-        <v>0.268642540207503</v>
+        <v>0.349566139392731</v>
       </c>
       <c r="J1978">
-        <v>0.4759929438680478</v>
+        <v>0.4782564790822359</v>
       </c>
       <c r="K1978">
-        <v>2.78</v>
+        <v>3.57</v>
       </c>
       <c r="L1978">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1978">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1978">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1978">
         <v>1</v>
       </c>
       <c r="P1978" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1979" spans="1:16">
       <c r="A1979" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1979" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C1979">
-        <v>2.938180039414744</v>
+        <v>3.432625379487503</v>
       </c>
       <c r="D1979" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1979">
-        <v>3.19538215625433</v>
+        <v>3.133058230283687</v>
       </c>
       <c r="F1979">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1979">
-        <v>0.005641819960585256</v>
+        <v>0.007067374620512497</v>
       </c>
       <c r="H1979">
-        <v>0.00618461784374567</v>
+        <v>0.006346941769716313</v>
       </c>
       <c r="I1979">
-        <v>0.2572021168395859</v>
+        <v>0.2995671492038161</v>
       </c>
       <c r="J1979">
-        <v>0.4759929438680478</v>
+        <v>0.4782564790822359</v>
       </c>
       <c r="K1979">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="L1979">
-        <v>4.29</v>
+        <v>5.25</v>
       </c>
       <c r="M1979">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1979">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1979">
         <v>1</v>
       </c>
       <c r="P1979" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1980" spans="1:16">
       <c r="A1980" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1980" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C1980">
-        <v>3.49070519039107</v>
+        <v>2.929140321660022</v>
       </c>
       <c r="D1980" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1980">
-        <v>3.14066370860336</v>
+        <v>3.19538215625433</v>
       </c>
       <c r="F1980">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1980">
-        <v>0.006889294809608931</v>
+        <v>0.005670859678339977</v>
       </c>
       <c r="H1980">
-        <v>0.00633933629139664</v>
+        <v>0.00618461784374567</v>
       </c>
       <c r="I1980">
-        <v>0.3500414817877098</v>
+        <v>0.2662418345943078</v>
       </c>
       <c r="J1980">
         <v>0.4759929438680478</v>
       </c>
       <c r="K1980">
-        <v>3.57</v>
+        <v>2.88</v>
       </c>
       <c r="L1980">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M1980">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1980">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1980">
         <v>1</v>
@@ -101161,46 +101161,46 @@
     </row>
     <row r="1981" spans="1:16">
       <c r="A1981" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1981" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C1981">
-        <v>3.441226813301419</v>
+        <v>2.941499545485507</v>
       </c>
       <c r="D1981" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1981">
-        <v>3.14066370860336</v>
+        <v>3.19538215625433</v>
       </c>
       <c r="F1981">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1981">
-        <v>0.007058773186698582</v>
+        <v>0.005578500454514492</v>
       </c>
       <c r="H1981">
-        <v>0.00633933629139664</v>
+        <v>0.00618461784374567</v>
       </c>
       <c r="I1981">
-        <v>0.3005631046980586</v>
+        <v>0.253882610768823</v>
       </c>
       <c r="J1981">
         <v>0.4759929438680478</v>
       </c>
       <c r="K1981">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="L1981">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="M1981">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1981">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1981">
         <v>1</v>
@@ -101211,40 +101211,40 @@
     </row>
     <row r="1982" spans="1:16">
       <c r="A1982" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1982" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C1982">
-        <v>2.939070121195086</v>
+        <v>2.926739616046827</v>
       </c>
       <c r="D1982" t="s">
         <v>436</v>
       </c>
       <c r="E1982">
-        <v>3.206208396025199</v>
+        <v>3.19538215625433</v>
       </c>
       <c r="F1982">
         <v>1</v>
       </c>
       <c r="G1982">
-        <v>0.005660929878804914</v>
+        <v>0.005573260383953173</v>
       </c>
       <c r="H1982">
-        <v>0.006173791603974802</v>
+        <v>0.00618461784374567</v>
       </c>
       <c r="I1982">
-        <v>0.2671382748301125</v>
+        <v>0.268642540207503</v>
       </c>
       <c r="J1982">
-        <v>0.4725450968072616</v>
+        <v>0.4759929438680478</v>
       </c>
       <c r="K1982">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="L1982">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="M1982">
         <v>3.14</v>
@@ -101256,45 +101256,45 @@
         <v>1</v>
       </c>
       <c r="P1982" t="s">
-        <v>249</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1983" spans="1:16">
       <c r="A1983" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1983" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="C1983">
-        <v>2.951050081843885</v>
+        <v>2.938180039414744</v>
       </c>
       <c r="D1983" t="s">
         <v>436</v>
       </c>
       <c r="E1983">
-        <v>3.206208396025199</v>
+        <v>3.19538215625433</v>
       </c>
       <c r="F1983">
         <v>1</v>
       </c>
       <c r="G1983">
-        <v>0.005568949918156115</v>
+        <v>0.005641819960585256</v>
       </c>
       <c r="H1983">
-        <v>0.006173791603974802</v>
+        <v>0.00618461784374567</v>
       </c>
       <c r="I1983">
-        <v>0.2551583141813136</v>
+        <v>0.2572021168395859</v>
       </c>
       <c r="J1983">
-        <v>0.4725450968072616</v>
+        <v>0.4759929438680478</v>
       </c>
       <c r="K1983">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="L1983">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
       <c r="M1983">
         <v>3.14</v>
@@ -101306,151 +101306,151 @@
         <v>1</v>
       </c>
       <c r="P1983" t="s">
-        <v>249</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1984" spans="1:16">
       <c r="A1984" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1984" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="C1984">
-        <v>2.936324630875813</v>
+        <v>3.49070519039107</v>
       </c>
       <c r="D1984" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1984">
-        <v>3.206208396025199</v>
+        <v>3.14066370860336</v>
       </c>
       <c r="F1984">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1984">
-        <v>0.005563675369124188</v>
+        <v>0.006889294809608931</v>
       </c>
       <c r="H1984">
-        <v>0.006173791603974802</v>
+        <v>0.00633933629139664</v>
       </c>
       <c r="I1984">
-        <v>0.2698837651493857</v>
+        <v>0.3500414817877098</v>
       </c>
       <c r="J1984">
-        <v>0.4725450968072616</v>
+        <v>0.4759929438680478</v>
       </c>
       <c r="K1984">
-        <v>2.78</v>
+        <v>3.57</v>
       </c>
       <c r="L1984">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1984">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1984">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1984">
         <v>1</v>
       </c>
       <c r="P1984" t="s">
-        <v>249</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1985" spans="1:16">
       <c r="A1985" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1985" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C1985">
-        <v>2.947971925067377</v>
+        <v>3.441226813301419</v>
       </c>
       <c r="D1985" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1985">
-        <v>3.206208396025199</v>
+        <v>3.14066370860336</v>
       </c>
       <c r="F1985">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1985">
-        <v>0.005632028074932623</v>
+        <v>0.007058773186698582</v>
       </c>
       <c r="H1985">
-        <v>0.006173791603974802</v>
+        <v>0.00633933629139664</v>
       </c>
       <c r="I1985">
-        <v>0.2582364709578213</v>
+        <v>0.3005631046980586</v>
       </c>
       <c r="J1985">
-        <v>0.4725450968072616</v>
+        <v>0.4759929438680478</v>
       </c>
       <c r="K1985">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="L1985">
-        <v>4.29</v>
+        <v>5.25</v>
       </c>
       <c r="M1985">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1985">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1985">
         <v>1</v>
       </c>
       <c r="P1985" t="s">
-        <v>249</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1986" spans="1:16">
       <c r="A1986" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1986" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C1986">
-        <v>3.503014004398076</v>
+        <v>2.953246474099304</v>
       </c>
       <c r="D1986" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1986">
-        <v>3.152248474727601</v>
+        <v>3.206208396025199</v>
       </c>
       <c r="F1986">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1986">
-        <v>0.006876985995601924</v>
+        <v>0.005646753525900696</v>
       </c>
       <c r="H1986">
-        <v>0.006327751525272399</v>
+        <v>0.006173791603974802</v>
       </c>
       <c r="I1986">
-        <v>0.350765529670475</v>
+        <v>0.2529619219258947</v>
       </c>
       <c r="J1986">
         <v>0.4725450968072616</v>
       </c>
       <c r="K1986">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="L1986">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M1986">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1986">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1986">
         <v>1</v>
@@ -101461,46 +101461,46 @@
     </row>
     <row r="1987" spans="1:16">
       <c r="A1987" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1987" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C1987">
-        <v>3.454328632132406</v>
+        <v>2.951050081843885</v>
       </c>
       <c r="D1987" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1987">
-        <v>3.152248474727601</v>
+        <v>3.206208396025199</v>
       </c>
       <c r="F1987">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1987">
-        <v>0.007045671367867595</v>
+        <v>0.005568949918156115</v>
       </c>
       <c r="H1987">
-        <v>0.006327751525272399</v>
+        <v>0.006173791603974802</v>
       </c>
       <c r="I1987">
-        <v>0.3020801574048044</v>
+        <v>0.2551583141813136</v>
       </c>
       <c r="J1987">
         <v>0.4725450968072616</v>
       </c>
       <c r="K1987">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="L1987">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="M1987">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1987">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1987">
         <v>1</v>
@@ -101511,40 +101511,40 @@
     </row>
     <row r="1988" spans="1:16">
       <c r="A1988" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1988" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C1988">
-        <v>2.970261345114207</v>
+        <v>2.936324630875813</v>
       </c>
       <c r="D1988" t="s">
         <v>436</v>
       </c>
       <c r="E1988">
-        <v>3.224954604792496</v>
+        <v>3.206208396025199</v>
       </c>
       <c r="F1988">
         <v>1</v>
       </c>
       <c r="G1988">
-        <v>0.005629738654885793</v>
+        <v>0.005563675369124188</v>
       </c>
       <c r="H1988">
-        <v>0.006155045395207505</v>
+        <v>0.006173791603974802</v>
       </c>
       <c r="I1988">
-        <v>0.2546932596782883</v>
+        <v>0.2698837651493857</v>
       </c>
       <c r="J1988">
-        <v>0.466574966626594</v>
+        <v>0.4725450968072616</v>
       </c>
       <c r="K1988">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="L1988">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="M1988">
         <v>3.14</v>
@@ -101556,45 +101556,45 @@
         <v>1</v>
       </c>
       <c r="P1988" t="s">
-        <v>588</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1989" spans="1:16">
       <c r="A1989" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1989" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="C1989">
-        <v>2.967587342444334</v>
+        <v>2.947971925067377</v>
       </c>
       <c r="D1989" t="s">
         <v>436</v>
       </c>
       <c r="E1989">
-        <v>3.224954604792496</v>
+        <v>3.206208396025199</v>
       </c>
       <c r="F1989">
         <v>1</v>
       </c>
       <c r="G1989">
-        <v>0.005552412657555666</v>
+        <v>0.005632028074932623</v>
       </c>
       <c r="H1989">
-        <v>0.006155045395207505</v>
+        <v>0.006173791603974802</v>
       </c>
       <c r="I1989">
-        <v>0.2573672623481613</v>
+        <v>0.2582364709578213</v>
       </c>
       <c r="J1989">
-        <v>0.466574966626594</v>
+        <v>0.4725450968072616</v>
       </c>
       <c r="K1989">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="L1989">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
       <c r="M1989">
         <v>3.14</v>
@@ -101606,151 +101606,151 @@
         <v>1</v>
       </c>
       <c r="P1989" t="s">
-        <v>588</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1990" spans="1:16">
       <c r="A1990" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1990" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="C1990">
-        <v>2.952921592778069</v>
+        <v>3.503014004398076</v>
       </c>
       <c r="D1990" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1990">
-        <v>3.224954604792496</v>
+        <v>3.152248474727601</v>
       </c>
       <c r="F1990">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1990">
-        <v>0.005547078407221932</v>
+        <v>0.006876985995601924</v>
       </c>
       <c r="H1990">
-        <v>0.006155045395207505</v>
+        <v>0.006327751525272399</v>
       </c>
       <c r="I1990">
-        <v>0.2720330120144268</v>
+        <v>0.350765529670475</v>
       </c>
       <c r="J1990">
-        <v>0.466574966626594</v>
+        <v>0.4725450968072616</v>
       </c>
       <c r="K1990">
-        <v>2.78</v>
+        <v>3.57</v>
       </c>
       <c r="L1990">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M1990">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1990">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1990">
         <v>1</v>
       </c>
       <c r="P1990" t="s">
-        <v>588</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1991" spans="1:16">
       <c r="A1991" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1991" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C1991">
-        <v>2.964927094780473</v>
+        <v>3.454328632132406</v>
       </c>
       <c r="D1991" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1991">
-        <v>3.224954604792496</v>
+        <v>3.152248474727601</v>
       </c>
       <c r="F1991">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1991">
-        <v>0.005615072905219527</v>
+        <v>0.007045671367867595</v>
       </c>
       <c r="H1991">
-        <v>0.006155045395207505</v>
+        <v>0.006327751525272399</v>
       </c>
       <c r="I1991">
-        <v>0.2600275100120224</v>
+        <v>0.3020801574048044</v>
       </c>
       <c r="J1991">
-        <v>0.466574966626594</v>
+        <v>0.4725450968072616</v>
       </c>
       <c r="K1991">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="L1991">
-        <v>4.29</v>
+        <v>5.25</v>
       </c>
       <c r="M1991">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1991">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1991">
         <v>1</v>
       </c>
       <c r="P1991" t="s">
-        <v>588</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1992" spans="1:16">
       <c r="A1992" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1992" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C1992">
-        <v>3.52432736914306</v>
+        <v>2.970261345114207</v>
       </c>
       <c r="D1992" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1992">
-        <v>3.172308112134645</v>
+        <v>3.224954604792496</v>
       </c>
       <c r="F1992">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1992">
-        <v>0.006855672630856941</v>
+        <v>0.005629738654885793</v>
       </c>
       <c r="H1992">
-        <v>0.006307691887865356</v>
+        <v>0.006155045395207505</v>
       </c>
       <c r="I1992">
-        <v>0.3520192570084149</v>
+        <v>0.2546932596782883</v>
       </c>
       <c r="J1992">
         <v>0.466574966626594</v>
       </c>
       <c r="K1992">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="L1992">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M1992">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1992">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1992">
         <v>1</v>
@@ -101761,46 +101761,46 @@
     </row>
     <row r="1993" spans="1:16">
       <c r="A1993" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1993" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C1993">
-        <v>3.477015126818943</v>
+        <v>2.967587342444334</v>
       </c>
       <c r="D1993" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1993">
-        <v>3.172308112134645</v>
+        <v>3.224954604792496</v>
       </c>
       <c r="F1993">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1993">
-        <v>0.007022984873181057</v>
+        <v>0.005552412657555666</v>
       </c>
       <c r="H1993">
-        <v>0.006307691887865356</v>
+        <v>0.006155045395207505</v>
       </c>
       <c r="I1993">
-        <v>0.3047070146842978</v>
+        <v>0.2573672623481613</v>
       </c>
       <c r="J1993">
         <v>0.466574966626594</v>
       </c>
       <c r="K1993">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="L1993">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="M1993">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1993">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1993">
         <v>1</v>
@@ -101811,40 +101811,40 @@
     </row>
     <row r="1994" spans="1:16">
       <c r="A1994" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1994" t="s">
         <v>270</v>
       </c>
       <c r="C1994">
-        <v>2.984944780390499</v>
+        <v>2.971584591443133</v>
       </c>
       <c r="D1994" t="s">
         <v>436</v>
       </c>
       <c r="E1994">
-        <v>3.238534751951859</v>
+        <v>3.224954604792496</v>
       </c>
       <c r="F1994">
         <v>1</v>
       </c>
       <c r="G1994">
-        <v>0.0055550552196095</v>
+        <v>0.005528415408556867</v>
       </c>
       <c r="H1994">
-        <v>0.006141465248048142</v>
+        <v>0.006155045395207505</v>
       </c>
       <c r="I1994">
-        <v>0.2535899715613601</v>
+        <v>0.2533700133493628</v>
       </c>
       <c r="J1994">
-        <v>0.4622500789962232</v>
+        <v>0.466574966626594</v>
       </c>
       <c r="K1994">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="L1994">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M1994">
         <v>3.14</v>
@@ -101856,45 +101856,45 @@
         <v>1</v>
       </c>
       <c r="P1994" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1995" spans="1:16">
       <c r="A1995" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1995" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C1995">
-        <v>2.982587274860764</v>
+        <v>2.964927094780473</v>
       </c>
       <c r="D1995" t="s">
         <v>436</v>
       </c>
       <c r="E1995">
-        <v>3.238534751951859</v>
+        <v>3.224954604792496</v>
       </c>
       <c r="F1995">
         <v>1</v>
       </c>
       <c r="G1995">
-        <v>0.005617412725139236</v>
+        <v>0.005615072905219527</v>
       </c>
       <c r="H1995">
-        <v>0.006141465248048142</v>
+        <v>0.006155045395207505</v>
       </c>
       <c r="I1995">
-        <v>0.2559474770910959</v>
+        <v>0.2600275100120224</v>
       </c>
       <c r="J1995">
-        <v>0.4622500789962232</v>
+        <v>0.466574966626594</v>
       </c>
       <c r="K1995">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="L1995">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="M1995">
         <v>3.14</v>
@@ -101906,118 +101906,118 @@
         <v>1</v>
       </c>
       <c r="P1995" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1996" spans="1:16">
       <c r="A1996" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1996" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C1996">
-        <v>2.985699778810575</v>
+        <v>3.52432736914306</v>
       </c>
       <c r="D1996" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1996">
-        <v>3.238534751951859</v>
+        <v>3.172308112134645</v>
       </c>
       <c r="F1996">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1996">
-        <v>0.005574300221189425</v>
+        <v>0.006855672630856941</v>
       </c>
       <c r="H1996">
-        <v>0.006141465248048142</v>
+        <v>0.006307691887865356</v>
       </c>
       <c r="I1996">
-        <v>0.252834973141284</v>
+        <v>0.3520192570084149</v>
       </c>
       <c r="J1996">
-        <v>0.4622500789962232</v>
+        <v>0.466574966626594</v>
       </c>
       <c r="K1996">
-        <v>2.8</v>
+        <v>3.57</v>
       </c>
       <c r="L1996">
-        <v>4.28</v>
+        <v>5.19</v>
       </c>
       <c r="M1996">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1996">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1996">
         <v>1</v>
       </c>
       <c r="P1996" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1997" spans="1:16">
       <c r="A1997" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1997" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C1997">
-        <v>2.983434783550348</v>
+        <v>3.477015126818943</v>
       </c>
       <c r="D1997" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1997">
-        <v>3.238534751951859</v>
+        <v>3.172308112134645</v>
       </c>
       <c r="F1997">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1997">
-        <v>0.005516565216449652</v>
+        <v>0.007022984873181057</v>
       </c>
       <c r="H1997">
-        <v>0.006141465248048142</v>
+        <v>0.006307691887865356</v>
       </c>
       <c r="I1997">
-        <v>0.2550999684015114</v>
+        <v>0.3047070146842978</v>
       </c>
       <c r="J1997">
-        <v>0.4622500789962232</v>
+        <v>0.466574966626594</v>
       </c>
       <c r="K1997">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="L1997">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="M1997">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1997">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1997">
         <v>1</v>
       </c>
       <c r="P1997" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1998" spans="1:16">
       <c r="A1998" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1998" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C1998">
-        <v>2.977209775650726</v>
+        <v>2.984944780390499</v>
       </c>
       <c r="D1998" t="s">
         <v>436</v>
@@ -102029,22 +102029,22 @@
         <v>1</v>
       </c>
       <c r="G1998">
-        <v>0.005602790224349274</v>
+        <v>0.0055550552196095</v>
       </c>
       <c r="H1998">
         <v>0.006141465248048142</v>
       </c>
       <c r="I1998">
-        <v>0.2613249763011334</v>
+        <v>0.2535899715613601</v>
       </c>
       <c r="J1998">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1998">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="L1998">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="M1998">
         <v>3.14</v>
@@ -102061,46 +102061,46 @@
     </row>
     <row r="1999" spans="1:16">
       <c r="A1999" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1999" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C1999">
-        <v>3.539767217983484</v>
+        <v>2.982587274860764</v>
       </c>
       <c r="D1999" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E1999">
-        <v>3.18683973457269</v>
+        <v>3.238534751951859</v>
       </c>
       <c r="F1999">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1999">
-        <v>0.006840232782016517</v>
+        <v>0.005617412725139236</v>
       </c>
       <c r="H1999">
-        <v>0.006293160265427311</v>
+        <v>0.006141465248048142</v>
       </c>
       <c r="I1999">
-        <v>0.3529274834107934</v>
+        <v>0.2559474770910959</v>
       </c>
       <c r="J1999">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1999">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="L1999">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M1999">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1999">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1999">
         <v>1</v>
@@ -102111,46 +102111,46 @@
     </row>
     <row r="2000" spans="1:16">
       <c r="A2000" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B2000" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C2000">
-        <v>3.493449699814352</v>
+        <v>2.985699778810575</v>
       </c>
       <c r="D2000" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2000">
-        <v>3.18683973457269</v>
+        <v>3.238534751951859</v>
       </c>
       <c r="F2000">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2000">
-        <v>0.007006550300185647</v>
+        <v>0.005574300221189425</v>
       </c>
       <c r="H2000">
-        <v>0.006293160265427311</v>
+        <v>0.006141465248048142</v>
       </c>
       <c r="I2000">
-        <v>0.3066099652416616</v>
+        <v>0.252834973141284</v>
       </c>
       <c r="J2000">
         <v>0.4622500789962232</v>
       </c>
       <c r="K2000">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="L2000">
-        <v>5.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2000">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2000">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2000">
         <v>1</v>
@@ -102161,40 +102161,40 @@
     </row>
     <row r="2001" spans="1:16">
       <c r="A2001" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2001" t="s">
         <v>270</v>
       </c>
       <c r="C2001">
-        <v>2.992568684079322</v>
+        <v>2.983434783550348</v>
       </c>
       <c r="D2001" t="s">
         <v>436</v>
       </c>
       <c r="E2001">
-        <v>3.247145923744271</v>
+        <v>3.238534751951859</v>
       </c>
       <c r="F2001">
         <v>1</v>
       </c>
       <c r="G2001">
-        <v>0.005547431315920677</v>
+        <v>0.005516565216449652</v>
       </c>
       <c r="H2001">
-        <v>0.00613285407625573</v>
+        <v>0.006141465248048142</v>
       </c>
       <c r="I2001">
-        <v>0.2545772396649486</v>
+        <v>0.2550999684015114</v>
       </c>
       <c r="J2001">
-        <v>0.459507667597366</v>
+        <v>0.4622500789962232</v>
       </c>
       <c r="K2001">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="L2001">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="M2001">
         <v>3.14</v>
@@ -102206,45 +102206,45 @@
         <v>1</v>
       </c>
       <c r="P2001" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="2002" spans="1:16">
       <c r="A2002" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2002" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C2002">
-        <v>2.990403147347507</v>
+        <v>2.977209775650726</v>
       </c>
       <c r="D2002" t="s">
         <v>436</v>
       </c>
       <c r="E2002">
-        <v>3.247145923744271</v>
+        <v>3.238534751951859</v>
       </c>
       <c r="F2002">
         <v>1</v>
       </c>
       <c r="G2002">
-        <v>0.005609596852652493</v>
+        <v>0.005602790224349274</v>
       </c>
       <c r="H2002">
-        <v>0.00613285407625573</v>
+        <v>0.006141465248048142</v>
       </c>
       <c r="I2002">
-        <v>0.2567427763967642</v>
+        <v>0.2613249763011334</v>
       </c>
       <c r="J2002">
-        <v>0.459507667597366</v>
+        <v>0.4622500789962232</v>
       </c>
       <c r="K2002">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="L2002">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="M2002">
         <v>3.14</v>
@@ -102256,118 +102256,118 @@
         <v>1</v>
       </c>
       <c r="P2002" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="2003" spans="1:16">
       <c r="A2003" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2003" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C2003">
-        <v>2.993378530727376</v>
+        <v>3.539767217983484</v>
       </c>
       <c r="D2003" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2003">
-        <v>3.247145923744271</v>
+        <v>3.18683973457269</v>
       </c>
       <c r="F2003">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2003">
-        <v>0.005566621469272625</v>
+        <v>0.006840232782016517</v>
       </c>
       <c r="H2003">
-        <v>0.00613285407625573</v>
+        <v>0.006293160265427311</v>
       </c>
       <c r="I2003">
-        <v>0.2537673930168953</v>
+        <v>0.3529274834107934</v>
       </c>
       <c r="J2003">
-        <v>0.459507667597366</v>
+        <v>0.4622500789962232</v>
       </c>
       <c r="K2003">
-        <v>2.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2003">
-        <v>4.28</v>
+        <v>5.19</v>
       </c>
       <c r="M2003">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2003">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2003">
         <v>1</v>
       </c>
       <c r="P2003" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="2004" spans="1:16">
       <c r="A2004" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2004" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C2004">
-        <v>2.990948990783217</v>
+        <v>3.493449699814352</v>
       </c>
       <c r="D2004" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2004">
-        <v>3.247145923744271</v>
+        <v>3.18683973457269</v>
       </c>
       <c r="F2004">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2004">
-        <v>0.005509051009216784</v>
+        <v>0.007006550300185647</v>
       </c>
       <c r="H2004">
-        <v>0.00613285407625573</v>
+        <v>0.006293160265427311</v>
       </c>
       <c r="I2004">
-        <v>0.2561969329610543</v>
+        <v>0.3066099652416616</v>
       </c>
       <c r="J2004">
-        <v>0.459507667597366</v>
+        <v>0.4622500789962232</v>
       </c>
       <c r="K2004">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="L2004">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="M2004">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2004">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2004">
         <v>1</v>
       </c>
       <c r="P2004" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="2005" spans="1:16">
       <c r="A2005" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2005" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C2005">
-        <v>2.984998224023481</v>
+        <v>2.992568684079322</v>
       </c>
       <c r="D2005" t="s">
         <v>436</v>
@@ -102379,22 +102379,22 @@
         <v>1</v>
       </c>
       <c r="G2005">
-        <v>0.00559500177597652</v>
+        <v>0.005547431315920677</v>
       </c>
       <c r="H2005">
         <v>0.00613285407625573</v>
       </c>
       <c r="I2005">
-        <v>0.2621476997207903</v>
+        <v>0.2545772396649486</v>
       </c>
       <c r="J2005">
         <v>0.459507667597366</v>
       </c>
       <c r="K2005">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="L2005">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="M2005">
         <v>3.14</v>
@@ -102411,46 +102411,46 @@
     </row>
     <row r="2006" spans="1:16">
       <c r="A2006" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2006" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C2006">
-        <v>3.549557626677404</v>
+        <v>2.990403147347507</v>
       </c>
       <c r="D2006" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2006">
-        <v>3.19605423687285</v>
+        <v>3.247145923744271</v>
       </c>
       <c r="F2006">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2006">
-        <v>0.006830442373322598</v>
+        <v>0.005609596852652493</v>
       </c>
       <c r="H2006">
-        <v>0.00628394576312715</v>
+        <v>0.00613285407625573</v>
       </c>
       <c r="I2006">
-        <v>0.3535033898045534</v>
+        <v>0.2567427763967642</v>
       </c>
       <c r="J2006">
         <v>0.459507667597366</v>
       </c>
       <c r="K2006">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="L2006">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M2006">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2006">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2006">
         <v>1</v>
@@ -102461,46 +102461,46 @@
     </row>
     <row r="2007" spans="1:16">
       <c r="A2007" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B2007" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C2007">
-        <v>3.503870863130009</v>
+        <v>2.993378530727376</v>
       </c>
       <c r="D2007" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2007">
-        <v>3.19605423687285</v>
+        <v>3.247145923744271</v>
       </c>
       <c r="F2007">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2007">
-        <v>0.006996129136869991</v>
+        <v>0.005566621469272625</v>
       </c>
       <c r="H2007">
-        <v>0.00628394576312715</v>
+        <v>0.00613285407625573</v>
       </c>
       <c r="I2007">
-        <v>0.3078166262571589</v>
+        <v>0.2537673930168953</v>
       </c>
       <c r="J2007">
         <v>0.459507667597366</v>
       </c>
       <c r="K2007">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="L2007">
-        <v>5.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2007">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2007">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2007">
         <v>1</v>
@@ -102511,40 +102511,40 @@
     </row>
     <row r="2008" spans="1:16">
       <c r="A2008" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2008" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C2008">
-        <v>2.997405526308626</v>
+        <v>2.990948990783217</v>
       </c>
       <c r="D2008" t="s">
         <v>436</v>
       </c>
       <c r="E2008">
-        <v>3.254860825476872</v>
+        <v>3.247145923744271</v>
       </c>
       <c r="F2008">
         <v>1</v>
       </c>
       <c r="G2008">
-        <v>0.005602594473691374</v>
+        <v>0.005509051009216784</v>
       </c>
       <c r="H2008">
-        <v>0.006125139174523129</v>
+        <v>0.00613285407625573</v>
       </c>
       <c r="I2008">
-        <v>0.2574552991682468</v>
+        <v>0.2561969329610543</v>
       </c>
       <c r="J2008">
-        <v>0.4570506925232892</v>
+        <v>0.459507667597366</v>
       </c>
       <c r="K2008">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="L2008">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="M2008">
         <v>3.14</v>
@@ -102556,45 +102556,45 @@
         <v>1</v>
       </c>
       <c r="P2008" t="s">
-        <v>270</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2009" spans="1:16">
       <c r="A2009" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2009" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="C2009">
-        <v>3.000258060934791</v>
+        <v>2.984998224023481</v>
       </c>
       <c r="D2009" t="s">
         <v>436</v>
       </c>
       <c r="E2009">
-        <v>3.254860825476872</v>
+        <v>3.247145923744271</v>
       </c>
       <c r="F2009">
         <v>1</v>
       </c>
       <c r="G2009">
-        <v>0.00555974193906521</v>
+        <v>0.00559500177597652</v>
       </c>
       <c r="H2009">
-        <v>0.006125139174523129</v>
+        <v>0.00613285407625573</v>
       </c>
       <c r="I2009">
-        <v>0.2546027645420819</v>
+        <v>0.2621476997207903</v>
       </c>
       <c r="J2009">
-        <v>0.4570506925232892</v>
+        <v>0.459507667597366</v>
       </c>
       <c r="K2009">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="L2009">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="M2009">
         <v>3.14</v>
@@ -102606,245 +102606,245 @@
         <v>1</v>
       </c>
       <c r="P2009" t="s">
-        <v>270</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2010" spans="1:16">
       <c r="A2010" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2010" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C2010">
-        <v>2.997681102486188</v>
+        <v>3.549557626677404</v>
       </c>
       <c r="D2010" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2010">
-        <v>3.254860825476872</v>
+        <v>3.19605423687285</v>
       </c>
       <c r="F2010">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2010">
-        <v>0.005502318897513812</v>
+        <v>0.006830442373322598</v>
       </c>
       <c r="H2010">
-        <v>0.006125139174523129</v>
+        <v>0.00628394576312715</v>
       </c>
       <c r="I2010">
-        <v>0.2571797229906849</v>
+        <v>0.3535033898045534</v>
       </c>
       <c r="J2010">
-        <v>0.4570506925232892</v>
+        <v>0.459507667597366</v>
       </c>
       <c r="K2010">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="L2010">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2010">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2010">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2010">
         <v>1</v>
       </c>
       <c r="P2010" t="s">
-        <v>270</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2011" spans="1:16">
       <c r="A2011" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2011" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C2011">
-        <v>2.991976033233859</v>
+        <v>3.503870863130009</v>
       </c>
       <c r="D2011" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2011">
-        <v>3.254860825476872</v>
+        <v>3.19605423687285</v>
       </c>
       <c r="F2011">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2011">
-        <v>0.00558802396676614</v>
+        <v>0.006996129136869991</v>
       </c>
       <c r="H2011">
-        <v>0.006125139174523129</v>
+        <v>0.00628394576312715</v>
       </c>
       <c r="I2011">
-        <v>0.2628847922430135</v>
+        <v>0.3078166262571589</v>
       </c>
       <c r="J2011">
-        <v>0.4570506925232892</v>
+        <v>0.459507667597366</v>
       </c>
       <c r="K2011">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="L2011">
-        <v>4.29</v>
+        <v>5.25</v>
       </c>
       <c r="M2011">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2011">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2011">
         <v>1</v>
       </c>
       <c r="P2011" t="s">
-        <v>270</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2012" spans="1:16">
       <c r="A2012" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2012" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C2012">
-        <v>3.558329027691858</v>
+        <v>2.997405526308626</v>
       </c>
       <c r="D2012" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2012">
-        <v>3.204309673121749</v>
+        <v>3.254860825476872</v>
       </c>
       <c r="F2012">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2012">
-        <v>0.006821670972308143</v>
+        <v>0.005602594473691374</v>
       </c>
       <c r="H2012">
-        <v>0.006275690326878251</v>
+        <v>0.006125139174523129</v>
       </c>
       <c r="I2012">
-        <v>0.3540193545701094</v>
+        <v>0.2574552991682468</v>
       </c>
       <c r="J2012">
         <v>0.4570506925232892</v>
       </c>
       <c r="K2012">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="L2012">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M2012">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2012">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2012">
         <v>1</v>
       </c>
       <c r="P2012" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2013" spans="1:16">
       <c r="A2013" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2013" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C2013">
-        <v>3.513207368411501</v>
+        <v>3.000258060934791</v>
       </c>
       <c r="D2013" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2013">
-        <v>3.204309673121749</v>
+        <v>3.254860825476872</v>
       </c>
       <c r="F2013">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2013">
-        <v>0.006986792631588498</v>
+        <v>0.00555974193906521</v>
       </c>
       <c r="H2013">
-        <v>0.006275690326878251</v>
+        <v>0.006125139174523129</v>
       </c>
       <c r="I2013">
-        <v>0.3088976952897524</v>
+        <v>0.2546027645420819</v>
       </c>
       <c r="J2013">
         <v>0.4570506925232892</v>
       </c>
       <c r="K2013">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="L2013">
-        <v>5.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2013">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2013">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2013">
         <v>1</v>
       </c>
       <c r="P2013" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2014" spans="1:16">
       <c r="A2014" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2014" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C2014">
-        <v>3.016096584510787</v>
+        <v>2.997681102486188</v>
       </c>
       <c r="D2014" t="s">
         <v>436</v>
       </c>
       <c r="E2014">
-        <v>3.266492268812767</v>
+        <v>3.254860825476872</v>
       </c>
       <c r="F2014">
         <v>1</v>
       </c>
       <c r="G2014">
-        <v>0.005563903415489213</v>
+        <v>0.005502318897513812</v>
       </c>
       <c r="H2014">
-        <v>0.006113507731187234</v>
+        <v>0.006125139174523129</v>
       </c>
       <c r="I2014">
-        <v>0.2503956843019792</v>
+        <v>0.2571797229906849</v>
       </c>
       <c r="J2014">
-        <v>0.4533464112061254</v>
+        <v>0.4570506925232892</v>
       </c>
       <c r="K2014">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="L2014">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="M2014">
         <v>3.14</v>
@@ -102856,45 +102856,45 @@
         <v>1</v>
       </c>
       <c r="P2014" t="s">
-        <v>591</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2015" spans="1:16">
       <c r="A2015" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2015" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="C2015">
-        <v>3.010630048622849</v>
+        <v>2.991976033233859</v>
       </c>
       <c r="D2015" t="s">
         <v>436</v>
       </c>
       <c r="E2015">
-        <v>3.266492268812767</v>
+        <v>3.254860825476872</v>
       </c>
       <c r="F2015">
         <v>1</v>
       </c>
       <c r="G2015">
-        <v>0.005549369951377152</v>
+        <v>0.00558802396676614</v>
       </c>
       <c r="H2015">
-        <v>0.006113507731187234</v>
+        <v>0.006125139174523129</v>
       </c>
       <c r="I2015">
-        <v>0.2558622201899174</v>
+        <v>0.2628847922430135</v>
       </c>
       <c r="J2015">
-        <v>0.4533464112061254</v>
+        <v>0.4570506925232892</v>
       </c>
       <c r="K2015">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="L2015">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="M2015">
         <v>3.14</v>
@@ -102906,151 +102906,151 @@
         <v>1</v>
       </c>
       <c r="P2015" t="s">
-        <v>591</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2016" spans="1:16">
       <c r="A2016" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2016" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C2016">
-        <v>3.007830833295216</v>
+        <v>3.558329027691858</v>
       </c>
       <c r="D2016" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2016">
-        <v>3.266492268812767</v>
+        <v>3.204309673121749</v>
       </c>
       <c r="F2016">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2016">
-        <v>0.005492169166704784</v>
+        <v>0.006821670972308143</v>
       </c>
       <c r="H2016">
-        <v>0.006113507731187234</v>
+        <v>0.006275690326878251</v>
       </c>
       <c r="I2016">
-        <v>0.2586614355175505</v>
+        <v>0.3540193545701094</v>
       </c>
       <c r="J2016">
-        <v>0.4533464112061254</v>
+        <v>0.4570506925232892</v>
       </c>
       <c r="K2016">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="L2016">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2016">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2016">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2016">
         <v>1</v>
       </c>
       <c r="P2016" t="s">
-        <v>591</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2017" spans="1:16">
       <c r="A2017" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2017" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C2017">
-        <v>3.002496192174604</v>
+        <v>3.513207368411501</v>
       </c>
       <c r="D2017" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2017">
-        <v>3.266492268812767</v>
+        <v>3.204309673121749</v>
       </c>
       <c r="F2017">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2017">
-        <v>0.005577503807825396</v>
+        <v>0.006986792631588498</v>
       </c>
       <c r="H2017">
-        <v>0.006113507731187234</v>
+        <v>0.006275690326878251</v>
       </c>
       <c r="I2017">
-        <v>0.2639960766381626</v>
+        <v>0.3088976952897524</v>
       </c>
       <c r="J2017">
-        <v>0.4533464112061254</v>
+        <v>0.4570506925232892</v>
       </c>
       <c r="K2017">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="L2017">
-        <v>4.29</v>
+        <v>5.25</v>
       </c>
       <c r="M2017">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2017">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2017">
         <v>1</v>
       </c>
       <c r="P2017" t="s">
-        <v>591</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2018" spans="1:16">
       <c r="A2018" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2018" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C2018">
-        <v>3.571553311994133</v>
+        <v>3.016096584510787</v>
       </c>
       <c r="D2018" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2018">
-        <v>3.216756058347419</v>
+        <v>3.266492268812767</v>
       </c>
       <c r="F2018">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2018">
-        <v>0.006808446688005869</v>
+        <v>0.005563903415489213</v>
       </c>
       <c r="H2018">
-        <v>0.006263243941652582</v>
+        <v>0.006113507731187234</v>
       </c>
       <c r="I2018">
-        <v>0.3547972536467139</v>
+        <v>0.2503956843019792</v>
       </c>
       <c r="J2018">
         <v>0.4533464112061254</v>
       </c>
       <c r="K2018">
-        <v>3.57</v>
+        <v>2.81</v>
       </c>
       <c r="L2018">
-        <v>5.19</v>
+        <v>4.29</v>
       </c>
       <c r="M2018">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2018">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2018">
         <v>1</v>
@@ -103061,46 +103061,46 @@
     </row>
     <row r="2019" spans="1:16">
       <c r="A2019" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2019" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C2019">
-        <v>3.527283637416724</v>
+        <v>3.010630048622849</v>
       </c>
       <c r="D2019" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2019">
-        <v>3.216756058347419</v>
+        <v>3.266492268812767</v>
       </c>
       <c r="F2019">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2019">
-        <v>0.006972716362583276</v>
+        <v>0.005549369951377152</v>
       </c>
       <c r="H2019">
-        <v>0.006263243941652582</v>
+        <v>0.006113507731187234</v>
       </c>
       <c r="I2019">
-        <v>0.3105275790693049</v>
+        <v>0.2558622201899174</v>
       </c>
       <c r="J2019">
         <v>0.4533464112061254</v>
       </c>
       <c r="K2019">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="L2019">
-        <v>5.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2019">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2019">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2019">
         <v>1</v>
@@ -103111,40 +103111,40 @@
     </row>
     <row r="2020" spans="1:16">
       <c r="A2020" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2020" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2020">
-        <v>3.018674810798719</v>
+        <v>3.007830833295216</v>
       </c>
       <c r="D2020" t="s">
         <v>436</v>
       </c>
       <c r="E2020">
-        <v>3.275513894967134</v>
+        <v>3.266492268812767</v>
       </c>
       <c r="F2020">
         <v>1</v>
       </c>
       <c r="G2020">
-        <v>0.005541325189201282</v>
+        <v>0.005492169166704784</v>
       </c>
       <c r="H2020">
-        <v>0.006104486105032866</v>
+        <v>0.006113507731187234</v>
       </c>
       <c r="I2020">
-        <v>0.2568390841684156</v>
+        <v>0.2586614355175505</v>
       </c>
       <c r="J2020">
-        <v>0.4504732818576006</v>
+        <v>0.4533464112061254</v>
       </c>
       <c r="K2020">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="L2020">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="M2020">
         <v>3.14</v>
@@ -103156,45 +103156,45 @@
         <v>1</v>
       </c>
       <c r="P2020" t="s">
-        <v>273</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2021" spans="1:16">
       <c r="A2021" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2021" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C2021">
-        <v>3.015703207710174</v>
+        <v>3.002496192174604</v>
       </c>
       <c r="D2021" t="s">
         <v>436</v>
       </c>
       <c r="E2021">
-        <v>3.275513894967134</v>
+        <v>3.266492268812767</v>
       </c>
       <c r="F2021">
         <v>1</v>
       </c>
       <c r="G2021">
-        <v>0.005484296792289825</v>
+        <v>0.005577503807825396</v>
       </c>
       <c r="H2021">
-        <v>0.006104486105032866</v>
+        <v>0.006113507731187234</v>
       </c>
       <c r="I2021">
-        <v>0.2598106872569601</v>
+        <v>0.2639960766381626</v>
       </c>
       <c r="J2021">
-        <v>0.4504732818576006</v>
+        <v>0.4533464112061254</v>
       </c>
       <c r="K2021">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="L2021">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="M2021">
         <v>3.14</v>
@@ -103206,95 +103206,95 @@
         <v>1</v>
       </c>
       <c r="P2021" t="s">
-        <v>273</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2022" spans="1:16">
       <c r="A2022" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2022" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C2022">
-        <v>3.010655879524414</v>
+        <v>3.571553311994133</v>
       </c>
       <c r="D2022" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2022">
-        <v>3.275513894967134</v>
+        <v>3.216756058347419</v>
       </c>
       <c r="F2022">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2022">
-        <v>0.005569344120475586</v>
+        <v>0.006808446688005869</v>
       </c>
       <c r="H2022">
-        <v>0.006104486105032866</v>
+        <v>0.006263243941652582</v>
       </c>
       <c r="I2022">
-        <v>0.2648580154427198</v>
+        <v>0.3547972536467139</v>
       </c>
       <c r="J2022">
-        <v>0.4504732818576006</v>
+        <v>0.4533464112061254</v>
       </c>
       <c r="K2022">
-        <v>2.84</v>
+        <v>3.57</v>
       </c>
       <c r="L2022">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="M2022">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2022">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2022">
         <v>1</v>
       </c>
       <c r="P2022" t="s">
-        <v>273</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2023" spans="1:16">
       <c r="A2023" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2023" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C2023">
-        <v>3.581810383768366</v>
+        <v>3.527283637416724</v>
       </c>
       <c r="D2023" t="s">
         <v>456</v>
       </c>
       <c r="E2023">
-        <v>3.226409772958462</v>
+        <v>3.216756058347419</v>
       </c>
       <c r="F2023">
         <v>-1</v>
       </c>
       <c r="G2023">
-        <v>0.006798189616231635</v>
+        <v>0.006972716362583276</v>
       </c>
       <c r="H2023">
-        <v>0.006253590227041538</v>
+        <v>0.006263243941652582</v>
       </c>
       <c r="I2023">
-        <v>0.3554006108099044</v>
+        <v>0.3105275790693049</v>
       </c>
       <c r="J2023">
-        <v>0.4504732818576006</v>
+        <v>0.4533464112061254</v>
       </c>
       <c r="K2023">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="L2023">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="M2023">
         <v>3.36</v>
@@ -103306,51 +103306,51 @@
         <v>1</v>
       </c>
       <c r="P2023" t="s">
-        <v>273</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2024" spans="1:16">
       <c r="A2024" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2024" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C2024">
-        <v>3.538201528941118</v>
+        <v>3.018674810798719</v>
       </c>
       <c r="D2024" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2024">
-        <v>3.226409772958462</v>
+        <v>3.275513894967134</v>
       </c>
       <c r="F2024">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2024">
-        <v>0.006961798471058883</v>
+        <v>0.005541325189201282</v>
       </c>
       <c r="H2024">
-        <v>0.006253590227041538</v>
+        <v>0.006104486105032866</v>
       </c>
       <c r="I2024">
-        <v>0.3117917559826555</v>
+        <v>0.2568390841684156</v>
       </c>
       <c r="J2024">
         <v>0.4504732818576006</v>
       </c>
       <c r="K2024">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="L2024">
-        <v>5.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2024">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2024">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2024">
         <v>1</v>
@@ -103361,40 +103361,40 @@
     </row>
     <row r="2025" spans="1:16">
       <c r="A2025" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2025" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2025">
-        <v>3.028785702645333</v>
+        <v>3.015703207710174</v>
       </c>
       <c r="D2025" t="s">
         <v>436</v>
       </c>
       <c r="E2025">
-        <v>3.286852537966552</v>
+        <v>3.275513894967134</v>
       </c>
       <c r="F2025">
         <v>1</v>
       </c>
       <c r="G2025">
-        <v>0.005531214297354667</v>
+        <v>0.005484296792289825</v>
       </c>
       <c r="H2025">
-        <v>0.006093147462033449</v>
+        <v>0.006104486105032866</v>
       </c>
       <c r="I2025">
-        <v>0.2580668353212188</v>
+        <v>0.2598106872569601</v>
       </c>
       <c r="J2025">
-        <v>0.4468622490552383</v>
+        <v>0.4504732818576006</v>
       </c>
       <c r="K2025">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="L2025">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="M2025">
         <v>3.14</v>
@@ -103406,45 +103406,45 @@
         <v>1</v>
       </c>
       <c r="P2025" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2026" spans="1:16">
       <c r="A2026" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2026" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C2026">
-        <v>3.025597437588647</v>
+        <v>3.010655879524414</v>
       </c>
       <c r="D2026" t="s">
         <v>436</v>
       </c>
       <c r="E2026">
-        <v>3.286852537966552</v>
+        <v>3.275513894967134</v>
       </c>
       <c r="F2026">
         <v>1</v>
       </c>
       <c r="G2026">
-        <v>0.005474402562411352</v>
+        <v>0.005569344120475586</v>
       </c>
       <c r="H2026">
-        <v>0.006093147462033449</v>
+        <v>0.006104486105032866</v>
       </c>
       <c r="I2026">
-        <v>0.2612551003779049</v>
+        <v>0.2648580154427198</v>
       </c>
       <c r="J2026">
-        <v>0.4468622490552383</v>
+        <v>0.4504732818576006</v>
       </c>
       <c r="K2026">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="L2026">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="M2026">
         <v>3.14</v>
@@ -103456,95 +103456,95 @@
         <v>1</v>
       </c>
       <c r="P2026" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2027" spans="1:16">
       <c r="A2027" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2027" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C2027">
-        <v>3.020911212683123</v>
+        <v>3.581810383768366</v>
       </c>
       <c r="D2027" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2027">
-        <v>3.286852537966552</v>
+        <v>3.226409772958462</v>
       </c>
       <c r="F2027">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2027">
-        <v>0.005559088787316877</v>
+        <v>0.006798189616231635</v>
       </c>
       <c r="H2027">
-        <v>0.006093147462033449</v>
+        <v>0.006253590227041538</v>
       </c>
       <c r="I2027">
-        <v>0.2659413252834284</v>
+        <v>0.3554006108099044</v>
       </c>
       <c r="J2027">
-        <v>0.4468622490552383</v>
+        <v>0.4504732818576006</v>
       </c>
       <c r="K2027">
-        <v>2.84</v>
+        <v>3.57</v>
       </c>
       <c r="L2027">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="M2027">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2027">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2027">
         <v>1</v>
       </c>
       <c r="P2027" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2028" spans="1:16">
       <c r="A2028" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2028" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C2028">
-        <v>3.5947017708728</v>
+        <v>3.538201528941118</v>
       </c>
       <c r="D2028" t="s">
         <v>456</v>
       </c>
       <c r="E2028">
-        <v>3.238542843174399</v>
+        <v>3.226409772958462</v>
       </c>
       <c r="F2028">
         <v>-1</v>
       </c>
       <c r="G2028">
-        <v>0.006785298229127201</v>
+        <v>0.006961798471058883</v>
       </c>
       <c r="H2028">
-        <v>0.006241457156825601</v>
+        <v>0.006253590227041538</v>
       </c>
       <c r="I2028">
-        <v>0.3561589276984005</v>
+        <v>0.3117917559826555</v>
       </c>
       <c r="J2028">
-        <v>0.4468622490552383</v>
+        <v>0.4504732818576006</v>
       </c>
       <c r="K2028">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="L2028">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="M2028">
         <v>3.36</v>
@@ -103556,51 +103556,51 @@
         <v>1</v>
       </c>
       <c r="P2028" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2029" spans="1:16">
       <c r="A2029" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2029" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C2029">
-        <v>3.551923453590095</v>
+        <v>3.028785702645333</v>
       </c>
       <c r="D2029" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2029">
-        <v>3.238542843174399</v>
+        <v>3.286852537966552</v>
       </c>
       <c r="F2029">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2029">
-        <v>0.006948076546409905</v>
+        <v>0.005531214297354667</v>
       </c>
       <c r="H2029">
-        <v>0.006241457156825601</v>
+        <v>0.006093147462033449</v>
       </c>
       <c r="I2029">
-        <v>0.3133806104156953</v>
+        <v>0.2580668353212188</v>
       </c>
       <c r="J2029">
         <v>0.4468622490552383</v>
       </c>
       <c r="K2029">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="L2029">
-        <v>5.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2029">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2029">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2029">
         <v>1</v>
@@ -103611,34 +103611,34 @@
     </row>
     <row r="2030" spans="1:16">
       <c r="A2030" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2030" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C2030">
-        <v>3.036494228717384</v>
+        <v>3.025597437588647</v>
       </c>
       <c r="D2030" t="s">
         <v>436</v>
       </c>
       <c r="E2030">
-        <v>3.299340101522843</v>
+        <v>3.286852537966552</v>
       </c>
       <c r="F2030">
         <v>1</v>
       </c>
       <c r="G2030">
-        <v>0.005463505771282616</v>
+        <v>0.005474402562411352</v>
       </c>
       <c r="H2030">
-        <v>0.006080659898477159</v>
+        <v>0.006093147462033449</v>
       </c>
       <c r="I2030">
-        <v>0.2628458728054581</v>
+        <v>0.2612551003779049</v>
       </c>
       <c r="J2030">
-        <v>0.442885317986356</v>
+        <v>0.4468622490552383</v>
       </c>
       <c r="K2030">
         <v>2.74</v>
@@ -103656,95 +103656,95 @@
         <v>1</v>
       </c>
       <c r="P2030" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2031" spans="1:16">
       <c r="A2031" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2031" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C2031">
-        <v>3.608899414788709</v>
+        <v>3.020911212683123</v>
       </c>
       <c r="D2031" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2031">
-        <v>3.251905331565844</v>
+        <v>3.286852537966552</v>
       </c>
       <c r="F2031">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2031">
-        <v>0.006771100585211291</v>
+        <v>0.005559088787316877</v>
       </c>
       <c r="H2031">
-        <v>0.006228094668434157</v>
+        <v>0.006093147462033449</v>
       </c>
       <c r="I2031">
-        <v>0.3569940832228653</v>
+        <v>0.2659413252834284</v>
       </c>
       <c r="J2031">
-        <v>0.442885317986356</v>
+        <v>0.4468622490552383</v>
       </c>
       <c r="K2031">
-        <v>3.57</v>
+        <v>2.84</v>
       </c>
       <c r="L2031">
-        <v>5.19</v>
+        <v>4.29</v>
       </c>
       <c r="M2031">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2031">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2031">
         <v>1</v>
       </c>
       <c r="P2031" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2032" spans="1:16">
       <c r="A2032" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2032" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2032">
-        <v>3.567035791651847</v>
+        <v>3.5947017708728</v>
       </c>
       <c r="D2032" t="s">
         <v>456</v>
       </c>
       <c r="E2032">
-        <v>3.251905331565844</v>
+        <v>3.238542843174399</v>
       </c>
       <c r="F2032">
         <v>-1</v>
       </c>
       <c r="G2032">
-        <v>0.006932964208348154</v>
+        <v>0.006785298229127201</v>
       </c>
       <c r="H2032">
-        <v>0.006228094668434157</v>
+        <v>0.006241457156825601</v>
       </c>
       <c r="I2032">
-        <v>0.3151304600860034</v>
+        <v>0.3561589276984005</v>
       </c>
       <c r="J2032">
-        <v>0.442885317986356</v>
+        <v>0.4468622490552383</v>
       </c>
       <c r="K2032">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2032">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2032">
         <v>3.36</v>
@@ -103756,145 +103756,145 @@
         <v>1</v>
       </c>
       <c r="P2032" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2033" spans="1:16">
       <c r="A2033" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2033" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C2033">
-        <v>3.052236224586666</v>
+        <v>3.551923453590095</v>
       </c>
       <c r="D2033" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2033">
-        <v>3.317380198978881</v>
+        <v>3.238542843174399</v>
       </c>
       <c r="F2033">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2033">
-        <v>0.005447763775413334</v>
+        <v>0.006948076546409905</v>
       </c>
       <c r="H2033">
-        <v>0.006062619801021119</v>
+        <v>0.006241457156825601</v>
       </c>
       <c r="I2033">
-        <v>0.265143974392215</v>
+        <v>0.3133806104156953</v>
       </c>
       <c r="J2033">
-        <v>0.4371400640194647</v>
+        <v>0.4468622490552383</v>
       </c>
       <c r="K2033">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="L2033">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="M2033">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2033">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2033">
         <v>1</v>
       </c>
       <c r="P2033" t="s">
-        <v>592</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2034" spans="1:16">
       <c r="A2034" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2034" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C2034">
-        <v>3.629409971450511</v>
+        <v>3.036494228717384</v>
       </c>
       <c r="D2034" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2034">
-        <v>3.271209384894599</v>
+        <v>3.299340101522843</v>
       </c>
       <c r="F2034">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2034">
-        <v>0.006750590028549489</v>
+        <v>0.005463505771282616</v>
       </c>
       <c r="H2034">
-        <v>0.006208790615105402</v>
+        <v>0.006080659898477159</v>
       </c>
       <c r="I2034">
-        <v>0.3582005865559128</v>
+        <v>0.2628458728054581</v>
       </c>
       <c r="J2034">
-        <v>0.4371400640194647</v>
+        <v>0.442885317986356</v>
       </c>
       <c r="K2034">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2034">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2034">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2034">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2034">
         <v>1</v>
       </c>
       <c r="P2034" t="s">
-        <v>592</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2035" spans="1:16">
       <c r="A2035" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2035" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2035">
-        <v>3.588867756726034</v>
+        <v>3.608899414788709</v>
       </c>
       <c r="D2035" t="s">
         <v>456</v>
       </c>
       <c r="E2035">
-        <v>3.271209384894599</v>
+        <v>3.251905331565844</v>
       </c>
       <c r="F2035">
         <v>-1</v>
       </c>
       <c r="G2035">
-        <v>0.006911132243273966</v>
+        <v>0.006771100585211291</v>
       </c>
       <c r="H2035">
-        <v>0.006208790615105402</v>
+        <v>0.006228094668434157</v>
       </c>
       <c r="I2035">
-        <v>0.3176583718314356</v>
+        <v>0.3569940832228653</v>
       </c>
       <c r="J2035">
-        <v>0.4371400640194647</v>
+        <v>0.442885317986356</v>
       </c>
       <c r="K2035">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2035">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2035">
         <v>3.36</v>
@@ -103906,145 +103906,145 @@
         <v>1</v>
       </c>
       <c r="P2035" t="s">
-        <v>592</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2036" spans="1:16">
       <c r="A2036" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2036" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C2036">
-        <v>3.062565775248474</v>
+        <v>3.567035791651847</v>
       </c>
       <c r="D2036" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2036">
-        <v>3.329217713240952</v>
+        <v>3.251905331565844</v>
       </c>
       <c r="F2036">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2036">
-        <v>0.005437434224751526</v>
+        <v>0.006932964208348154</v>
       </c>
       <c r="H2036">
-        <v>0.006050782286759049</v>
+        <v>0.006228094668434157</v>
       </c>
       <c r="I2036">
-        <v>0.2666519379924779</v>
+        <v>0.3151304600860034</v>
       </c>
       <c r="J2036">
-        <v>0.4333701550188053</v>
+        <v>0.442885317986356</v>
       </c>
       <c r="K2036">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="L2036">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="M2036">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2036">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2036">
         <v>1</v>
       </c>
       <c r="P2036" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2037" spans="1:16">
       <c r="A2037" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2037" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C2037">
-        <v>3.642868546582866</v>
+        <v>3.052236224586666</v>
       </c>
       <c r="D2037" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2037">
-        <v>3.283876279136814</v>
+        <v>3.317380198978881</v>
       </c>
       <c r="F2037">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2037">
-        <v>0.006737131453417135</v>
+        <v>0.005447763775413334</v>
       </c>
       <c r="H2037">
-        <v>0.006196123720863186</v>
+        <v>0.006062619801021119</v>
       </c>
       <c r="I2037">
-        <v>0.3589922674460513</v>
+        <v>0.265143974392215</v>
       </c>
       <c r="J2037">
-        <v>0.4333701550188053</v>
+        <v>0.4371400640194647</v>
       </c>
       <c r="K2037">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2037">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2037">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2037">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2037">
         <v>1</v>
       </c>
       <c r="P2037" t="s">
-        <v>271</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2038" spans="1:16">
       <c r="A2038" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2038" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2038">
-        <v>3.60319341092854</v>
+        <v>3.629409971450511</v>
       </c>
       <c r="D2038" t="s">
         <v>456</v>
       </c>
       <c r="E2038">
-        <v>3.283876279136814</v>
+        <v>3.271209384894599</v>
       </c>
       <c r="F2038">
         <v>-1</v>
       </c>
       <c r="G2038">
-        <v>0.00689680658907146</v>
+        <v>0.006750590028549489</v>
       </c>
       <c r="H2038">
-        <v>0.006196123720863186</v>
+        <v>0.006208790615105402</v>
       </c>
       <c r="I2038">
-        <v>0.3193171317917258</v>
+        <v>0.3582005865559128</v>
       </c>
       <c r="J2038">
-        <v>0.4333701550188053</v>
+        <v>0.4371400640194647</v>
       </c>
       <c r="K2038">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2038">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2038">
         <v>3.36</v>
@@ -104056,145 +104056,145 @@
         <v>1</v>
       </c>
       <c r="P2038" t="s">
-        <v>271</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2039" spans="1:16">
       <c r="A2039" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2039" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C2039">
-        <v>3.07490254446135</v>
+        <v>3.588867756726034</v>
       </c>
       <c r="D2039" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E2039">
-        <v>3.343355470660088</v>
+        <v>3.271209384894599</v>
       </c>
       <c r="F2039">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2039">
-        <v>0.00542509745553865</v>
+        <v>0.006911132243273966</v>
       </c>
       <c r="H2039">
-        <v>0.006036644529339913</v>
+        <v>0.006208790615105402</v>
       </c>
       <c r="I2039">
-        <v>0.2684529261987381</v>
+        <v>0.3176583718314356</v>
       </c>
       <c r="J2039">
-        <v>0.428867684503157</v>
+        <v>0.4371400640194647</v>
       </c>
       <c r="K2039">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="L2039">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="M2039">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2039">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2039">
         <v>1</v>
       </c>
       <c r="P2039" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2040" spans="1:16">
       <c r="A2040" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2040" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C2040">
-        <v>3.65894236632373</v>
+        <v>3.062565775248474</v>
       </c>
       <c r="D2040" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2040">
-        <v>3.299004580069393</v>
+        <v>3.329217713240952</v>
       </c>
       <c r="F2040">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2040">
-        <v>0.006721057633676271</v>
+        <v>0.005437434224751526</v>
       </c>
       <c r="H2040">
-        <v>0.006180995419930608</v>
+        <v>0.006050782286759049</v>
       </c>
       <c r="I2040">
-        <v>0.3599377862543376</v>
+        <v>0.2666519379924779</v>
       </c>
       <c r="J2040">
-        <v>0.428867684503157</v>
+        <v>0.4333701550188053</v>
       </c>
       <c r="K2040">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2040">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2040">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2040">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2040">
         <v>1</v>
       </c>
       <c r="P2040" t="s">
-        <v>593</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2041" spans="1:16">
       <c r="A2041" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2041" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2041">
-        <v>3.620302798888003</v>
+        <v>3.642868546582866</v>
       </c>
       <c r="D2041" t="s">
         <v>456</v>
       </c>
       <c r="E2041">
-        <v>3.299004580069393</v>
+        <v>3.283876279136814</v>
       </c>
       <c r="F2041">
         <v>-1</v>
       </c>
       <c r="G2041">
-        <v>0.006879697201111997</v>
+        <v>0.006737131453417135</v>
       </c>
       <c r="H2041">
-        <v>0.006180995419930608</v>
+        <v>0.006196123720863186</v>
       </c>
       <c r="I2041">
-        <v>0.3212982188186109</v>
+        <v>0.3589922674460513</v>
       </c>
       <c r="J2041">
-        <v>0.428867684503157</v>
+        <v>0.4333701550188053</v>
       </c>
       <c r="K2041">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2041">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2041">
         <v>3.36</v>
@@ -104206,45 +104206,45 @@
         <v>1</v>
       </c>
       <c r="P2041" t="s">
-        <v>593</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2042" spans="1:16">
       <c r="A2042" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2042" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C2042">
-        <v>3.67507574915134</v>
+        <v>3.60319341092854</v>
       </c>
       <c r="D2042" t="s">
         <v>456</v>
       </c>
       <c r="E2042">
-        <v>3.314188940377731</v>
+        <v>3.283876279136814</v>
       </c>
       <c r="F2042">
         <v>-1</v>
       </c>
       <c r="G2042">
-        <v>0.006704924250848661</v>
+        <v>0.00689680658907146</v>
       </c>
       <c r="H2042">
-        <v>0.00616581105962227</v>
+        <v>0.006196123720863186</v>
       </c>
       <c r="I2042">
-        <v>0.3608868087736088</v>
+        <v>0.3193171317917258</v>
       </c>
       <c r="J2042">
-        <v>0.4243485296494848</v>
+        <v>0.4333701550188053</v>
       </c>
       <c r="K2042">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="L2042">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="M2042">
         <v>3.36</v>
@@ -104256,89 +104256,89 @@
         <v>1</v>
       </c>
       <c r="P2042" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2043" spans="1:16">
       <c r="A2043" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2043" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C2043">
-        <v>3.637475587331958</v>
+        <v>3.07490254446135</v>
       </c>
       <c r="D2043" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E2043">
-        <v>3.314188940377731</v>
+        <v>3.343355470660088</v>
       </c>
       <c r="F2043">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2043">
-        <v>0.006862524412668043</v>
+        <v>0.00542509745553865</v>
       </c>
       <c r="H2043">
-        <v>0.00616581105962227</v>
+        <v>0.006036644529339913</v>
       </c>
       <c r="I2043">
-        <v>0.3232866469542266</v>
+        <v>0.2684529261987381</v>
       </c>
       <c r="J2043">
-        <v>0.4243485296494848</v>
+        <v>0.428867684503157</v>
       </c>
       <c r="K2043">
-        <v>3.8</v>
+        <v>2.74</v>
       </c>
       <c r="L2043">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="M2043">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2043">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2043">
         <v>1</v>
       </c>
       <c r="P2043" t="s">
-        <v>269</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2044" spans="1:16">
       <c r="A2044" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2044" t="s">
         <v>266</v>
       </c>
       <c r="C2044">
-        <v>3.690644898610331</v>
+        <v>3.65894236632373</v>
       </c>
       <c r="D2044" t="s">
         <v>456</v>
       </c>
       <c r="E2044">
-        <v>3.328842257515606</v>
+        <v>3.299004580069393</v>
       </c>
       <c r="F2044">
         <v>-1</v>
       </c>
       <c r="G2044">
-        <v>0.00668935510138967</v>
+        <v>0.006721057633676271</v>
       </c>
       <c r="H2044">
-        <v>0.006151157742484395</v>
+        <v>0.006180995419930608</v>
       </c>
       <c r="I2044">
-        <v>0.3618026410947253</v>
+        <v>0.3599377862543376</v>
       </c>
       <c r="J2044">
-        <v>0.4199874233584508</v>
+        <v>0.428867684503157</v>
       </c>
       <c r="K2044">
         <v>3.57</v>
@@ -104356,39 +104356,39 @@
         <v>1</v>
       </c>
       <c r="P2044" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2045" spans="1:16">
       <c r="A2045" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2045" t="s">
         <v>267</v>
       </c>
       <c r="C2045">
-        <v>3.654047791237887</v>
+        <v>3.620302798888003</v>
       </c>
       <c r="D2045" t="s">
         <v>456</v>
       </c>
       <c r="E2045">
-        <v>3.328842257515606</v>
+        <v>3.299004580069393</v>
       </c>
       <c r="F2045">
         <v>-1</v>
       </c>
       <c r="G2045">
-        <v>0.006845952208762113</v>
+        <v>0.006879697201111997</v>
       </c>
       <c r="H2045">
-        <v>0.006151157742484395</v>
+        <v>0.006180995419930608</v>
       </c>
       <c r="I2045">
-        <v>0.3252055337222814</v>
+        <v>0.3212982188186109</v>
       </c>
       <c r="J2045">
-        <v>0.4199874233584508</v>
+        <v>0.428867684503157</v>
       </c>
       <c r="K2045">
         <v>3.8</v>
@@ -104406,7 +104406,7 @@
         <v>1</v>
       </c>
       <c r="P2045" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2046" spans="1:16">
@@ -104417,28 +104417,28 @@
         <v>266</v>
       </c>
       <c r="C2046">
-        <v>3.70107854524594</v>
+        <v>3.67507574915134</v>
       </c>
       <c r="D2046" t="s">
         <v>456</v>
       </c>
       <c r="E2046">
-        <v>3.338662160231472</v>
+        <v>3.314188940377731</v>
       </c>
       <c r="F2046">
         <v>-1</v>
       </c>
       <c r="G2046">
-        <v>0.006678921454754061</v>
+        <v>0.006704924250848661</v>
       </c>
       <c r="H2046">
-        <v>0.006141337839768528</v>
+        <v>0.00616581105962227</v>
       </c>
       <c r="I2046">
-        <v>0.3624163850144675</v>
+        <v>0.3608868087736088</v>
       </c>
       <c r="J2046">
-        <v>0.4170648332644428</v>
+        <v>0.4243485296494848</v>
       </c>
       <c r="K2046">
         <v>3.57</v>
@@ -104456,7 +104456,7 @@
         <v>1</v>
       </c>
       <c r="P2046" t="s">
-        <v>595</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2047" spans="1:16">
@@ -104467,28 +104467,28 @@
         <v>267</v>
       </c>
       <c r="C2047">
-        <v>3.665153633595117</v>
+        <v>3.637475587331958</v>
       </c>
       <c r="D2047" t="s">
         <v>456</v>
       </c>
       <c r="E2047">
-        <v>3.338662160231472</v>
+        <v>3.314188940377731</v>
       </c>
       <c r="F2047">
         <v>-1</v>
       </c>
       <c r="G2047">
-        <v>0.006834846366404882</v>
+        <v>0.006862524412668043</v>
       </c>
       <c r="H2047">
-        <v>0.006141337839768528</v>
+        <v>0.00616581105962227</v>
       </c>
       <c r="I2047">
-        <v>0.326491473363645</v>
+        <v>0.3232866469542266</v>
       </c>
       <c r="J2047">
-        <v>0.4170648332644428</v>
+        <v>0.4243485296494848</v>
       </c>
       <c r="K2047">
         <v>3.8</v>
@@ -104506,7 +104506,7 @@
         <v>1</v>
       </c>
       <c r="P2047" t="s">
-        <v>595</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2048" spans="1:16">
@@ -104517,28 +104517,28 @@
         <v>266</v>
       </c>
       <c r="C2048">
-        <v>3.707160342770936</v>
+        <v>3.690644898610331</v>
       </c>
       <c r="D2048" t="s">
         <v>456</v>
       </c>
       <c r="E2048">
-        <v>3.344386204960881</v>
+        <v>3.328842257515606</v>
       </c>
       <c r="F2048">
         <v>-1</v>
       </c>
       <c r="G2048">
-        <v>0.006672839657229064</v>
+        <v>0.00668935510138967</v>
       </c>
       <c r="H2048">
-        <v>0.006135613795039119</v>
+        <v>0.006151157742484395</v>
       </c>
       <c r="I2048">
-        <v>0.3627741378100549</v>
+        <v>0.3618026410947253</v>
       </c>
       <c r="J2048">
-        <v>0.4153612485235474</v>
+        <v>0.4199874233584508</v>
       </c>
       <c r="K2048">
         <v>3.57</v>
@@ -104556,7 +104556,7 @@
         <v>1</v>
       </c>
       <c r="P2048" t="s">
-        <v>272</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2049" spans="1:16">
@@ -104567,28 +104567,28 @@
         <v>267</v>
       </c>
       <c r="C2049">
-        <v>3.67162725561052</v>
+        <v>3.654047791237887</v>
       </c>
       <c r="D2049" t="s">
         <v>456</v>
       </c>
       <c r="E2049">
-        <v>3.344386204960881</v>
+        <v>3.328842257515606</v>
       </c>
       <c r="F2049">
         <v>-1</v>
       </c>
       <c r="G2049">
-        <v>0.00682837274438948</v>
+        <v>0.006845952208762113</v>
       </c>
       <c r="H2049">
-        <v>0.006135613795039119</v>
+        <v>0.006151157742484395</v>
       </c>
       <c r="I2049">
-        <v>0.327241050649639</v>
+        <v>0.3252055337222814</v>
       </c>
       <c r="J2049">
-        <v>0.4153612485235474</v>
+        <v>0.4199874233584508</v>
       </c>
       <c r="K2049">
         <v>3.8</v>
@@ -104606,7 +104606,7 @@
         <v>1</v>
       </c>
       <c r="P2049" t="s">
-        <v>272</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2050" spans="1:16">
@@ -104617,28 +104617,28 @@
         <v>266</v>
       </c>
       <c r="C2050">
-        <v>3.714769378692448</v>
+        <v>3.70107854524594</v>
       </c>
       <c r="D2050" t="s">
         <v>456</v>
       </c>
       <c r="E2050">
-        <v>3.351547650534069</v>
+        <v>3.338662160231472</v>
       </c>
       <c r="F2050">
         <v>-1</v>
       </c>
       <c r="G2050">
-        <v>0.006665230621307553</v>
+        <v>0.006678921454754061</v>
       </c>
       <c r="H2050">
-        <v>0.006128452349465931</v>
+        <v>0.006141337839768528</v>
       </c>
       <c r="I2050">
-        <v>0.3632217281583792</v>
+        <v>0.3624163850144675</v>
       </c>
       <c r="J2050">
-        <v>0.4132298659124795</v>
+        <v>0.4170648332644428</v>
       </c>
       <c r="K2050">
         <v>3.57</v>
@@ -104656,7 +104656,7 @@
         <v>1</v>
       </c>
       <c r="P2050" t="s">
-        <v>251</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2051" spans="1:16">
@@ -104667,28 +104667,28 @@
         <v>267</v>
       </c>
       <c r="C2051">
-        <v>3.679726509532578</v>
+        <v>3.665153633595117</v>
       </c>
       <c r="D2051" t="s">
         <v>456</v>
       </c>
       <c r="E2051">
-        <v>3.351547650534069</v>
+        <v>3.338662160231472</v>
       </c>
       <c r="F2051">
         <v>-1</v>
       </c>
       <c r="G2051">
-        <v>0.006820273490467422</v>
+        <v>0.006834846366404882</v>
       </c>
       <c r="H2051">
-        <v>0.006128452349465931</v>
+        <v>0.006141337839768528</v>
       </c>
       <c r="I2051">
-        <v>0.3281788589985091</v>
+        <v>0.326491473363645</v>
       </c>
       <c r="J2051">
-        <v>0.4132298659124795</v>
+        <v>0.4170648332644428</v>
       </c>
       <c r="K2051">
         <v>3.8</v>
@@ -104706,7 +104706,7 @@
         <v>1</v>
       </c>
       <c r="P2051" t="s">
-        <v>251</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2052" spans="1:16">
@@ -104717,28 +104717,28 @@
         <v>266</v>
       </c>
       <c r="C2052">
-        <v>3.736478196776529</v>
+        <v>3.707160342770936</v>
       </c>
       <c r="D2052" t="s">
         <v>456</v>
       </c>
       <c r="E2052">
-        <v>3.371979479319086</v>
+        <v>3.344386204960881</v>
       </c>
       <c r="F2052">
         <v>-1</v>
       </c>
       <c r="G2052">
-        <v>0.006643521803223472</v>
+        <v>0.006672839657229064</v>
       </c>
       <c r="H2052">
-        <v>0.006108020520680915</v>
+        <v>0.006135613795039119</v>
       </c>
       <c r="I2052">
-        <v>0.364498717457443</v>
+        <v>0.3627741378100549</v>
       </c>
       <c r="J2052">
-        <v>0.4071489644883673</v>
+        <v>0.4153612485235474</v>
       </c>
       <c r="K2052">
         <v>3.57</v>
@@ -104756,7 +104756,7 @@
         <v>1</v>
       </c>
       <c r="P2052" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2053" spans="1:16">
@@ -104767,28 +104767,28 @@
         <v>267</v>
       </c>
       <c r="C2053">
-        <v>3.702833934944204</v>
+        <v>3.67162725561052</v>
       </c>
       <c r="D2053" t="s">
         <v>456</v>
       </c>
       <c r="E2053">
-        <v>3.371979479319086</v>
+        <v>3.344386204960881</v>
       </c>
       <c r="F2053">
         <v>-1</v>
       </c>
       <c r="G2053">
-        <v>0.006797166065055796</v>
+        <v>0.00682837274438948</v>
       </c>
       <c r="H2053">
-        <v>0.006108020520680915</v>
+        <v>0.006135613795039119</v>
       </c>
       <c r="I2053">
-        <v>0.3308544556251181</v>
+        <v>0.327241050649639</v>
       </c>
       <c r="J2053">
-        <v>0.4071489644883673</v>
+        <v>0.4153612485235474</v>
       </c>
       <c r="K2053">
         <v>3.8</v>
@@ -104806,6 +104806,206 @@
         <v>1</v>
       </c>
       <c r="P2053" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:16">
+      <c r="A2054" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2054" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2054">
+        <v>3.714769378692448</v>
+      </c>
+      <c r="D2054" t="s">
+        <v>456</v>
+      </c>
+      <c r="E2054">
+        <v>3.351547650534069</v>
+      </c>
+      <c r="F2054">
+        <v>-1</v>
+      </c>
+      <c r="G2054">
+        <v>0.006665230621307553</v>
+      </c>
+      <c r="H2054">
+        <v>0.006128452349465931</v>
+      </c>
+      <c r="I2054">
+        <v>0.3632217281583792</v>
+      </c>
+      <c r="J2054">
+        <v>0.4132298659124795</v>
+      </c>
+      <c r="K2054">
+        <v>3.57</v>
+      </c>
+      <c r="L2054">
+        <v>5.19</v>
+      </c>
+      <c r="M2054">
+        <v>3.36</v>
+      </c>
+      <c r="N2054">
+        <v>4.74</v>
+      </c>
+      <c r="O2054">
+        <v>1</v>
+      </c>
+      <c r="P2054" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:16">
+      <c r="A2055" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2055" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2055">
+        <v>3.679726509532578</v>
+      </c>
+      <c r="D2055" t="s">
+        <v>456</v>
+      </c>
+      <c r="E2055">
+        <v>3.351547650534069</v>
+      </c>
+      <c r="F2055">
+        <v>-1</v>
+      </c>
+      <c r="G2055">
+        <v>0.006820273490467422</v>
+      </c>
+      <c r="H2055">
+        <v>0.006128452349465931</v>
+      </c>
+      <c r="I2055">
+        <v>0.3281788589985091</v>
+      </c>
+      <c r="J2055">
+        <v>0.4132298659124795</v>
+      </c>
+      <c r="K2055">
+        <v>3.8</v>
+      </c>
+      <c r="L2055">
+        <v>5.25</v>
+      </c>
+      <c r="M2055">
+        <v>3.36</v>
+      </c>
+      <c r="N2055">
+        <v>4.74</v>
+      </c>
+      <c r="O2055">
+        <v>1</v>
+      </c>
+      <c r="P2055" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:16">
+      <c r="A2056" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2056" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2056">
+        <v>3.736478196776529</v>
+      </c>
+      <c r="D2056" t="s">
+        <v>456</v>
+      </c>
+      <c r="E2056">
+        <v>3.371979479319086</v>
+      </c>
+      <c r="F2056">
+        <v>-1</v>
+      </c>
+      <c r="G2056">
+        <v>0.006643521803223472</v>
+      </c>
+      <c r="H2056">
+        <v>0.006108020520680915</v>
+      </c>
+      <c r="I2056">
+        <v>0.364498717457443</v>
+      </c>
+      <c r="J2056">
+        <v>0.4071489644883673</v>
+      </c>
+      <c r="K2056">
+        <v>3.57</v>
+      </c>
+      <c r="L2056">
+        <v>5.19</v>
+      </c>
+      <c r="M2056">
+        <v>3.36</v>
+      </c>
+      <c r="N2056">
+        <v>4.74</v>
+      </c>
+      <c r="O2056">
+        <v>1</v>
+      </c>
+      <c r="P2056" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:16">
+      <c r="A2057" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2057" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2057">
+        <v>3.702833934944204</v>
+      </c>
+      <c r="D2057" t="s">
+        <v>456</v>
+      </c>
+      <c r="E2057">
+        <v>3.371979479319086</v>
+      </c>
+      <c r="F2057">
+        <v>-1</v>
+      </c>
+      <c r="G2057">
+        <v>0.006797166065055796</v>
+      </c>
+      <c r="H2057">
+        <v>0.006108020520680915</v>
+      </c>
+      <c r="I2057">
+        <v>0.3308544556251181</v>
+      </c>
+      <c r="J2057">
+        <v>0.4071489644883673</v>
+      </c>
+      <c r="K2057">
+        <v>3.8</v>
+      </c>
+      <c r="L2057">
+        <v>5.25</v>
+      </c>
+      <c r="M2057">
+        <v>3.36</v>
+      </c>
+      <c r="N2057">
+        <v>4.74</v>
+      </c>
+      <c r="O2057">
+        <v>1</v>
+      </c>
+      <c r="P2057" t="s">
         <v>252</v>
       </c>
     </row>

--- a/s60_signal/position-00857-601857.xlsx
+++ b/s60_signal/position-00857-601857.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6135" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6132" uniqueCount="604">
   <si>
     <t>trade_time</t>
   </si>
@@ -835,7 +835,7 @@
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2021-08-06</t>
+    <t>2021-08-09</t>
   </si>
   <si>
     <t>2021-07-30</t>
@@ -1396,10 +1396,10 @@
     <t>2021-07-26</t>
   </si>
   <si>
-    <t>2021-08-11</t>
+    <t>2021-08-12</t>
   </si>
   <si>
-    <t>2021-08-09</t>
+    <t>2021-08-11</t>
   </si>
   <si>
     <t>2016-07-22</t>
@@ -2183,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2041"/>
+  <dimension ref="A1:P2040"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -100644,10 +100644,10 @@
         <v>3.482624369676418</v>
       </c>
       <c r="D1970" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1970">
-        <v>3.133058230283687</v>
+        <v>3.0900141373552</v>
       </c>
       <c r="F1970">
         <v>-1</v>
@@ -100656,10 +100656,10 @@
         <v>0.006897375630323582</v>
       </c>
       <c r="H1970">
-        <v>0.006346941769716313</v>
+        <v>0.0061699858626448</v>
       </c>
       <c r="I1970">
-        <v>0.349566139392731</v>
+        <v>0.3926102323212182</v>
       </c>
       <c r="J1970">
         <v>0.4782564790822359</v>
@@ -100671,10 +100671,10 @@
         <v>5.19</v>
       </c>
       <c r="M1970">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="N1970">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="O1970">
         <v>1</v>
@@ -100788,10 +100788,10 @@
         <v>2</v>
       </c>
       <c r="B1973" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="C1973">
-        <v>2.938180039414744</v>
+        <v>2.932459827730785</v>
       </c>
       <c r="D1973" t="s">
         <v>438</v>
@@ -100803,22 +100803,22 @@
         <v>1</v>
       </c>
       <c r="G1973">
-        <v>0.005641819960585256</v>
+        <v>0.005607540172269214</v>
       </c>
       <c r="H1973">
         <v>0.00618461784374567</v>
       </c>
       <c r="I1973">
-        <v>0.2572021168395859</v>
+        <v>0.2629223285235454</v>
       </c>
       <c r="J1973">
         <v>0.4759929438680478</v>
       </c>
       <c r="K1973">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="L1973">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="M1973">
         <v>3.14</v>
@@ -100844,10 +100844,10 @@
         <v>3.49070519039107</v>
       </c>
       <c r="D1974" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1974">
-        <v>3.14066370860336</v>
+        <v>3.097302720744886</v>
       </c>
       <c r="F1974">
         <v>-1</v>
@@ -100856,10 +100856,10 @@
         <v>0.006889294809608931</v>
       </c>
       <c r="H1974">
-        <v>0.00633933629139664</v>
+        <v>0.006162697279255114</v>
       </c>
       <c r="I1974">
-        <v>0.3500414817877098</v>
+        <v>0.3934024696461838</v>
       </c>
       <c r="J1974">
         <v>0.4759929438680478</v>
@@ -100871,10 +100871,10 @@
         <v>5.19</v>
       </c>
       <c r="M1974">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="N1974">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="O1974">
         <v>1</v>
@@ -101138,10 +101138,10 @@
         <v>1</v>
       </c>
       <c r="B1980" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C1980">
-        <v>2.967587342444334</v>
+        <v>2.952921592778069</v>
       </c>
       <c r="D1980" t="s">
         <v>438</v>
@@ -101153,22 +101153,22 @@
         <v>1</v>
       </c>
       <c r="G1980">
-        <v>0.005552412657555666</v>
+        <v>0.005547078407221932</v>
       </c>
       <c r="H1980">
         <v>0.006155045395207505</v>
       </c>
       <c r="I1980">
-        <v>0.2573672623481613</v>
+        <v>0.2720330120144268</v>
       </c>
       <c r="J1980">
         <v>0.466574966626594</v>
       </c>
       <c r="K1980">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="L1980">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="M1980">
         <v>3.14</v>
@@ -101188,10 +101188,10 @@
         <v>2</v>
       </c>
       <c r="B1981" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C1981">
-        <v>2.952921592778069</v>
+        <v>2.964927094780473</v>
       </c>
       <c r="D1981" t="s">
         <v>438</v>
@@ -101203,22 +101203,22 @@
         <v>1</v>
       </c>
       <c r="G1981">
-        <v>0.005547078407221932</v>
+        <v>0.005615072905219527</v>
       </c>
       <c r="H1981">
         <v>0.006155045395207505</v>
       </c>
       <c r="I1981">
-        <v>0.2720330120144268</v>
+        <v>0.2600275100120224</v>
       </c>
       <c r="J1981">
         <v>0.466574966626594</v>
       </c>
       <c r="K1981">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="L1981">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="M1981">
         <v>3.14</v>
@@ -101238,43 +101238,43 @@
         <v>3</v>
       </c>
       <c r="B1982" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C1982">
-        <v>2.964927094780473</v>
+        <v>3.52432736914306</v>
       </c>
       <c r="D1982" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E1982">
-        <v>3.224954604792496</v>
+        <v>3.172308112134645</v>
       </c>
       <c r="F1982">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1982">
-        <v>0.005615072905219527</v>
+        <v>0.006855672630856941</v>
       </c>
       <c r="H1982">
-        <v>0.006155045395207505</v>
+        <v>0.006307691887865356</v>
       </c>
       <c r="I1982">
-        <v>0.2600275100120224</v>
+        <v>0.3520192570084149</v>
       </c>
       <c r="J1982">
         <v>0.466574966626594</v>
       </c>
       <c r="K1982">
-        <v>2.84</v>
+        <v>3.57</v>
       </c>
       <c r="L1982">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="M1982">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1982">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1982">
         <v>1</v>
@@ -101285,63 +101285,63 @@
     </row>
     <row r="1983" spans="1:16">
       <c r="A1983" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1983" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C1983">
-        <v>3.52432736914306</v>
+        <v>2.968719772490877</v>
       </c>
       <c r="D1983" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E1983">
-        <v>3.172308112134645</v>
+        <v>3.238534751951859</v>
       </c>
       <c r="F1983">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1983">
-        <v>0.006855672630856941</v>
+        <v>0.005631280227509123</v>
       </c>
       <c r="H1983">
-        <v>0.006307691887865356</v>
+        <v>0.006141465248048142</v>
       </c>
       <c r="I1983">
-        <v>0.3520192570084149</v>
+        <v>0.2698149794609828</v>
       </c>
       <c r="J1983">
-        <v>0.466574966626594</v>
+        <v>0.4622500789962232</v>
       </c>
       <c r="K1983">
-        <v>3.57</v>
+        <v>2.88</v>
       </c>
       <c r="L1983">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M1983">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1983">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1983">
         <v>1</v>
       </c>
       <c r="P1983" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1984" spans="1:16">
       <c r="A1984" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1984" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C1984">
-        <v>2.968719772490877</v>
+        <v>2.979567281180461</v>
       </c>
       <c r="D1984" t="s">
         <v>438</v>
@@ -101353,22 +101353,22 @@
         <v>1</v>
       </c>
       <c r="G1984">
-        <v>0.005631280227509123</v>
+        <v>0.005540432718819538</v>
       </c>
       <c r="H1984">
         <v>0.006141465248048142</v>
       </c>
       <c r="I1984">
-        <v>0.2698149794609828</v>
+        <v>0.258967470771398</v>
       </c>
       <c r="J1984">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1984">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="L1984">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="M1984">
         <v>3.14</v>
@@ -101385,13 +101385,13 @@
     </row>
     <row r="1985" spans="1:16">
       <c r="A1985" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1985" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C1985">
-        <v>2.979567281180461</v>
+        <v>2.9649447803905</v>
       </c>
       <c r="D1985" t="s">
         <v>438</v>
@@ -101403,22 +101403,22 @@
         <v>1</v>
       </c>
       <c r="G1985">
-        <v>0.005540432718819538</v>
+        <v>0.0055350552196095</v>
       </c>
       <c r="H1985">
         <v>0.006141465248048142</v>
       </c>
       <c r="I1985">
-        <v>0.258967470771398</v>
+        <v>0.2735899715613597</v>
       </c>
       <c r="J1985">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1985">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="L1985">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="M1985">
         <v>3.14</v>
@@ -101435,13 +101435,13 @@
     </row>
     <row r="1986" spans="1:16">
       <c r="A1986" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1986" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C1986">
-        <v>2.9649447803905</v>
+        <v>2.977209775650726</v>
       </c>
       <c r="D1986" t="s">
         <v>438</v>
@@ -101453,22 +101453,22 @@
         <v>1</v>
       </c>
       <c r="G1986">
-        <v>0.0055350552196095</v>
+        <v>0.005602790224349274</v>
       </c>
       <c r="H1986">
         <v>0.006141465248048142</v>
       </c>
       <c r="I1986">
-        <v>0.2735899715613597</v>
+        <v>0.2613249763011334</v>
       </c>
       <c r="J1986">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1986">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="L1986">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="M1986">
         <v>3.14</v>
@@ -101485,46 +101485,46 @@
     </row>
     <row r="1987" spans="1:16">
       <c r="A1987" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1987" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C1987">
-        <v>2.977209775650726</v>
+        <v>3.539767217983484</v>
       </c>
       <c r="D1987" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E1987">
-        <v>3.238534751951859</v>
+        <v>3.18683973457269</v>
       </c>
       <c r="F1987">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1987">
-        <v>0.005602790224349274</v>
+        <v>0.006840232782016517</v>
       </c>
       <c r="H1987">
-        <v>0.006141465248048142</v>
+        <v>0.006293160265427311</v>
       </c>
       <c r="I1987">
-        <v>0.2613249763011334</v>
+        <v>0.3529274834107934</v>
       </c>
       <c r="J1987">
         <v>0.4622500789962232</v>
       </c>
       <c r="K1987">
-        <v>2.84</v>
+        <v>3.57</v>
       </c>
       <c r="L1987">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="M1987">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1987">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1987">
         <v>1</v>
@@ -101535,63 +101535,63 @@
     </row>
     <row r="1988" spans="1:16">
       <c r="A1988" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1988" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C1988">
-        <v>3.539767217983484</v>
+        <v>2.990403147347507</v>
       </c>
       <c r="D1988" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E1988">
-        <v>3.18683973457269</v>
+        <v>3.247145923744271</v>
       </c>
       <c r="F1988">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1988">
-        <v>0.006840232782016517</v>
+        <v>0.005609596852652493</v>
       </c>
       <c r="H1988">
-        <v>0.006293160265427311</v>
+        <v>0.00613285407625573</v>
       </c>
       <c r="I1988">
-        <v>0.3529274834107934</v>
+        <v>0.2567427763967642</v>
       </c>
       <c r="J1988">
-        <v>0.4622500789962232</v>
+        <v>0.459507667597366</v>
       </c>
       <c r="K1988">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="L1988">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M1988">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1988">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1988">
         <v>1</v>
       </c>
       <c r="P1988" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1989" spans="1:16">
       <c r="A1989" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1989" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C1989">
-        <v>2.990403147347507</v>
+        <v>2.987163760755296</v>
       </c>
       <c r="D1989" t="s">
         <v>438</v>
@@ -101603,22 +101603,22 @@
         <v>1</v>
       </c>
       <c r="G1989">
-        <v>0.005609596852652493</v>
+        <v>0.005532836239244704</v>
       </c>
       <c r="H1989">
         <v>0.00613285407625573</v>
       </c>
       <c r="I1989">
-        <v>0.2567427763967642</v>
+        <v>0.2599821629889751</v>
       </c>
       <c r="J1989">
         <v>0.459507667597366</v>
       </c>
       <c r="K1989">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="L1989">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="M1989">
         <v>3.14</v>
@@ -101635,13 +101635,13 @@
     </row>
     <row r="1990" spans="1:16">
       <c r="A1990" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1990" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="C1990">
-        <v>2.987163760755296</v>
+        <v>2.972568684079323</v>
       </c>
       <c r="D1990" t="s">
         <v>438</v>
@@ -101653,22 +101653,22 @@
         <v>1</v>
       </c>
       <c r="G1990">
-        <v>0.005532836239244704</v>
+        <v>0.005527431315920677</v>
       </c>
       <c r="H1990">
         <v>0.00613285407625573</v>
       </c>
       <c r="I1990">
-        <v>0.2599821629889751</v>
+        <v>0.2745772396649482</v>
       </c>
       <c r="J1990">
         <v>0.459507667597366</v>
       </c>
       <c r="K1990">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="L1990">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="M1990">
         <v>3.14</v>
@@ -101685,13 +101685,13 @@
     </row>
     <row r="1991" spans="1:16">
       <c r="A1991" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1991" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="C1991">
-        <v>2.990948990783217</v>
+        <v>2.984998224023481</v>
       </c>
       <c r="D1991" t="s">
         <v>438</v>
@@ -101703,22 +101703,22 @@
         <v>1</v>
       </c>
       <c r="G1991">
-        <v>0.005509051009216784</v>
+        <v>0.00559500177597652</v>
       </c>
       <c r="H1991">
         <v>0.00613285407625573</v>
       </c>
       <c r="I1991">
-        <v>0.2561969329610543</v>
+        <v>0.2621476997207903</v>
       </c>
       <c r="J1991">
         <v>0.459507667597366</v>
       </c>
       <c r="K1991">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="L1991">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="M1991">
         <v>3.14</v>
@@ -101735,46 +101735,46 @@
     </row>
     <row r="1992" spans="1:16">
       <c r="A1992" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1992" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C1992">
-        <v>2.984998224023481</v>
+        <v>3.549557626677404</v>
       </c>
       <c r="D1992" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E1992">
-        <v>3.247145923744271</v>
+        <v>3.19605423687285</v>
       </c>
       <c r="F1992">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1992">
-        <v>0.00559500177597652</v>
+        <v>0.006830442373322598</v>
       </c>
       <c r="H1992">
-        <v>0.00613285407625573</v>
+        <v>0.00628394576312715</v>
       </c>
       <c r="I1992">
-        <v>0.2621476997207903</v>
+        <v>0.3535033898045534</v>
       </c>
       <c r="J1992">
         <v>0.459507667597366</v>
       </c>
       <c r="K1992">
-        <v>2.84</v>
+        <v>3.57</v>
       </c>
       <c r="L1992">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="M1992">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1992">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1992">
         <v>1</v>
@@ -101785,63 +101785,63 @@
     </row>
     <row r="1993" spans="1:16">
       <c r="A1993" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1993" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C1993">
-        <v>3.549557626677404</v>
+        <v>2.997405526308626</v>
       </c>
       <c r="D1993" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E1993">
-        <v>3.19605423687285</v>
+        <v>3.254860825476872</v>
       </c>
       <c r="F1993">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1993">
-        <v>0.006830442373322598</v>
+        <v>0.005602594473691374</v>
       </c>
       <c r="H1993">
-        <v>0.00628394576312715</v>
+        <v>0.006125139174523129</v>
       </c>
       <c r="I1993">
-        <v>0.3535033898045534</v>
+        <v>0.2574552991682468</v>
       </c>
       <c r="J1993">
-        <v>0.459507667597366</v>
+        <v>0.4570506925232892</v>
       </c>
       <c r="K1993">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="L1993">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M1993">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1993">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1993">
         <v>1</v>
       </c>
       <c r="P1993" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1994" spans="1:16">
       <c r="A1994" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1994" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C1994">
-        <v>2.997405526308626</v>
+        <v>2.993969581710489</v>
       </c>
       <c r="D1994" t="s">
         <v>438</v>
@@ -101853,22 +101853,22 @@
         <v>1</v>
       </c>
       <c r="G1994">
-        <v>0.005602594473691374</v>
+        <v>0.005526030418289511</v>
       </c>
       <c r="H1994">
         <v>0.006125139174523129</v>
       </c>
       <c r="I1994">
-        <v>0.2574552991682468</v>
+        <v>0.260891243766384</v>
       </c>
       <c r="J1994">
         <v>0.4570506925232892</v>
       </c>
       <c r="K1994">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="L1994">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="M1994">
         <v>3.14</v>
@@ -101885,13 +101885,13 @@
     </row>
     <row r="1995" spans="1:16">
       <c r="A1995" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1995" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1995">
-        <v>3.000258060934791</v>
+        <v>2.997681102486188</v>
       </c>
       <c r="D1995" t="s">
         <v>438</v>
@@ -101903,22 +101903,22 @@
         <v>1</v>
       </c>
       <c r="G1995">
-        <v>0.00555974193906521</v>
+        <v>0.005502318897513812</v>
       </c>
       <c r="H1995">
         <v>0.006125139174523129</v>
       </c>
       <c r="I1995">
-        <v>0.2546027645420819</v>
+        <v>0.2571797229906849</v>
       </c>
       <c r="J1995">
         <v>0.4570506925232892</v>
       </c>
       <c r="K1995">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="L1995">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="M1995">
         <v>3.14</v>
@@ -101935,13 +101935,13 @@
     </row>
     <row r="1996" spans="1:16">
       <c r="A1996" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1996" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="C1996">
-        <v>2.997681102486188</v>
+        <v>2.991976033233859</v>
       </c>
       <c r="D1996" t="s">
         <v>438</v>
@@ -101953,22 +101953,22 @@
         <v>1</v>
       </c>
       <c r="G1996">
-        <v>0.005502318897513812</v>
+        <v>0.00558802396676614</v>
       </c>
       <c r="H1996">
         <v>0.006125139174523129</v>
       </c>
       <c r="I1996">
-        <v>0.2571797229906849</v>
+        <v>0.2628847922430135</v>
       </c>
       <c r="J1996">
         <v>0.4570506925232892</v>
       </c>
       <c r="K1996">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="L1996">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="M1996">
         <v>3.14</v>
@@ -101985,46 +101985,46 @@
     </row>
     <row r="1997" spans="1:16">
       <c r="A1997" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1997" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C1997">
-        <v>2.991976033233859</v>
+        <v>3.558329027691858</v>
       </c>
       <c r="D1997" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E1997">
-        <v>3.254860825476872</v>
+        <v>3.204309673121749</v>
       </c>
       <c r="F1997">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1997">
-        <v>0.00558802396676614</v>
+        <v>0.006821670972308143</v>
       </c>
       <c r="H1997">
-        <v>0.006125139174523129</v>
+        <v>0.006275690326878251</v>
       </c>
       <c r="I1997">
-        <v>0.2628847922430135</v>
+        <v>0.3540193545701094</v>
       </c>
       <c r="J1997">
         <v>0.4570506925232892</v>
       </c>
       <c r="K1997">
-        <v>2.84</v>
+        <v>3.57</v>
       </c>
       <c r="L1997">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="M1997">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N1997">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1997">
         <v>1</v>
@@ -102035,63 +102035,63 @@
     </row>
     <row r="1998" spans="1:16">
       <c r="A1998" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1998" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C1998">
-        <v>3.558329027691858</v>
+        <v>3.007962728062543</v>
       </c>
       <c r="D1998" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E1998">
-        <v>3.204309673121749</v>
+        <v>3.266492268812767</v>
       </c>
       <c r="F1998">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1998">
-        <v>0.006821670972308143</v>
+        <v>0.005592037271937457</v>
       </c>
       <c r="H1998">
-        <v>0.006275690326878251</v>
+        <v>0.006113507731187234</v>
       </c>
       <c r="I1998">
-        <v>0.3540193545701094</v>
+        <v>0.2585295407502239</v>
       </c>
       <c r="J1998">
-        <v>0.4570506925232892</v>
+        <v>0.4533464112061254</v>
       </c>
       <c r="K1998">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="L1998">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M1998">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N1998">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1998">
         <v>1</v>
       </c>
       <c r="P1998" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1999" spans="1:16">
       <c r="A1999" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1999" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C1999">
-        <v>3.007962728062543</v>
+        <v>3.010630048622849</v>
       </c>
       <c r="D1999" t="s">
         <v>438</v>
@@ -102103,22 +102103,22 @@
         <v>1</v>
       </c>
       <c r="G1999">
-        <v>0.005592037271937457</v>
+        <v>0.005549369951377152</v>
       </c>
       <c r="H1999">
         <v>0.006113507731187234</v>
       </c>
       <c r="I1999">
-        <v>0.2585295407502239</v>
+        <v>0.2558622201899174</v>
       </c>
       <c r="J1999">
         <v>0.4533464112061254</v>
       </c>
       <c r="K1999">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="L1999">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="M1999">
         <v>3.14</v>
@@ -102135,13 +102135,13 @@
     </row>
     <row r="2000" spans="1:16">
       <c r="A2000" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2000" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2000">
-        <v>3.010630048622849</v>
+        <v>3.007830833295216</v>
       </c>
       <c r="D2000" t="s">
         <v>438</v>
@@ -102153,22 +102153,22 @@
         <v>1</v>
       </c>
       <c r="G2000">
-        <v>0.005549369951377152</v>
+        <v>0.005492169166704784</v>
       </c>
       <c r="H2000">
         <v>0.006113507731187234</v>
       </c>
       <c r="I2000">
-        <v>0.2558622201899174</v>
+        <v>0.2586614355175505</v>
       </c>
       <c r="J2000">
         <v>0.4533464112061254</v>
       </c>
       <c r="K2000">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="L2000">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="M2000">
         <v>3.14</v>
@@ -102185,13 +102185,13 @@
     </row>
     <row r="2001" spans="1:16">
       <c r="A2001" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2001" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="C2001">
-        <v>3.007830833295216</v>
+        <v>3.002496192174604</v>
       </c>
       <c r="D2001" t="s">
         <v>438</v>
@@ -102203,22 +102203,22 @@
         <v>1</v>
       </c>
       <c r="G2001">
-        <v>0.005492169166704784</v>
+        <v>0.005577503807825396</v>
       </c>
       <c r="H2001">
         <v>0.006113507731187234</v>
       </c>
       <c r="I2001">
-        <v>0.2586614355175505</v>
+        <v>0.2639960766381626</v>
       </c>
       <c r="J2001">
         <v>0.4533464112061254</v>
       </c>
       <c r="K2001">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="L2001">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="M2001">
         <v>3.14</v>
@@ -102235,46 +102235,46 @@
     </row>
     <row r="2002" spans="1:16">
       <c r="A2002" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2002" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C2002">
-        <v>3.002496192174604</v>
+        <v>3.571553311994133</v>
       </c>
       <c r="D2002" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E2002">
-        <v>3.266492268812767</v>
+        <v>3.216756058347419</v>
       </c>
       <c r="F2002">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2002">
-        <v>0.005577503807825396</v>
+        <v>0.006808446688005869</v>
       </c>
       <c r="H2002">
-        <v>0.006113507731187234</v>
+        <v>0.006263243941652582</v>
       </c>
       <c r="I2002">
-        <v>0.2639960766381626</v>
+        <v>0.3547972536467139</v>
       </c>
       <c r="J2002">
         <v>0.4533464112061254</v>
       </c>
       <c r="K2002">
-        <v>2.84</v>
+        <v>3.57</v>
       </c>
       <c r="L2002">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="M2002">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2002">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2002">
         <v>1</v>
@@ -102285,57 +102285,57 @@
     </row>
     <row r="2003" spans="1:16">
       <c r="A2003" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2003" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C2003">
-        <v>3.571553311994133</v>
+        <v>3.016151146705838</v>
       </c>
       <c r="D2003" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E2003">
-        <v>3.216756058347419</v>
+        <v>3.275513894967134</v>
       </c>
       <c r="F2003">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2003">
-        <v>0.006808446688005869</v>
+        <v>0.005583848853294163</v>
       </c>
       <c r="H2003">
-        <v>0.006263243941652582</v>
+        <v>0.006104486105032866</v>
       </c>
       <c r="I2003">
-        <v>0.3547972536467139</v>
+        <v>0.2593627482612963</v>
       </c>
       <c r="J2003">
-        <v>0.4533464112061254</v>
+        <v>0.4504732818576006</v>
       </c>
       <c r="K2003">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="L2003">
-        <v>5.19</v>
+        <v>4.3</v>
       </c>
       <c r="M2003">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2003">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2003">
         <v>1</v>
       </c>
       <c r="P2003" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2004" spans="1:16">
       <c r="A2004" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2004" t="s">
         <v>271</v>
@@ -102385,7 +102385,7 @@
     </row>
     <row r="2005" spans="1:16">
       <c r="A2005" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2005" t="s">
         <v>270</v>
@@ -102435,7 +102435,7 @@
     </row>
     <row r="2006" spans="1:16">
       <c r="A2006" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2006" t="s">
         <v>252</v>
@@ -102485,7 +102485,7 @@
     </row>
     <row r="2007" spans="1:16">
       <c r="A2007" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2007" t="s">
         <v>266</v>
@@ -102938,10 +102938,10 @@
         <v>0</v>
       </c>
       <c r="B2016" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C2016">
-        <v>3.052236224586666</v>
+        <v>3.056007820745499</v>
       </c>
       <c r="D2016" t="s">
         <v>438</v>
@@ -102953,22 +102953,22 @@
         <v>1</v>
       </c>
       <c r="G2016">
-        <v>0.005447763775413334</v>
+        <v>0.005503992179254501</v>
       </c>
       <c r="H2016">
         <v>0.006062619801021119</v>
       </c>
       <c r="I2016">
-        <v>0.265143974392215</v>
+        <v>0.2613723782333821</v>
       </c>
       <c r="J2016">
         <v>0.4371400640194647</v>
       </c>
       <c r="K2016">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="L2016">
-        <v>4.25</v>
+        <v>4.28</v>
       </c>
       <c r="M2016">
         <v>3.14</v>
@@ -102988,10 +102988,10 @@
         <v>1</v>
       </c>
       <c r="B2017" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="C2017">
-        <v>3.04852221818472</v>
+        <v>3.052236224586666</v>
       </c>
       <c r="D2017" t="s">
         <v>438</v>
@@ -103003,22 +103003,22 @@
         <v>1</v>
       </c>
       <c r="G2017">
-        <v>0.00553147778181528</v>
+        <v>0.005447763775413334</v>
       </c>
       <c r="H2017">
         <v>0.006062619801021119</v>
       </c>
       <c r="I2017">
-        <v>0.2688579807941611</v>
+        <v>0.265143974392215</v>
       </c>
       <c r="J2017">
         <v>0.4371400640194647</v>
       </c>
       <c r="K2017">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="L2017">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="M2017">
         <v>3.14</v>
@@ -103038,43 +103038,43 @@
         <v>2</v>
       </c>
       <c r="B2018" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C2018">
-        <v>3.629409971450511</v>
+        <v>3.04852221818472</v>
       </c>
       <c r="D2018" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E2018">
-        <v>3.271209384894599</v>
+        <v>3.317380198978881</v>
       </c>
       <c r="F2018">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2018">
-        <v>0.006750590028549489</v>
+        <v>0.00553147778181528</v>
       </c>
       <c r="H2018">
-        <v>0.006208790615105402</v>
+        <v>0.006062619801021119</v>
       </c>
       <c r="I2018">
-        <v>0.3582005865559128</v>
+        <v>0.2688579807941611</v>
       </c>
       <c r="J2018">
         <v>0.4371400640194647</v>
       </c>
       <c r="K2018">
-        <v>3.57</v>
+        <v>2.84</v>
       </c>
       <c r="L2018">
-        <v>5.19</v>
+        <v>4.29</v>
       </c>
       <c r="M2018">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2018">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2018">
         <v>1</v>
@@ -103085,96 +103085,96 @@
     </row>
     <row r="2019" spans="1:16">
       <c r="A2019" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2019" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C2019">
-        <v>3.062565775248474</v>
+        <v>3.629409971450511</v>
       </c>
       <c r="D2019" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E2019">
-        <v>3.329217713240952</v>
+        <v>3.271209384894599</v>
       </c>
       <c r="F2019">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2019">
-        <v>0.005437434224751526</v>
+        <v>0.006750590028549489</v>
       </c>
       <c r="H2019">
-        <v>0.006050782286759049</v>
+        <v>0.006208790615105402</v>
       </c>
       <c r="I2019">
-        <v>0.2666519379924779</v>
+        <v>0.3582005865559128</v>
       </c>
       <c r="J2019">
-        <v>0.4333701550188053</v>
+        <v>0.4371400640194647</v>
       </c>
       <c r="K2019">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="L2019">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2019">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2019">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2019">
         <v>1</v>
       </c>
       <c r="P2019" t="s">
-        <v>271</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2020" spans="1:16">
       <c r="A2020" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2020" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C2020">
-        <v>3.642868546582866</v>
+        <v>3.062565775248474</v>
       </c>
       <c r="D2020" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E2020">
-        <v>3.283876279136814</v>
+        <v>3.329217713240952</v>
       </c>
       <c r="F2020">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2020">
-        <v>0.006737131453417135</v>
+        <v>0.005437434224751526</v>
       </c>
       <c r="H2020">
-        <v>0.006196123720863186</v>
+        <v>0.006050782286759049</v>
       </c>
       <c r="I2020">
-        <v>0.3589922674460513</v>
+        <v>0.2666519379924779</v>
       </c>
       <c r="J2020">
         <v>0.4333701550188053</v>
       </c>
       <c r="K2020">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2020">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2020">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2020">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2020">
         <v>1</v>
@@ -103185,96 +103185,96 @@
     </row>
     <row r="2021" spans="1:16">
       <c r="A2021" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2021" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C2021">
-        <v>3.07490254446135</v>
+        <v>3.642868546582866</v>
       </c>
       <c r="D2021" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E2021">
-        <v>3.343355470660088</v>
+        <v>3.283876279136814</v>
       </c>
       <c r="F2021">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2021">
-        <v>0.00542509745553865</v>
+        <v>0.006737131453417135</v>
       </c>
       <c r="H2021">
-        <v>0.006036644529339913</v>
+        <v>0.006196123720863186</v>
       </c>
       <c r="I2021">
-        <v>0.2684529261987381</v>
+        <v>0.3589922674460513</v>
       </c>
       <c r="J2021">
-        <v>0.428867684503157</v>
+        <v>0.4333701550188053</v>
       </c>
       <c r="K2021">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="L2021">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2021">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2021">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2021">
         <v>1</v>
       </c>
       <c r="P2021" t="s">
-        <v>600</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2022" spans="1:16">
       <c r="A2022" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2022" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C2022">
-        <v>3.65894236632373</v>
+        <v>3.07490254446135</v>
       </c>
       <c r="D2022" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E2022">
-        <v>3.299004580069393</v>
+        <v>3.343355470660088</v>
       </c>
       <c r="F2022">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2022">
-        <v>0.006721057633676271</v>
+        <v>0.00542509745553865</v>
       </c>
       <c r="H2022">
-        <v>0.006180995419930608</v>
+        <v>0.006036644529339913</v>
       </c>
       <c r="I2022">
-        <v>0.3599377862543376</v>
+        <v>0.2684529261987381</v>
       </c>
       <c r="J2022">
         <v>0.428867684503157</v>
       </c>
       <c r="K2022">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2022">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2022">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2022">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2022">
         <v>1</v>
@@ -103285,13 +103285,13 @@
     </row>
     <row r="2023" spans="1:16">
       <c r="A2023" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2023" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2023">
-        <v>3.620302798888003</v>
+        <v>3.65894236632373</v>
       </c>
       <c r="D2023" t="s">
         <v>458</v>
@@ -103303,22 +103303,22 @@
         <v>-1</v>
       </c>
       <c r="G2023">
-        <v>0.006879697201111997</v>
+        <v>0.006721057633676271</v>
       </c>
       <c r="H2023">
         <v>0.006180995419930608</v>
       </c>
       <c r="I2023">
-        <v>0.3212982188186109</v>
+        <v>0.3599377862543376</v>
       </c>
       <c r="J2023">
         <v>0.428867684503157</v>
       </c>
       <c r="K2023">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2023">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2023">
         <v>3.36</v>
@@ -103435,96 +103435,96 @@
     </row>
     <row r="2026" spans="1:16">
       <c r="A2026" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2026" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C2026">
-        <v>3.637475587331958</v>
+        <v>3.099234459997845</v>
       </c>
       <c r="D2026" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E2026">
-        <v>3.314188940377731</v>
+        <v>3.371239490654465</v>
       </c>
       <c r="F2026">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2026">
-        <v>0.006862524412668043</v>
+        <v>0.005400765540002155</v>
       </c>
       <c r="H2026">
-        <v>0.00616581105962227</v>
+        <v>0.006008760509345536</v>
       </c>
       <c r="I2026">
-        <v>0.3232866469542266</v>
+        <v>0.27200503065662</v>
       </c>
       <c r="J2026">
-        <v>0.4243485296494848</v>
+        <v>0.4199874233584508</v>
       </c>
       <c r="K2026">
-        <v>3.8</v>
+        <v>2.74</v>
       </c>
       <c r="L2026">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="M2026">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2026">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2026">
         <v>1</v>
       </c>
       <c r="P2026" t="s">
-        <v>269</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2027" spans="1:16">
       <c r="A2027" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2027" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C2027">
-        <v>3.099234459997845</v>
+        <v>3.690644898610331</v>
       </c>
       <c r="D2027" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E2027">
-        <v>3.371239490654465</v>
+        <v>3.328842257515606</v>
       </c>
       <c r="F2027">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2027">
-        <v>0.005400765540002155</v>
+        <v>0.00668935510138967</v>
       </c>
       <c r="H2027">
-        <v>0.006008760509345536</v>
+        <v>0.006151157742484395</v>
       </c>
       <c r="I2027">
-        <v>0.27200503065662</v>
+        <v>0.3618026410947253</v>
       </c>
       <c r="J2027">
         <v>0.4199874233584508</v>
       </c>
       <c r="K2027">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="L2027">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2027">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2027">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2027">
         <v>1</v>
@@ -103535,90 +103535,90 @@
     </row>
     <row r="2028" spans="1:16">
       <c r="A2028" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2028" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C2028">
-        <v>3.690644898610331</v>
+        <v>3.107242356855426</v>
       </c>
       <c r="D2028" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E2028">
-        <v>3.328842257515606</v>
+        <v>3.38041642354965</v>
       </c>
       <c r="F2028">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2028">
-        <v>0.00668935510138967</v>
+        <v>0.005392757643144574</v>
       </c>
       <c r="H2028">
-        <v>0.006151157742484395</v>
+        <v>0.005999583576450351</v>
       </c>
       <c r="I2028">
-        <v>0.3618026410947253</v>
+        <v>0.2731740666942235</v>
       </c>
       <c r="J2028">
-        <v>0.4199874233584508</v>
+        <v>0.4170648332644428</v>
       </c>
       <c r="K2028">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2028">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2028">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2028">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2028">
         <v>1</v>
       </c>
       <c r="P2028" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2029" spans="1:16">
       <c r="A2029" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2029" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2029">
-        <v>3.654047791237887</v>
+        <v>3.70107854524594</v>
       </c>
       <c r="D2029" t="s">
         <v>458</v>
       </c>
       <c r="E2029">
-        <v>3.328842257515606</v>
+        <v>3.338662160231472</v>
       </c>
       <c r="F2029">
         <v>-1</v>
       </c>
       <c r="G2029">
-        <v>0.006845952208762113</v>
+        <v>0.006678921454754061</v>
       </c>
       <c r="H2029">
-        <v>0.006151157742484395</v>
+        <v>0.006141337839768528</v>
       </c>
       <c r="I2029">
-        <v>0.3252055337222814</v>
+        <v>0.3624163850144675</v>
       </c>
       <c r="J2029">
-        <v>0.4199874233584508</v>
+        <v>0.4170648332644428</v>
       </c>
       <c r="K2029">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2029">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2029">
         <v>3.36</v>
@@ -103630,18 +103630,18 @@
         <v>1</v>
       </c>
       <c r="P2029" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2030" spans="1:16">
       <c r="A2030" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2030" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C2030">
-        <v>3.70107854524594</v>
+        <v>3.665153633595117</v>
       </c>
       <c r="D2030" t="s">
         <v>458</v>
@@ -103653,22 +103653,22 @@
         <v>-1</v>
       </c>
       <c r="G2030">
-        <v>0.006678921454754061</v>
+        <v>0.006834846366404882</v>
       </c>
       <c r="H2030">
         <v>0.006141337839768528</v>
       </c>
       <c r="I2030">
-        <v>0.3624163850144675</v>
+        <v>0.326491473363645</v>
       </c>
       <c r="J2030">
         <v>0.4170648332644428</v>
       </c>
       <c r="K2030">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="L2030">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="M2030">
         <v>3.36</v>
@@ -103685,40 +103685,40 @@
     </row>
     <row r="2031" spans="1:16">
       <c r="A2031" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2031" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2031">
-        <v>3.665153633595117</v>
+        <v>3.707160342770936</v>
       </c>
       <c r="D2031" t="s">
         <v>458</v>
       </c>
       <c r="E2031">
-        <v>3.338662160231472</v>
+        <v>3.344386204960881</v>
       </c>
       <c r="F2031">
         <v>-1</v>
       </c>
       <c r="G2031">
-        <v>0.006834846366404882</v>
+        <v>0.006672839657229064</v>
       </c>
       <c r="H2031">
-        <v>0.006141337839768528</v>
+        <v>0.006135613795039119</v>
       </c>
       <c r="I2031">
-        <v>0.326491473363645</v>
+        <v>0.3627741378100549</v>
       </c>
       <c r="J2031">
-        <v>0.4170648332644428</v>
+        <v>0.4153612485235474</v>
       </c>
       <c r="K2031">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2031">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2031">
         <v>3.36</v>
@@ -103730,18 +103730,18 @@
         <v>1</v>
       </c>
       <c r="P2031" t="s">
-        <v>602</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2032" spans="1:16">
       <c r="A2032" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2032" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C2032">
-        <v>3.707160342770936</v>
+        <v>3.67162725561052</v>
       </c>
       <c r="D2032" t="s">
         <v>458</v>
@@ -103753,22 +103753,22 @@
         <v>-1</v>
       </c>
       <c r="G2032">
-        <v>0.006672839657229064</v>
+        <v>0.00682837274438948</v>
       </c>
       <c r="H2032">
         <v>0.006135613795039119</v>
       </c>
       <c r="I2032">
-        <v>0.3627741378100549</v>
+        <v>0.327241050649639</v>
       </c>
       <c r="J2032">
         <v>0.4153612485235474</v>
       </c>
       <c r="K2032">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="L2032">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="M2032">
         <v>3.36</v>
@@ -103785,40 +103785,40 @@
     </row>
     <row r="2033" spans="1:16">
       <c r="A2033" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2033" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2033">
-        <v>3.67162725561052</v>
+        <v>3.714769378692448</v>
       </c>
       <c r="D2033" t="s">
         <v>458</v>
       </c>
       <c r="E2033">
-        <v>3.344386204960881</v>
+        <v>3.351547650534069</v>
       </c>
       <c r="F2033">
         <v>-1</v>
       </c>
       <c r="G2033">
-        <v>0.00682837274438948</v>
+        <v>0.006665230621307553</v>
       </c>
       <c r="H2033">
-        <v>0.006135613795039119</v>
+        <v>0.006128452349465931</v>
       </c>
       <c r="I2033">
-        <v>0.327241050649639</v>
+        <v>0.3632217281583792</v>
       </c>
       <c r="J2033">
-        <v>0.4153612485235474</v>
+        <v>0.4132298659124795</v>
       </c>
       <c r="K2033">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2033">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2033">
         <v>3.36</v>
@@ -103830,18 +103830,18 @@
         <v>1</v>
       </c>
       <c r="P2033" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2034" spans="1:16">
       <c r="A2034" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2034" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C2034">
-        <v>3.714769378692448</v>
+        <v>3.679726509532578</v>
       </c>
       <c r="D2034" t="s">
         <v>458</v>
@@ -103853,22 +103853,22 @@
         <v>-1</v>
       </c>
       <c r="G2034">
-        <v>0.006665230621307553</v>
+        <v>0.006820273490467422</v>
       </c>
       <c r="H2034">
         <v>0.006128452349465931</v>
       </c>
       <c r="I2034">
-        <v>0.3632217281583792</v>
+        <v>0.3281788589985091</v>
       </c>
       <c r="J2034">
         <v>0.4132298659124795</v>
       </c>
       <c r="K2034">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="L2034">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="M2034">
         <v>3.36</v>
@@ -103885,40 +103885,40 @@
     </row>
     <row r="2035" spans="1:16">
       <c r="A2035" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2035" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2035">
-        <v>3.679726509532578</v>
+        <v>3.736478196776529</v>
       </c>
       <c r="D2035" t="s">
         <v>458</v>
       </c>
       <c r="E2035">
-        <v>3.351547650534069</v>
+        <v>3.371979479319086</v>
       </c>
       <c r="F2035">
         <v>-1</v>
       </c>
       <c r="G2035">
-        <v>0.006820273490467422</v>
+        <v>0.006643521803223472</v>
       </c>
       <c r="H2035">
-        <v>0.006128452349465931</v>
+        <v>0.006108020520680915</v>
       </c>
       <c r="I2035">
-        <v>0.3281788589985091</v>
+        <v>0.364498717457443</v>
       </c>
       <c r="J2035">
-        <v>0.4132298659124795</v>
+        <v>0.4071489644883673</v>
       </c>
       <c r="K2035">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L2035">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2035">
         <v>3.36</v>
@@ -103930,18 +103930,18 @@
         <v>1</v>
       </c>
       <c r="P2035" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2036" spans="1:16">
       <c r="A2036" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2036" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C2036">
-        <v>3.736478196776529</v>
+        <v>3.702833934944204</v>
       </c>
       <c r="D2036" t="s">
         <v>458</v>
@@ -103953,22 +103953,22 @@
         <v>-1</v>
       </c>
       <c r="G2036">
-        <v>0.006643521803223472</v>
+        <v>0.006797166065055796</v>
       </c>
       <c r="H2036">
         <v>0.006108020520680915</v>
       </c>
       <c r="I2036">
-        <v>0.364498717457443</v>
+        <v>0.3308544556251181</v>
       </c>
       <c r="J2036">
         <v>0.4071489644883673</v>
       </c>
       <c r="K2036">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="L2036">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="M2036">
         <v>3.36</v>
@@ -103985,96 +103985,96 @@
     </row>
     <row r="2037" spans="1:16">
       <c r="A2037" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2037" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C2037">
-        <v>3.702833934944204</v>
+        <v>1.800987352365764</v>
       </c>
       <c r="D2037" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E2037">
-        <v>3.371979479319086</v>
+        <v>1.71084355840465</v>
       </c>
       <c r="F2037">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2037">
-        <v>0.006797166065055796</v>
+        <v>0.007359012647634236</v>
       </c>
       <c r="H2037">
-        <v>0.006108020520680915</v>
+        <v>0.007489156441595349</v>
       </c>
       <c r="I2037">
-        <v>0.3308544556251181</v>
+        <v>-0.09014379396111405</v>
       </c>
       <c r="J2037">
-        <v>0.4071489644883673</v>
+        <v>0.8472599535470232</v>
       </c>
       <c r="K2037">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="L2037">
-        <v>5.25</v>
+        <v>4.58</v>
       </c>
       <c r="M2037">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="N2037">
-        <v>4.74</v>
+        <v>4.6</v>
       </c>
       <c r="O2037">
         <v>1</v>
       </c>
       <c r="P2037" t="s">
-        <v>252</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2038" spans="1:16">
       <c r="A2038" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2038" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C2038">
-        <v>1.800987352365764</v>
+        <v>1.811822949578585</v>
       </c>
       <c r="D2038" t="s">
         <v>460</v>
       </c>
       <c r="E2038">
-        <v>1.780151755152943</v>
+        <v>1.71084355840465</v>
       </c>
       <c r="F2038">
         <v>1</v>
       </c>
       <c r="G2038">
-        <v>0.007359012647634236</v>
+        <v>0.007268177050421415</v>
       </c>
       <c r="H2038">
-        <v>0.007439848244847058</v>
+        <v>0.007489156441595349</v>
       </c>
       <c r="I2038">
-        <v>-0.02083559721282136</v>
+        <v>-0.1009793911739347</v>
       </c>
       <c r="J2038">
         <v>0.8472599535470232</v>
       </c>
       <c r="K2038">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="L2038">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="M2038">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="N2038">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="O2038">
         <v>1</v>
@@ -104085,52 +104085,52 @@
     </row>
     <row r="2039" spans="1:16">
       <c r="A2039" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2039" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C2039">
-        <v>1.830295549114055</v>
+        <v>1.789933027597667</v>
       </c>
       <c r="D2039" t="s">
-        <v>460</v>
+        <v>272</v>
       </c>
       <c r="E2039">
-        <v>1.780151755152943</v>
+        <v>1.654253188432206</v>
       </c>
       <c r="F2039">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2039">
-        <v>0.007269704450885945</v>
+        <v>0.007570066972402333</v>
       </c>
       <c r="H2039">
-        <v>0.007439848244847058</v>
+        <v>0.007505746811567794</v>
       </c>
       <c r="I2039">
-        <v>-0.05014379396111224</v>
+        <v>0.1356798391654603</v>
       </c>
       <c r="J2039">
-        <v>0.8472599535470232</v>
+        <v>0.8919959791365225</v>
       </c>
       <c r="K2039">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="L2039">
-        <v>4.55</v>
+        <v>4.68</v>
       </c>
       <c r="M2039">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="N2039">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="O2039">
         <v>1</v>
       </c>
       <c r="P2039" t="s">
-        <v>452</v>
+        <v>603</v>
       </c>
     </row>
     <row r="2040" spans="1:16">
@@ -104138,98 +104138,48 @@
         <v>0</v>
       </c>
       <c r="B2040" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C2040">
-        <v>1.789933027597667</v>
+        <v>1.668381258671795</v>
       </c>
       <c r="D2040" t="s">
-        <v>272</v>
+        <v>461</v>
       </c>
       <c r="E2040">
-        <v>1.654253188432206</v>
+        <v>1.60127520372704</v>
       </c>
       <c r="F2040">
         <v>-1</v>
       </c>
       <c r="G2040">
-        <v>0.007570066972402333</v>
+        <v>0.007451618741328204</v>
       </c>
       <c r="H2040">
-        <v>0.007505746811567794</v>
+        <v>0.007618724796272961</v>
       </c>
       <c r="I2040">
-        <v>0.1356798391654603</v>
+        <v>0.0671060549447553</v>
       </c>
       <c r="J2040">
-        <v>0.8919959791365225</v>
+        <v>0.9008158072673534</v>
       </c>
       <c r="K2040">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="L2040">
-        <v>4.68</v>
+        <v>4.56</v>
       </c>
       <c r="M2040">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="N2040">
-        <v>4.58</v>
+        <v>4.61</v>
       </c>
       <c r="O2040">
         <v>1</v>
       </c>
       <c r="P2040" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="2041" spans="1:16">
-      <c r="A2041" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2041" t="s">
-        <v>275</v>
-      </c>
-      <c r="C2041">
-        <v>1.668381258671795</v>
-      </c>
-      <c r="D2041" t="s">
-        <v>461</v>
-      </c>
-      <c r="E2041">
-        <v>1.639373100599122</v>
-      </c>
-      <c r="F2041">
-        <v>-1</v>
-      </c>
-      <c r="G2041">
-        <v>0.007451618741328204</v>
-      </c>
-      <c r="H2041">
-        <v>0.007440626899400878</v>
-      </c>
-      <c r="I2041">
-        <v>0.02900815807267332</v>
-      </c>
-      <c r="J2041">
-        <v>0.9008158072673534</v>
-      </c>
-      <c r="K2041">
-        <v>3.21</v>
-      </c>
-      <c r="L2041">
-        <v>4.56</v>
-      </c>
-      <c r="M2041">
-        <v>3.22</v>
-      </c>
-      <c r="N2041">
-        <v>4.54</v>
-      </c>
-      <c r="O2041">
-        <v>1</v>
-      </c>
-      <c r="P2041" t="s">
         <v>272</v>
       </c>
     </row>

--- a/s60_signal/position-00857-601857.xlsx
+++ b/s60_signal/position-00857-601857.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6159" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6162" uniqueCount="611">
   <si>
     <t>trade_time</t>
   </si>
@@ -838,19 +838,19 @@
     <t>2021-08-23</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2021-08-11</t>
   </si>
   <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
-    <t>2021-08-26</t>
+    <t>2021-08-27</t>
   </si>
   <si>
     <t>2021-08-12</t>
   </si>
   <si>
-    <t>2021-08-27</t>
+    <t>2021-08-26</t>
   </si>
   <si>
     <t>2016-08-15</t>
@@ -1408,7 +1408,7 @@
     <t>2021-08-25</t>
   </si>
   <si>
-    <t>2021-08-31</t>
+    <t>2021-09-01</t>
   </si>
   <si>
     <t>2021-08-20</t>
@@ -1843,9 +1843,6 @@
     <t>2021-08-02</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>2021-08-09</t>
   </si>
   <si>
@@ -2207,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2049"/>
+  <dimension ref="A1:P2050"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -103162,43 +103159,43 @@
         <v>1</v>
       </c>
       <c r="B2020" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C2020">
-        <v>3.072015776011034</v>
+        <v>3.65894236632373</v>
       </c>
       <c r="D2020" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="E2020">
-        <v>3.343355470660088</v>
+        <v>3.299004580069393</v>
       </c>
       <c r="F2020">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2020">
-        <v>0.005507984223988966</v>
+        <v>0.006721057633676271</v>
       </c>
       <c r="H2020">
-        <v>0.006036644529339913</v>
+        <v>0.006180995419930608</v>
       </c>
       <c r="I2020">
-        <v>0.2713396946490532</v>
+        <v>0.3599377862543376</v>
       </c>
       <c r="J2020">
         <v>0.428867684503157</v>
       </c>
       <c r="K2020">
-        <v>2.84</v>
+        <v>3.57</v>
       </c>
       <c r="L2020">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="M2020">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2020">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2020">
         <v>1</v>
@@ -103209,96 +103206,96 @@
     </row>
     <row r="2021" spans="1:16">
       <c r="A2021" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2021" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C2021">
-        <v>3.65894236632373</v>
+        <v>3.087285028760411</v>
       </c>
       <c r="D2021" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="E2021">
-        <v>3.299004580069393</v>
+        <v>3.357545616900618</v>
       </c>
       <c r="F2021">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2021">
-        <v>0.006721057633676271</v>
+        <v>0.005412714971239589</v>
       </c>
       <c r="H2021">
-        <v>0.006180995419930608</v>
+        <v>0.006022454383099383</v>
       </c>
       <c r="I2021">
-        <v>0.3599377862543376</v>
+        <v>0.2702605881402063</v>
       </c>
       <c r="J2021">
-        <v>0.428867684503157</v>
+        <v>0.4243485296494848</v>
       </c>
       <c r="K2021">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2021">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2021">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2021">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2021">
         <v>1</v>
       </c>
       <c r="P2021" t="s">
-        <v>604</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2022" spans="1:16">
       <c r="A2022" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2022" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C2022">
-        <v>3.087285028760411</v>
+        <v>3.67507574915134</v>
       </c>
       <c r="D2022" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="E2022">
-        <v>3.357545616900618</v>
+        <v>3.314188940377731</v>
       </c>
       <c r="F2022">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2022">
-        <v>0.005412714971239589</v>
+        <v>0.006704924250848661</v>
       </c>
       <c r="H2022">
-        <v>0.006022454383099383</v>
+        <v>0.00616581105962227</v>
       </c>
       <c r="I2022">
-        <v>0.2702605881402063</v>
+        <v>0.3608868087736088</v>
       </c>
       <c r="J2022">
         <v>0.4243485296494848</v>
       </c>
       <c r="K2022">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="L2022">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2022">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2022">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2022">
         <v>1</v>
@@ -103309,96 +103306,96 @@
     </row>
     <row r="2023" spans="1:16">
       <c r="A2023" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2023" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C2023">
-        <v>3.67507574915134</v>
+        <v>3.099234459997845</v>
       </c>
       <c r="D2023" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="E2023">
-        <v>3.314188940377731</v>
+        <v>3.371239490654465</v>
       </c>
       <c r="F2023">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2023">
-        <v>0.006704924250848661</v>
+        <v>0.005400765540002155</v>
       </c>
       <c r="H2023">
-        <v>0.00616581105962227</v>
+        <v>0.006008760509345536</v>
       </c>
       <c r="I2023">
-        <v>0.3608868087736088</v>
+        <v>0.27200503065662</v>
       </c>
       <c r="J2023">
-        <v>0.4243485296494848</v>
+        <v>0.4199874233584508</v>
       </c>
       <c r="K2023">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2023">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2023">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2023">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2023">
         <v>1</v>
       </c>
       <c r="P2023" t="s">
-        <v>269</v>
+        <v>605</v>
       </c>
     </row>
     <row r="2024" spans="1:16">
       <c r="A2024" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2024" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C2024">
-        <v>3.099234459997845</v>
+        <v>3.690644898610331</v>
       </c>
       <c r="D2024" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="E2024">
-        <v>3.371239490654465</v>
+        <v>3.328842257515606</v>
       </c>
       <c r="F2024">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2024">
-        <v>0.005400765540002155</v>
+        <v>0.00668935510138967</v>
       </c>
       <c r="H2024">
-        <v>0.006008760509345536</v>
+        <v>0.006151157742484395</v>
       </c>
       <c r="I2024">
-        <v>0.27200503065662</v>
+        <v>0.3618026410947253</v>
       </c>
       <c r="J2024">
         <v>0.4199874233584508</v>
       </c>
       <c r="K2024">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="L2024">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2024">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2024">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2024">
         <v>1</v>
@@ -103409,96 +103406,96 @@
     </row>
     <row r="2025" spans="1:16">
       <c r="A2025" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2025" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C2025">
-        <v>3.690644898610331</v>
+        <v>3.107242356855426</v>
       </c>
       <c r="D2025" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="E2025">
-        <v>3.328842257515606</v>
+        <v>3.38041642354965</v>
       </c>
       <c r="F2025">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2025">
-        <v>0.00668935510138967</v>
+        <v>0.005392757643144574</v>
       </c>
       <c r="H2025">
-        <v>0.006151157742484395</v>
+        <v>0.005999583576450351</v>
       </c>
       <c r="I2025">
-        <v>0.3618026410947253</v>
+        <v>0.2731740666942235</v>
       </c>
       <c r="J2025">
-        <v>0.4199874233584508</v>
+        <v>0.4170648332644428</v>
       </c>
       <c r="K2025">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="L2025">
-        <v>5.19</v>
+        <v>4.25</v>
       </c>
       <c r="M2025">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="N2025">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O2025">
         <v>1</v>
       </c>
       <c r="P2025" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2026" spans="1:16">
       <c r="A2026" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2026" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C2026">
-        <v>3.107242356855426</v>
+        <v>3.70107854524594</v>
       </c>
       <c r="D2026" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="E2026">
-        <v>3.38041642354965</v>
+        <v>3.338662160231472</v>
       </c>
       <c r="F2026">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2026">
-        <v>0.005392757643144574</v>
+        <v>0.006678921454754061</v>
       </c>
       <c r="H2026">
-        <v>0.005999583576450351</v>
+        <v>0.006141337839768528</v>
       </c>
       <c r="I2026">
-        <v>0.2731740666942235</v>
+        <v>0.3624163850144675</v>
       </c>
       <c r="J2026">
         <v>0.4170648332644428</v>
       </c>
       <c r="K2026">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="L2026">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="M2026">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N2026">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O2026">
         <v>1</v>
@@ -103509,46 +103506,46 @@
     </row>
     <row r="2027" spans="1:16">
       <c r="A2027" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2027" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C2027">
-        <v>3.70107854524594</v>
+        <v>3.140320863566183</v>
       </c>
       <c r="D2027" t="s">
-        <v>461</v>
+        <v>276</v>
       </c>
       <c r="E2027">
-        <v>3.338662160231472</v>
+        <v>3.407904478551717</v>
       </c>
       <c r="F2027">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2027">
-        <v>0.006678921454754061</v>
+        <v>0.005959679136433816</v>
       </c>
       <c r="H2027">
-        <v>0.006141337839768528</v>
+        <v>0.006052095521448284</v>
       </c>
       <c r="I2027">
-        <v>0.3624163850144675</v>
+        <v>0.2675836149855337</v>
       </c>
       <c r="J2027">
         <v>0.4170648332644428</v>
       </c>
       <c r="K2027">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="L2027">
-        <v>5.19</v>
+        <v>4.55</v>
       </c>
       <c r="M2027">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="N2027">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="O2027">
         <v>1</v>
@@ -103609,96 +103606,96 @@
     </row>
     <row r="2029" spans="1:16">
       <c r="A2029" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2029" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C2029">
-        <v>3.714769378692448</v>
+        <v>3.14607897999041</v>
       </c>
       <c r="D2029" t="s">
-        <v>461</v>
+        <v>276</v>
       </c>
       <c r="E2029">
-        <v>3.351547650534069</v>
+        <v>3.413304842180355</v>
       </c>
       <c r="F2029">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2029">
-        <v>0.006665230621307553</v>
+        <v>0.00595392102000959</v>
       </c>
       <c r="H2029">
-        <v>0.006128452349465931</v>
+        <v>0.006046695157819646</v>
       </c>
       <c r="I2029">
-        <v>0.3632217281583792</v>
+        <v>0.267225862189945</v>
       </c>
       <c r="J2029">
-        <v>0.4132298659124795</v>
+        <v>0.4153612485235474</v>
       </c>
       <c r="K2029">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="L2029">
-        <v>5.19</v>
+        <v>4.55</v>
       </c>
       <c r="M2029">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="N2029">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="O2029">
         <v>1</v>
       </c>
       <c r="P2029" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2030" spans="1:16">
       <c r="A2030" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2030" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C2030">
-        <v>3.153283053215819</v>
+        <v>3.714769378692448</v>
       </c>
       <c r="D2030" t="s">
-        <v>278</v>
+        <v>461</v>
       </c>
       <c r="E2030">
-        <v>3.420061325057441</v>
+        <v>3.351547650534069</v>
       </c>
       <c r="F2030">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2030">
-        <v>0.00594671694678418</v>
+        <v>0.006665230621307553</v>
       </c>
       <c r="H2030">
-        <v>0.00603993867494256</v>
+        <v>0.006128452349465931</v>
       </c>
       <c r="I2030">
-        <v>0.2667782718416212</v>
+        <v>0.3632217281583792</v>
       </c>
       <c r="J2030">
         <v>0.4132298659124795</v>
       </c>
       <c r="K2030">
-        <v>3.38</v>
+        <v>3.57</v>
       </c>
       <c r="L2030">
-        <v>4.55</v>
+        <v>5.19</v>
       </c>
       <c r="M2030">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="N2030">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="O2030">
         <v>1</v>
@@ -103709,96 +103706,96 @@
     </row>
     <row r="2031" spans="1:16">
       <c r="A2031" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2031" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C2031">
-        <v>3.736478196776529</v>
+        <v>3.153283053215819</v>
       </c>
       <c r="D2031" t="s">
-        <v>461</v>
+        <v>276</v>
       </c>
       <c r="E2031">
-        <v>3.371979479319086</v>
+        <v>3.420061325057441</v>
       </c>
       <c r="F2031">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2031">
-        <v>0.006643521803223472</v>
+        <v>0.00594671694678418</v>
       </c>
       <c r="H2031">
-        <v>0.006108020520680915</v>
+        <v>0.00603993867494256</v>
       </c>
       <c r="I2031">
-        <v>0.364498717457443</v>
+        <v>0.2667782718416212</v>
       </c>
       <c r="J2031">
-        <v>0.4071489644883673</v>
+        <v>0.4132298659124795</v>
       </c>
       <c r="K2031">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="L2031">
-        <v>5.19</v>
+        <v>4.55</v>
       </c>
       <c r="M2031">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="N2031">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="O2031">
         <v>1</v>
       </c>
       <c r="P2031" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2032" spans="1:16">
       <c r="A2032" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2032" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C2032">
-        <v>3.173836500029318</v>
+        <v>3.736478196776529</v>
       </c>
       <c r="D2032" t="s">
-        <v>278</v>
+        <v>461</v>
       </c>
       <c r="E2032">
-        <v>3.439337782571876</v>
+        <v>3.371979479319086</v>
       </c>
       <c r="F2032">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2032">
-        <v>0.005926163499970681</v>
+        <v>0.006643521803223472</v>
       </c>
       <c r="H2032">
-        <v>0.006020662217428125</v>
+        <v>0.006108020520680915</v>
       </c>
       <c r="I2032">
-        <v>0.2655012825425573</v>
+        <v>0.364498717457443</v>
       </c>
       <c r="J2032">
         <v>0.4071489644883673</v>
       </c>
       <c r="K2032">
-        <v>3.38</v>
+        <v>3.57</v>
       </c>
       <c r="L2032">
-        <v>4.55</v>
+        <v>5.19</v>
       </c>
       <c r="M2032">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="N2032">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="O2032">
         <v>1</v>
@@ -103809,16 +103806,16 @@
     </row>
     <row r="2033" spans="1:16">
       <c r="A2033" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2033" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C2033">
-        <v>3.180052679020712</v>
+        <v>3.173836500029318</v>
       </c>
       <c r="D2033" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E2033">
         <v>3.439337782571876</v>
@@ -103827,22 +103824,22 @@
         <v>1</v>
       </c>
       <c r="G2033">
-        <v>0.005679947320979287</v>
+        <v>0.005926163499970681</v>
       </c>
       <c r="H2033">
         <v>0.006020662217428125</v>
       </c>
       <c r="I2033">
-        <v>0.2592851035511634</v>
+        <v>0.2655012825425573</v>
       </c>
       <c r="J2033">
         <v>0.4071489644883673</v>
       </c>
       <c r="K2033">
-        <v>3.07</v>
+        <v>3.38</v>
       </c>
       <c r="L2033">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="M2033">
         <v>3.17</v>
@@ -103859,63 +103856,63 @@
     </row>
     <row r="2034" spans="1:16">
       <c r="A2034" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2034" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C2034">
-        <v>1.780151755152943</v>
+        <v>3.180052679020712</v>
       </c>
       <c r="D2034" t="s">
-        <v>463</v>
+        <v>276</v>
       </c>
       <c r="E2034">
-        <v>1.949603745862347</v>
+        <v>3.439337782571876</v>
       </c>
       <c r="F2034">
         <v>1</v>
       </c>
       <c r="G2034">
-        <v>0.007439848244847058</v>
+        <v>0.005679947320979287</v>
       </c>
       <c r="H2034">
-        <v>0.007270396254137653</v>
+        <v>0.006020662217428125</v>
       </c>
       <c r="I2034">
-        <v>0.1694519907094043</v>
+        <v>0.2592851035511634</v>
       </c>
       <c r="J2034">
-        <v>0.8472599535470232</v>
+        <v>0.4071489644883673</v>
       </c>
       <c r="K2034">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
       <c r="L2034">
-        <v>4.61</v>
+        <v>4.43</v>
       </c>
       <c r="M2034">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="N2034">
-        <v>4.61</v>
+        <v>4.73</v>
       </c>
       <c r="O2034">
         <v>1</v>
       </c>
       <c r="P2034" t="s">
-        <v>455</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2035" spans="1:16">
       <c r="A2035" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2035" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C2035">
-        <v>1.794877750507645</v>
+        <v>1.800987352365764</v>
       </c>
       <c r="D2035" t="s">
         <v>463</v>
@@ -103927,22 +103924,22 @@
         <v>1</v>
       </c>
       <c r="G2035">
-        <v>0.007285122249492355</v>
+        <v>0.007359012647634236</v>
       </c>
       <c r="H2035">
         <v>0.007270396254137653</v>
       </c>
       <c r="I2035">
-        <v>0.1547259953547027</v>
+        <v>0.148616393496583</v>
       </c>
       <c r="J2035">
         <v>0.8472599535470232</v>
       </c>
       <c r="K2035">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="L2035">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="M2035">
         <v>3.14</v>
@@ -103959,46 +103956,46 @@
     </row>
     <row r="2036" spans="1:16">
       <c r="A2036" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2036" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C2036">
-        <v>1.989603745862347</v>
+        <v>1.780151755152943</v>
       </c>
       <c r="D2036" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E2036">
-        <v>2.050843558404651</v>
+        <v>1.949603745862347</v>
       </c>
       <c r="F2036">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2036">
-        <v>0.007310396254137654</v>
+        <v>0.007439848244847058</v>
       </c>
       <c r="H2036">
-        <v>0.007829156441595351</v>
+        <v>0.007270396254137653</v>
       </c>
       <c r="I2036">
-        <v>-0.06123981254230371</v>
+        <v>0.1694519907094043</v>
       </c>
       <c r="J2036">
         <v>0.8472599535470232</v>
       </c>
       <c r="K2036">
+        <v>3.34</v>
+      </c>
+      <c r="L2036">
+        <v>4.61</v>
+      </c>
+      <c r="M2036">
         <v>3.14</v>
       </c>
-      <c r="L2036">
-        <v>4.65</v>
-      </c>
-      <c r="M2036">
-        <v>3.41</v>
-      </c>
       <c r="N2036">
-        <v>4.94</v>
+        <v>4.61</v>
       </c>
       <c r="O2036">
         <v>1</v>
@@ -104009,96 +104006,96 @@
     </row>
     <row r="2037" spans="1:16">
       <c r="A2037" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2037" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2037">
-        <v>1.558293711144458</v>
+        <v>2.044185947255937</v>
       </c>
       <c r="D2037" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E2037">
-        <v>1.741851982173163</v>
+        <v>2.03237095886918</v>
       </c>
       <c r="F2037">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2037">
-        <v>0.007641706288855542</v>
+        <v>0.007415814052744065</v>
       </c>
       <c r="H2037">
-        <v>0.007058148017826838</v>
+        <v>0.00782762904113082</v>
       </c>
       <c r="I2037">
-        <v>0.1835582710287054</v>
+        <v>0.01181498838675665</v>
       </c>
       <c r="J2037">
-        <v>0.8919959791365225</v>
+        <v>0.8472599535470232</v>
       </c>
       <c r="K2037">
-        <v>3.41</v>
+        <v>3.17</v>
       </c>
       <c r="L2037">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="M2037">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="N2037">
-        <v>4.4</v>
+        <v>4.93</v>
       </c>
       <c r="O2037">
         <v>1</v>
       </c>
       <c r="P2037" t="s">
-        <v>607</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2038" spans="1:16">
       <c r="A2038" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2038" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2038">
-        <v>1.84913262551132</v>
+        <v>1.558293711144458</v>
       </c>
       <c r="D2038" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E2038">
-        <v>1.898293711144459</v>
+        <v>1.741851982173163</v>
       </c>
       <c r="F2038">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2038">
-        <v>0.00745086737448868</v>
+        <v>0.007641706288855542</v>
       </c>
       <c r="H2038">
-        <v>0.007981706288855542</v>
+        <v>0.007058148017826838</v>
       </c>
       <c r="I2038">
-        <v>-0.04916108563313903</v>
+        <v>0.1835582710287054</v>
       </c>
       <c r="J2038">
         <v>0.8919959791365225</v>
       </c>
       <c r="K2038">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="L2038">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="M2038">
-        <v>3.41</v>
+        <v>2.98</v>
       </c>
       <c r="N2038">
-        <v>4.94</v>
+        <v>4.4</v>
       </c>
       <c r="O2038">
         <v>1</v>
@@ -104109,96 +104106,96 @@
     </row>
     <row r="2039" spans="1:16">
       <c r="A2039" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2039" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2039">
-        <v>1.544772806976353</v>
+        <v>1.84913262551132</v>
       </c>
       <c r="D2039" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E2039">
-        <v>1.730036060055582</v>
+        <v>1.879373751353093</v>
       </c>
       <c r="F2039">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2039">
-        <v>0.007655227193023646</v>
+        <v>0.00745086737448868</v>
       </c>
       <c r="H2039">
-        <v>0.007069963939944419</v>
+        <v>0.007980626248646906</v>
       </c>
       <c r="I2039">
-        <v>0.1852632530792291</v>
+        <v>-0.03024112584177319</v>
       </c>
       <c r="J2039">
-        <v>0.8959610536726235</v>
+        <v>0.8919959791365225</v>
       </c>
       <c r="K2039">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="L2039">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="M2039">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="N2039">
-        <v>4.4</v>
+        <v>4.93</v>
       </c>
       <c r="O2039">
         <v>1</v>
       </c>
       <c r="P2039" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="2040" spans="1:16">
       <c r="A2040" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2040" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2040">
-        <v>1.836682291467962</v>
+        <v>1.544772806976353</v>
       </c>
       <c r="D2040" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E2040">
-        <v>1.884772806976354</v>
+        <v>1.730036060055582</v>
       </c>
       <c r="F2040">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2040">
-        <v>0.007463317708532038</v>
+        <v>0.007655227193023646</v>
       </c>
       <c r="H2040">
-        <v>0.007995227193023646</v>
+        <v>0.007069963939944419</v>
       </c>
       <c r="I2040">
-        <v>-0.04809051550839172</v>
+        <v>0.1852632530792291</v>
       </c>
       <c r="J2040">
         <v>0.8959610536726235</v>
       </c>
       <c r="K2040">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="L2040">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="M2040">
-        <v>3.41</v>
+        <v>2.98</v>
       </c>
       <c r="N2040">
-        <v>4.94</v>
+        <v>4.4</v>
       </c>
       <c r="O2040">
         <v>1</v>
@@ -104209,434 +104206,434 @@
     </row>
     <row r="2041" spans="1:16">
       <c r="A2041" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2041" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2041">
-        <v>1.528218097218324</v>
+        <v>1.836682291467962</v>
       </c>
       <c r="D2041" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E2041">
-        <v>1.715568894343287</v>
+        <v>1.865813196439627</v>
       </c>
       <c r="F2041">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2041">
-        <v>0.007671781902781675</v>
+        <v>0.007463317708532038</v>
       </c>
       <c r="H2041">
-        <v>0.007084431105656714</v>
+        <v>0.007994186803560371</v>
       </c>
       <c r="I2041">
-        <v>0.1873507971249628</v>
+        <v>-0.02913090497166504</v>
       </c>
       <c r="J2041">
-        <v>0.9008158072673534</v>
+        <v>0.8959610536726235</v>
       </c>
       <c r="K2041">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="L2041">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="M2041">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="N2041">
-        <v>4.4</v>
+        <v>4.93</v>
       </c>
       <c r="O2041">
         <v>1</v>
       </c>
       <c r="P2041" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2042" spans="1:16">
       <c r="A2042" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2042" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2042">
-        <v>1.82143836518051</v>
+        <v>1.528218097218324</v>
       </c>
       <c r="D2042" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E2042">
-        <v>1.868218097218325</v>
+        <v>1.715568894343287</v>
       </c>
       <c r="F2042">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2042">
-        <v>0.00747856163481949</v>
+        <v>0.007671781902781675</v>
       </c>
       <c r="H2042">
-        <v>0.008011781902781677</v>
+        <v>0.007084431105656714</v>
       </c>
       <c r="I2042">
-        <v>-0.04677973203781471</v>
+        <v>0.1873507971249628</v>
       </c>
       <c r="J2042">
         <v>0.9008158072673534</v>
       </c>
       <c r="K2042">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="L2042">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="M2042">
-        <v>3.41</v>
+        <v>2.98</v>
       </c>
       <c r="N2042">
-        <v>4.94</v>
+        <v>4.4</v>
       </c>
       <c r="O2042">
         <v>1</v>
       </c>
       <c r="P2042" t="s">
-        <v>609</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2043" spans="1:16">
       <c r="A2043" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2043" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2043">
-        <v>1.457708868054979</v>
+        <v>1.82143836518051</v>
       </c>
       <c r="D2043" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E2043">
-        <v>1.653950858300246</v>
+        <v>1.849209939145651</v>
       </c>
       <c r="F2043">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2043">
-        <v>0.00774229113194502</v>
+        <v>0.00747856163481949</v>
       </c>
       <c r="H2043">
-        <v>0.007146049141699754</v>
+        <v>0.008010790060854348</v>
       </c>
       <c r="I2043">
-        <v>0.1962419902452672</v>
+        <v>-0.02777157396514074</v>
       </c>
       <c r="J2043">
-        <v>0.9214930005703872</v>
+        <v>0.9008158072673534</v>
       </c>
       <c r="K2043">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="L2043">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="M2043">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="N2043">
-        <v>4.4</v>
+        <v>4.93</v>
       </c>
       <c r="O2043">
         <v>1</v>
       </c>
       <c r="P2043" t="s">
-        <v>610</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2044" spans="1:16">
       <c r="A2044" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2044" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2044">
-        <v>1.756511978208985</v>
+        <v>1.457708868054979</v>
       </c>
       <c r="D2044" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E2044">
-        <v>1.79770886805498</v>
+        <v>1.653950858300246</v>
       </c>
       <c r="F2044">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2044">
-        <v>0.007543488021791016</v>
+        <v>0.00774229113194502</v>
       </c>
       <c r="H2044">
-        <v>0.008082291131945019</v>
+        <v>0.007146049141699754</v>
       </c>
       <c r="I2044">
-        <v>-0.04119688984599534</v>
+        <v>0.1962419902452672</v>
       </c>
       <c r="J2044">
         <v>0.9214930005703872</v>
       </c>
       <c r="K2044">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="L2044">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="M2044">
-        <v>3.41</v>
+        <v>2.98</v>
       </c>
       <c r="N2044">
-        <v>4.94</v>
+        <v>4.4</v>
       </c>
       <c r="O2044">
         <v>1</v>
       </c>
       <c r="P2044" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2045" spans="1:16">
       <c r="A2045" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2045" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2045">
-        <v>1.428548452245339</v>
+        <v>1.756511978208985</v>
       </c>
       <c r="D2045" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E2045">
-        <v>1.62846756237276</v>
+        <v>1.778493938049276</v>
       </c>
       <c r="F2045">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2045">
-        <v>0.007771451547754661</v>
+        <v>0.007543488021791016</v>
       </c>
       <c r="H2045">
-        <v>0.00717153243762724</v>
+        <v>0.008081506061950723</v>
       </c>
       <c r="I2045">
-        <v>0.1999191101274214</v>
+        <v>-0.02198195984029105</v>
       </c>
       <c r="J2045">
-        <v>0.9300444421567921</v>
+        <v>0.9214930005703872</v>
       </c>
       <c r="K2045">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="L2045">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="M2045">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="N2045">
-        <v>4.4</v>
+        <v>4.93</v>
       </c>
       <c r="O2045">
         <v>1</v>
       </c>
       <c r="P2045" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2046" spans="1:16">
       <c r="A2046" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2046" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2046">
-        <v>1.729660451627673</v>
+        <v>1.428548452245339</v>
       </c>
       <c r="D2046" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E2046">
-        <v>1.768548452245339</v>
+        <v>1.62846756237276</v>
       </c>
       <c r="F2046">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2046">
-        <v>0.007570339548372328</v>
+        <v>0.007771451547754661</v>
       </c>
       <c r="H2046">
-        <v>0.008111451547754661</v>
+        <v>0.00717153243762724</v>
       </c>
       <c r="I2046">
-        <v>-0.0388880006176664</v>
+        <v>0.1999191101274214</v>
       </c>
       <c r="J2046">
         <v>0.9300444421567921</v>
       </c>
       <c r="K2046">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="L2046">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="M2046">
-        <v>3.41</v>
+        <v>2.98</v>
       </c>
       <c r="N2046">
-        <v>4.94</v>
+        <v>4.4</v>
       </c>
       <c r="O2046">
         <v>1</v>
       </c>
       <c r="P2046" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2047" spans="1:16">
       <c r="A2047" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2047" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2047">
-        <v>1.402533944446475</v>
+        <v>1.78175911836297</v>
       </c>
       <c r="D2047" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E2047">
-        <v>1.605733476378445</v>
+        <v>1.749248007823771</v>
       </c>
       <c r="F2047">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2047">
-        <v>0.007797466055553525</v>
+        <v>0.007678240881637031</v>
       </c>
       <c r="H2047">
-        <v>0.007194266523621556</v>
+        <v>0.008110751992176228</v>
       </c>
       <c r="I2047">
-        <v>0.2031995319319702</v>
+        <v>0.03251111053919864</v>
       </c>
       <c r="J2047">
-        <v>0.9376733300743474</v>
+        <v>0.9300444421567921</v>
       </c>
       <c r="K2047">
-        <v>3.41</v>
+        <v>3.17</v>
       </c>
       <c r="L2047">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="M2047">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="N2047">
-        <v>4.4</v>
+        <v>4.93</v>
       </c>
       <c r="O2047">
         <v>1</v>
       </c>
       <c r="P2047" t="s">
-        <v>274</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2048" spans="1:16">
       <c r="A2048" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2048" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2048">
-        <v>1.705705743566549</v>
+        <v>1.402533944446475</v>
       </c>
       <c r="D2048" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E2048">
-        <v>1.742533944446476</v>
+        <v>1.605733476378445</v>
       </c>
       <c r="F2048">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2048">
-        <v>0.007594294256433452</v>
+        <v>0.007797466055553525</v>
       </c>
       <c r="H2048">
-        <v>0.008137466055553525</v>
+        <v>0.007194266523621556</v>
       </c>
       <c r="I2048">
-        <v>-0.03682820087992633</v>
+        <v>0.2031995319319702</v>
       </c>
       <c r="J2048">
         <v>0.9376733300743474</v>
       </c>
       <c r="K2048">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="L2048">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="M2048">
-        <v>3.41</v>
+        <v>2.98</v>
       </c>
       <c r="N2048">
-        <v>4.94</v>
+        <v>4.4</v>
       </c>
       <c r="O2048">
         <v>1</v>
       </c>
       <c r="P2048" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2049" spans="1:16">
       <c r="A2049" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2049" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C2049">
-        <v>1.567523324934625</v>
+        <v>1.757575543664319</v>
       </c>
       <c r="D2049" t="s">
         <v>464</v>
       </c>
       <c r="E2049">
-        <v>1.538092914204123</v>
+        <v>1.723157211145732</v>
       </c>
       <c r="F2049">
         <v>-1</v>
       </c>
       <c r="G2049">
-        <v>0.007892476675065376</v>
+        <v>0.007702424456335681</v>
       </c>
       <c r="H2049">
-        <v>0.008341907085795878</v>
+        <v>0.008136842788854267</v>
       </c>
       <c r="I2049">
-        <v>0.02943041073050212</v>
+        <v>0.03441833251858784</v>
       </c>
       <c r="J2049">
-        <v>0.9976267113770901</v>
+        <v>0.9376733300743474</v>
       </c>
       <c r="K2049">
         <v>3.17</v>
@@ -104645,15 +104642,65 @@
         <v>4.73</v>
       </c>
       <c r="M2049">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="N2049">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="O2049">
         <v>1</v>
       </c>
       <c r="P2049" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:16">
+      <c r="A2050" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2050" t="s">
+        <v>276</v>
+      </c>
+      <c r="C2050">
+        <v>1.567523324934625</v>
+      </c>
+      <c r="D2050" t="s">
+        <v>464</v>
+      </c>
+      <c r="E2050">
+        <v>1.518116647090352</v>
+      </c>
+      <c r="F2050">
+        <v>-1</v>
+      </c>
+      <c r="G2050">
+        <v>0.007892476675065376</v>
+      </c>
+      <c r="H2050">
+        <v>0.008341883352909647</v>
+      </c>
+      <c r="I2050">
+        <v>0.04940667784427344</v>
+      </c>
+      <c r="J2050">
+        <v>0.9976267113770901</v>
+      </c>
+      <c r="K2050">
+        <v>3.17</v>
+      </c>
+      <c r="L2050">
+        <v>4.73</v>
+      </c>
+      <c r="M2050">
+        <v>3.42</v>
+      </c>
+      <c r="N2050">
+        <v>4.93</v>
+      </c>
+      <c r="O2050">
+        <v>1</v>
+      </c>
+      <c r="P2050" t="s">
         <v>273</v>
       </c>
     </row>

--- a/s60_signal/position-00857-601857.xlsx
+++ b/s60_signal/position-00857-601857.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6186" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6201" uniqueCount="620">
   <si>
     <t>trade_time</t>
   </si>
@@ -850,16 +850,16 @@
     <t>2021-08-11</t>
   </si>
   <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
     <t>2021-08-12</t>
   </si>
   <si>
     <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
   </si>
   <si>
     <t>2016-08-15</t>
@@ -1417,10 +1417,10 @@
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-09-06</t>
+    <t>2021-09-13</t>
   </si>
   <si>
-    <t>2021-09-09</t>
+    <t>2021-08-26</t>
   </si>
   <si>
     <t>2021-08-25</t>
@@ -1863,6 +1863,18 @@
   <si>
     <t>2021-08-10</t>
   </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2021-08-31</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-02</t>
+  </si>
 </sst>
 </file>
 
@@ -2219,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2058"/>
+  <dimension ref="A1:P2063"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -103630,7 +103642,7 @@
         <v>3.581931786909161</v>
       </c>
       <c r="D2029" t="s">
-        <v>467</v>
+        <v>281</v>
       </c>
       <c r="E2029">
         <v>3.541931786909161</v>
@@ -104030,7 +104042,7 @@
         <v>3.667166274669823</v>
       </c>
       <c r="D2037" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E2037">
         <v>3.709563170647197</v>
@@ -104280,10 +104292,10 @@
         <v>3.68869266571118</v>
       </c>
       <c r="D2042" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E2042">
-        <v>3.906050968963969</v>
+        <v>4.042406707131645</v>
       </c>
       <c r="F2042">
         <v>-1</v>
@@ -104292,10 +104304,10 @@
         <v>0.00657130733428882</v>
       </c>
       <c r="H2042">
-        <v>0.006633949031036031</v>
+        <v>0.006957593292868354</v>
       </c>
       <c r="I2042">
-        <v>-0.2173583032527895</v>
+        <v>-0.3537140414204658</v>
       </c>
       <c r="J2042">
         <v>0.4071489644883673</v>
@@ -104307,10 +104319,10 @@
         <v>5.13</v>
       </c>
       <c r="M2042">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="N2042">
-        <v>5.27</v>
+        <v>5.5</v>
       </c>
       <c r="O2042">
         <v>1</v>
@@ -104330,10 +104342,10 @@
         <v>1.780151755152943</v>
       </c>
       <c r="D2043" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E2043">
-        <v>1.949603745862347</v>
+        <v>1.989603745862347</v>
       </c>
       <c r="F2043">
         <v>1</v>
@@ -104342,10 +104354,10 @@
         <v>0.007439848244847058</v>
       </c>
       <c r="H2043">
-        <v>0.007270396254137653</v>
+        <v>0.007310396254137654</v>
       </c>
       <c r="I2043">
-        <v>0.1694519907094043</v>
+        <v>0.2094519907094043</v>
       </c>
       <c r="J2043">
         <v>0.8472599535470232</v>
@@ -104360,7 +104372,7 @@
         <v>3.14</v>
       </c>
       <c r="N2043">
-        <v>4.61</v>
+        <v>4.65</v>
       </c>
       <c r="O2043">
         <v>1</v>
@@ -104374,43 +104386,43 @@
         <v>1</v>
       </c>
       <c r="B2044" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C2044">
-        <v>1.794877750507645</v>
+        <v>2.130699764443538</v>
       </c>
       <c r="D2044" t="s">
-        <v>469</v>
+        <v>280</v>
       </c>
       <c r="E2044">
-        <v>1.949603745862347</v>
+        <v>2.431679155617472</v>
       </c>
       <c r="F2044">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2044">
-        <v>0.007285122249492355</v>
+        <v>0.008129300235556462</v>
       </c>
       <c r="H2044">
-        <v>0.007270396254137653</v>
+        <v>0.008108320844382528</v>
       </c>
       <c r="I2044">
-        <v>0.1547259953547027</v>
+        <v>-0.300979391173934</v>
       </c>
       <c r="J2044">
         <v>0.8472599535470232</v>
       </c>
       <c r="K2044">
-        <v>3.24</v>
+        <v>3.54</v>
       </c>
       <c r="L2044">
-        <v>4.54</v>
+        <v>5.13</v>
       </c>
       <c r="M2044">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="N2044">
-        <v>4.61</v>
+        <v>5.27</v>
       </c>
       <c r="O2044">
         <v>1</v>
@@ -104421,552 +104433,552 @@
     </row>
     <row r="2045" spans="1:16">
       <c r="A2045" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2045" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C2045">
-        <v>2.064042153294824</v>
+        <v>1.558293711144458</v>
       </c>
       <c r="D2045" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E2045">
-        <v>2.431679155617472</v>
+        <v>1.80913262551132</v>
       </c>
       <c r="F2045">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2045">
-        <v>0.007655957846705177</v>
+        <v>0.007641706288855542</v>
       </c>
       <c r="H2045">
-        <v>0.008108320844382528</v>
+        <v>0.007410867374488682</v>
       </c>
       <c r="I2045">
-        <v>-0.3676370023226481</v>
+        <v>0.2508389143668617</v>
       </c>
       <c r="J2045">
-        <v>0.8472599535470232</v>
+        <v>0.8919959791365225</v>
       </c>
       <c r="K2045">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="L2045">
-        <v>4.86</v>
+        <v>4.6</v>
       </c>
       <c r="M2045">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="N2045">
-        <v>5.27</v>
+        <v>4.61</v>
       </c>
       <c r="O2045">
         <v>1</v>
       </c>
       <c r="P2045" t="s">
-        <v>458</v>
+        <v>611</v>
       </c>
     </row>
     <row r="2046" spans="1:16">
       <c r="A2046" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2046" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C2046">
-        <v>2.067644963514478</v>
+        <v>2.029094113230806</v>
       </c>
       <c r="D2046" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E2046">
-        <v>2.431679155617472</v>
+        <v>2.306654394691249</v>
       </c>
       <c r="F2046">
         <v>-1</v>
       </c>
       <c r="G2046">
-        <v>0.008032355036485521</v>
+        <v>0.008290905886769194</v>
       </c>
       <c r="H2046">
-        <v>0.008108320844382528</v>
+        <v>0.008693345605308749</v>
       </c>
       <c r="I2046">
-        <v>-0.3640341921029937</v>
+        <v>-0.2775602814604432</v>
       </c>
       <c r="J2046">
-        <v>0.8472599535470232</v>
+        <v>0.8919959791365225</v>
       </c>
       <c r="K2046">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="L2046">
-        <v>5.05</v>
+        <v>5.16</v>
       </c>
       <c r="M2046">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="N2046">
-        <v>5.27</v>
+        <v>5.5</v>
       </c>
       <c r="O2046">
         <v>1</v>
       </c>
       <c r="P2046" t="s">
-        <v>458</v>
+        <v>611</v>
       </c>
     </row>
     <row r="2047" spans="1:16">
       <c r="A2047" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2047" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C2047">
-        <v>2.130699764443538</v>
+        <v>1.544772806976353</v>
       </c>
       <c r="D2047" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E2047">
-        <v>2.431679155617472</v>
+        <v>1.796682291467962</v>
       </c>
       <c r="F2047">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2047">
-        <v>0.008129300235556462</v>
+        <v>0.007655227193023646</v>
       </c>
       <c r="H2047">
-        <v>0.008108320844382528</v>
+        <v>0.007423317708532038</v>
       </c>
       <c r="I2047">
-        <v>-0.300979391173934</v>
+        <v>0.251909484491609</v>
       </c>
       <c r="J2047">
-        <v>0.8472599535470232</v>
+        <v>0.8959610536726235</v>
       </c>
       <c r="K2047">
-        <v>3.54</v>
+        <v>3.41</v>
       </c>
       <c r="L2047">
-        <v>5.13</v>
+        <v>4.6</v>
       </c>
       <c r="M2047">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="N2047">
-        <v>5.27</v>
+        <v>4.61</v>
       </c>
       <c r="O2047">
         <v>1</v>
       </c>
       <c r="P2047" t="s">
-        <v>458</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2048" spans="1:16">
       <c r="A2048" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2048" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C2048">
-        <v>1.558293711144458</v>
+        <v>2.015176701609092</v>
       </c>
       <c r="D2048" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E2048">
-        <v>1.80913262551132</v>
+        <v>2.292459427852008</v>
       </c>
       <c r="F2048">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2048">
-        <v>0.007641706288855542</v>
+        <v>0.008304823298390907</v>
       </c>
       <c r="H2048">
-        <v>0.007410867374488682</v>
+        <v>0.008707540572147992</v>
       </c>
       <c r="I2048">
-        <v>0.2508389143668617</v>
+        <v>-0.2772827262429161</v>
       </c>
       <c r="J2048">
-        <v>0.8919959791365225</v>
+        <v>0.8959610536726235</v>
       </c>
       <c r="K2048">
-        <v>3.41</v>
+        <v>3.51</v>
       </c>
       <c r="L2048">
-        <v>4.6</v>
+        <v>5.16</v>
       </c>
       <c r="M2048">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="N2048">
-        <v>4.61</v>
+        <v>5.5</v>
       </c>
       <c r="O2048">
         <v>1</v>
       </c>
       <c r="P2048" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2049" spans="1:16">
       <c r="A2049" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2049" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C2049">
-        <v>1.97233423385671</v>
+        <v>1.528218097218324</v>
       </c>
       <c r="D2049" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E2049">
-        <v>2.281813469892649</v>
+        <v>1.78143836518051</v>
       </c>
       <c r="F2049">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2049">
-        <v>0.008287665766143291</v>
+        <v>0.007671781902781675</v>
       </c>
       <c r="H2049">
-        <v>0.008258186530107351</v>
+        <v>0.00743856163481949</v>
       </c>
       <c r="I2049">
-        <v>-0.3094792360359389</v>
+        <v>0.253220267962186</v>
       </c>
       <c r="J2049">
-        <v>0.8919959791365225</v>
+        <v>0.9008158072673534</v>
       </c>
       <c r="K2049">
-        <v>3.54</v>
+        <v>3.41</v>
       </c>
       <c r="L2049">
-        <v>5.13</v>
+        <v>4.6</v>
       </c>
       <c r="M2049">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="N2049">
-        <v>5.27</v>
+        <v>4.61</v>
       </c>
       <c r="O2049">
         <v>1</v>
       </c>
       <c r="P2049" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2050" spans="1:16">
       <c r="A2050" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2050" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C2050">
-        <v>1.544772806976353</v>
+        <v>1.99813651649159</v>
       </c>
       <c r="D2050" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E2050">
-        <v>1.796682291467962</v>
+        <v>2.275079409982875</v>
       </c>
       <c r="F2050">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2050">
-        <v>0.007655227193023646</v>
+        <v>0.008321863483508411</v>
       </c>
       <c r="H2050">
-        <v>0.007423317708532038</v>
+        <v>0.008724920590017126</v>
       </c>
       <c r="I2050">
-        <v>0.251909484491609</v>
+        <v>-0.276942893491285</v>
       </c>
       <c r="J2050">
-        <v>0.8959610536726235</v>
+        <v>0.9008158072673534</v>
       </c>
       <c r="K2050">
-        <v>3.41</v>
+        <v>3.51</v>
       </c>
       <c r="L2050">
-        <v>4.6</v>
+        <v>5.16</v>
       </c>
       <c r="M2050">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="N2050">
-        <v>4.61</v>
+        <v>5.5</v>
       </c>
       <c r="O2050">
         <v>1</v>
       </c>
       <c r="P2050" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2051" spans="1:16">
       <c r="A2051" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2051" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C2051">
-        <v>1.958297869998913</v>
+        <v>1.532213378094907</v>
       </c>
       <c r="D2051" t="s">
         <v>468</v>
       </c>
       <c r="E2051">
-        <v>2.268530470196711</v>
+        <v>1.756511978208985</v>
       </c>
       <c r="F2051">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2051">
-        <v>0.008301702130001086</v>
+        <v>0.007687786621905094</v>
       </c>
       <c r="H2051">
-        <v>0.008271469529803288</v>
+        <v>0.007543488021791016</v>
       </c>
       <c r="I2051">
-        <v>-0.3102326001977982</v>
+        <v>0.2242986001140772</v>
       </c>
       <c r="J2051">
-        <v>0.8959610536726235</v>
+        <v>0.9214930005703872</v>
       </c>
       <c r="K2051">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="L2051">
-        <v>5.13</v>
+        <v>4.61</v>
       </c>
       <c r="M2051">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="N2051">
-        <v>5.27</v>
+        <v>4.65</v>
       </c>
       <c r="O2051">
         <v>1</v>
       </c>
       <c r="P2051" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2052" spans="1:16">
       <c r="A2052" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2052" t="s">
         <v>280</v>
       </c>
       <c r="C2052">
-        <v>1.528218097218324</v>
+        <v>2.182998448089203</v>
       </c>
       <c r="D2052" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E2052">
-        <v>1.78143836518051</v>
+        <v>2.201055057958014</v>
       </c>
       <c r="F2052">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2052">
-        <v>0.007671781902781675</v>
+        <v>0.008357001551910796</v>
       </c>
       <c r="H2052">
-        <v>0.00743856163481949</v>
+        <v>0.008798944942041987</v>
       </c>
       <c r="I2052">
-        <v>0.253220267962186</v>
+        <v>-0.01805660986881108</v>
       </c>
       <c r="J2052">
-        <v>0.9008158072673534</v>
+        <v>0.9214930005703872</v>
       </c>
       <c r="K2052">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="L2052">
-        <v>4.6</v>
+        <v>5.27</v>
       </c>
       <c r="M2052">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="N2052">
-        <v>4.61</v>
+        <v>5.5</v>
       </c>
       <c r="O2052">
         <v>1</v>
       </c>
       <c r="P2052" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2053" spans="1:16">
       <c r="A2053" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2053" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C2053">
-        <v>1.941112042273569</v>
+        <v>1.503651563196315</v>
       </c>
       <c r="D2053" t="s">
         <v>468</v>
       </c>
       <c r="E2053">
-        <v>2.252267045654365</v>
+        <v>1.729660451627673</v>
       </c>
       <c r="F2053">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2053">
-        <v>0.008318887957726432</v>
+        <v>0.007716348436803686</v>
       </c>
       <c r="H2053">
-        <v>0.008287732954345635</v>
+        <v>0.007570339548372328</v>
       </c>
       <c r="I2053">
-        <v>-0.3111550033807968</v>
+        <v>0.226008888431358</v>
       </c>
       <c r="J2053">
-        <v>0.9008158072673534</v>
+        <v>0.9300444421567921</v>
       </c>
       <c r="K2053">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="L2053">
-        <v>5.13</v>
+        <v>4.61</v>
       </c>
       <c r="M2053">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="N2053">
-        <v>5.27</v>
+        <v>4.65</v>
       </c>
       <c r="O2053">
         <v>1</v>
       </c>
       <c r="P2053" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2054" spans="1:16">
       <c r="A2054" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2054" t="s">
         <v>280</v>
       </c>
       <c r="C2054">
-        <v>1.457708868054979</v>
+        <v>2.154351118774746</v>
       </c>
       <c r="D2054" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E2054">
-        <v>1.716511978208985</v>
+        <v>2.170440897078684</v>
       </c>
       <c r="F2054">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2054">
-        <v>0.00774229113194502</v>
+        <v>0.008385648881225253</v>
       </c>
       <c r="H2054">
-        <v>0.007503488021791016</v>
+        <v>0.008829559102921316</v>
       </c>
       <c r="I2054">
-        <v>0.2588031101540054</v>
+        <v>-0.01608977830393821</v>
       </c>
       <c r="J2054">
-        <v>0.9214930005703872</v>
+        <v>0.9300444421567921</v>
       </c>
       <c r="K2054">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="L2054">
-        <v>4.6</v>
+        <v>5.27</v>
       </c>
       <c r="M2054">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="N2054">
-        <v>4.61</v>
+        <v>5.5</v>
       </c>
       <c r="O2054">
         <v>1</v>
       </c>
       <c r="P2054" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2055" spans="1:16">
       <c r="A2055" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2055" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C2055">
-        <v>1.867914777980829</v>
+        <v>2.128794344250936</v>
       </c>
       <c r="D2055" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E2055">
-        <v>2.182998448089203</v>
+        <v>2.143129478333836</v>
       </c>
       <c r="F2055">
         <v>-1</v>
       </c>
       <c r="G2055">
-        <v>0.008392085222019171</v>
+        <v>0.008411205655749062</v>
       </c>
       <c r="H2055">
-        <v>0.008357001551910796</v>
+        <v>0.008856870521666163</v>
       </c>
       <c r="I2055">
-        <v>-0.3150836701083732</v>
+        <v>-0.01433513408290032</v>
       </c>
       <c r="J2055">
-        <v>0.9214930005703872</v>
+        <v>0.9376733300743474</v>
       </c>
       <c r="K2055">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="L2055">
-        <v>5.13</v>
+        <v>5.27</v>
       </c>
       <c r="M2055">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="N2055">
-        <v>5.27</v>
+        <v>5.5</v>
       </c>
       <c r="O2055">
         <v>1</v>
       </c>
       <c r="P2055" t="s">
-        <v>614</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2056" spans="1:16">
@@ -104974,99 +104986,99 @@
         <v>0</v>
       </c>
       <c r="B2056" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C2056">
-        <v>1.503651563196315</v>
+        <v>1.927950516886748</v>
       </c>
       <c r="D2056" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E2056">
-        <v>1.689660451627673</v>
+        <v>1.928496373270017</v>
       </c>
       <c r="F2056">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2056">
-        <v>0.007716348436803686</v>
+        <v>0.008612049483113251</v>
       </c>
       <c r="H2056">
-        <v>0.007530339548372328</v>
+        <v>0.009071503626729984</v>
       </c>
       <c r="I2056">
-        <v>0.186008888431358</v>
+        <v>-0.0005458563832694274</v>
       </c>
       <c r="J2056">
-        <v>0.9300444421567921</v>
+        <v>0.9976267113770901</v>
       </c>
       <c r="K2056">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="L2056">
-        <v>4.61</v>
+        <v>5.27</v>
       </c>
       <c r="M2056">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="N2056">
-        <v>4.61</v>
+        <v>5.5</v>
       </c>
       <c r="O2056">
         <v>1</v>
       </c>
       <c r="P2056" t="s">
-        <v>615</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2057" spans="1:16">
       <c r="A2057" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2057" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C2057">
-        <v>1.89554400802966</v>
+        <v>1.904942733140869</v>
       </c>
       <c r="D2057" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E2057">
-        <v>2.154351118774746</v>
+        <v>1.903908950640094</v>
       </c>
       <c r="F2057">
         <v>-1</v>
       </c>
       <c r="G2057">
-        <v>0.00842445599197034</v>
+        <v>0.00863505726685913</v>
       </c>
       <c r="H2057">
-        <v>0.008385648881225253</v>
+        <v>0.009096091049359906</v>
       </c>
       <c r="I2057">
-        <v>-0.258807110745086</v>
+        <v>0.001033782500775349</v>
       </c>
       <c r="J2057">
-        <v>0.9300444421567921</v>
+        <v>1.004494706525114</v>
       </c>
       <c r="K2057">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="L2057">
-        <v>5.16</v>
+        <v>5.27</v>
       </c>
       <c r="M2057">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="N2057">
-        <v>5.27</v>
+        <v>5.5</v>
       </c>
       <c r="O2057">
         <v>1</v>
       </c>
       <c r="P2057" t="s">
-        <v>615</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2058" spans="1:16">
@@ -105074,49 +105086,299 @@
         <v>0</v>
       </c>
       <c r="B2058" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C2058">
-        <v>1.868766611439041</v>
+        <v>1.897212176017408</v>
       </c>
       <c r="D2058" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E2058">
-        <v>2.128794344250936</v>
+        <v>1.895647638848455</v>
       </c>
       <c r="F2058">
         <v>-1</v>
       </c>
       <c r="G2058">
-        <v>0.00845123338856096</v>
+        <v>0.008642787823982591</v>
       </c>
       <c r="H2058">
-        <v>0.008411205655749062</v>
+        <v>0.009104352361151544</v>
       </c>
       <c r="I2058">
-        <v>-0.2600277328118947</v>
+        <v>0.001564537168953439</v>
       </c>
       <c r="J2058">
-        <v>0.9376733300743474</v>
+        <v>1.006802335517191</v>
       </c>
       <c r="K2058">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="L2058">
-        <v>5.16</v>
+        <v>5.27</v>
       </c>
       <c r="M2058">
+        <v>3.58</v>
+      </c>
+      <c r="N2058">
+        <v>5.5</v>
+      </c>
+      <c r="O2058">
+        <v>1</v>
+      </c>
+      <c r="P2058" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:16">
+      <c r="A2059" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2059" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2059">
+        <v>1.883275808664677</v>
+      </c>
+      <c r="D2059" t="s">
+        <v>467</v>
+      </c>
+      <c r="E2059">
+        <v>1.880754446274492</v>
+      </c>
+      <c r="F2059">
+        <v>-1</v>
+      </c>
+      <c r="G2059">
+        <v>0.008656724191335322</v>
+      </c>
+      <c r="H2059">
+        <v>0.00911924555372551</v>
+      </c>
+      <c r="I2059">
+        <v>0.002521362390185633</v>
+      </c>
+      <c r="J2059">
+        <v>1.010962445174723</v>
+      </c>
+      <c r="K2059">
         <v>3.35</v>
       </c>
-      <c r="N2058">
+      <c r="L2059">
         <v>5.27</v>
       </c>
-      <c r="O2058">
-        <v>1</v>
-      </c>
-      <c r="P2058" t="s">
-        <v>277</v>
+      <c r="M2059">
+        <v>3.58</v>
+      </c>
+      <c r="N2059">
+        <v>5.5</v>
+      </c>
+      <c r="O2059">
+        <v>1</v>
+      </c>
+      <c r="P2059" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:16">
+      <c r="A2060" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2060" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2060">
+        <v>1.871766371196939</v>
+      </c>
+      <c r="D2060" t="s">
+        <v>467</v>
+      </c>
+      <c r="E2060">
+        <v>1.8684548086224</v>
+      </c>
+      <c r="F2060">
+        <v>-1</v>
+      </c>
+      <c r="G2060">
+        <v>0.008668233628803061</v>
+      </c>
+      <c r="H2060">
+        <v>0.009131545191377599</v>
+      </c>
+      <c r="I2060">
+        <v>0.003311562574538129</v>
+      </c>
+      <c r="J2060">
+        <v>1.014398098150167</v>
+      </c>
+      <c r="K2060">
+        <v>3.35</v>
+      </c>
+      <c r="L2060">
+        <v>5.27</v>
+      </c>
+      <c r="M2060">
+        <v>3.58</v>
+      </c>
+      <c r="N2060">
+        <v>5.5</v>
+      </c>
+      <c r="O2060">
+        <v>1</v>
+      </c>
+      <c r="P2060" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:16">
+      <c r="A2061" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2061" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2061">
+        <v>1.854141549147799</v>
+      </c>
+      <c r="D2061" t="s">
+        <v>467</v>
+      </c>
+      <c r="E2061">
+        <v>1.849619924163917</v>
+      </c>
+      <c r="F2061">
+        <v>-1</v>
+      </c>
+      <c r="G2061">
+        <v>0.008685858450852202</v>
+      </c>
+      <c r="H2061">
+        <v>0.009150380075836082</v>
+      </c>
+      <c r="I2061">
+        <v>0.004521624983881978</v>
+      </c>
+      <c r="J2061">
+        <v>1.019659239060358</v>
+      </c>
+      <c r="K2061">
+        <v>3.35</v>
+      </c>
+      <c r="L2061">
+        <v>5.27</v>
+      </c>
+      <c r="M2061">
+        <v>3.58</v>
+      </c>
+      <c r="N2061">
+        <v>5.5</v>
+      </c>
+      <c r="O2061">
+        <v>1</v>
+      </c>
+      <c r="P2061" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:16">
+      <c r="A2062" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2062" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2062">
+        <v>1.408244507803489</v>
+      </c>
+      <c r="D2062" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2062">
+        <v>1.842192926460707</v>
+      </c>
+      <c r="F2062">
+        <v>1</v>
+      </c>
+      <c r="G2062">
+        <v>0.00861175549219651</v>
+      </c>
+      <c r="H2062">
+        <v>0.008697807073539293</v>
+      </c>
+      <c r="I2062">
+        <v>0.4339484186572173</v>
+      </c>
+      <c r="J2062">
+        <v>1.023225992101281</v>
+      </c>
+      <c r="K2062">
+        <v>3.52</v>
+      </c>
+      <c r="L2062">
+        <v>5.01</v>
+      </c>
+      <c r="M2062">
+        <v>3.35</v>
+      </c>
+      <c r="N2062">
+        <v>5.27</v>
+      </c>
+      <c r="O2062">
+        <v>1</v>
+      </c>
+      <c r="P2062" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:16">
+      <c r="A2063" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2063" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2063">
+        <v>1.399942599777031</v>
+      </c>
+      <c r="D2063" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2063">
+        <v>1.834291962855981</v>
+      </c>
+      <c r="F2063">
+        <v>1</v>
+      </c>
+      <c r="G2063">
+        <v>0.008620057400222968</v>
+      </c>
+      <c r="H2063">
+        <v>0.008705708037144017</v>
+      </c>
+      <c r="I2063">
+        <v>0.4343493630789497</v>
+      </c>
+      <c r="J2063">
+        <v>1.025584488699707</v>
+      </c>
+      <c r="K2063">
+        <v>3.52</v>
+      </c>
+      <c r="L2063">
+        <v>5.01</v>
+      </c>
+      <c r="M2063">
+        <v>3.35</v>
+      </c>
+      <c r="N2063">
+        <v>5.27</v>
+      </c>
+      <c r="O2063">
+        <v>1</v>
+      </c>
+      <c r="P2063" t="s">
+        <v>619</v>
       </c>
     </row>
   </sheetData>
